--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2780" uniqueCount="856">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2802" uniqueCount="859">
   <si>
     <t>현재 구현 규칙</t>
   </si>
@@ -211,7 +211,7 @@
     <t>총 노드</t>
   </si>
   <si>
-    <t>8구역 × 20노드</t>
+    <t>8구역 × 30노드</t>
   </si>
   <si>
     <t>src/data/facilityLayout.js</t>
@@ -1747,9 +1747,6 @@
     <t>① 체력 보강</t>
   </si>
   <si>
-    <t>{"유형":"maxHpBonus","수치":7}</t>
-  </si>
-  <si>
     <t>최대 체력 +7</t>
   </si>
   <si>
@@ -1759,10 +1756,7 @@
     <t>② 위협 감지</t>
   </si>
   <si>
-    <t>{"유형":"combatStartDebuffAll","취약":1,"약화":1}</t>
-  </si>
-  <si>
-    <t>전투 시작 시 모든 적 취약1·약화1</t>
+    <t>전투 시작 시 모든 적 취약1·약화1 (과부화 획득 +20%)</t>
   </si>
   <si>
     <t>지각 +1</t>
@@ -1774,9 +1768,6 @@
     <t>③ 수납 확장</t>
   </si>
   <si>
-    <t>{"유형":"inventoryBonus","수치":5}</t>
-  </si>
-  <si>
     <t>인벤토리 +5칸</t>
   </si>
   <si>
@@ -1786,10 +1777,7 @@
     <t>④ 반응 가속</t>
   </si>
   <si>
-    <t>{"유형":"extraDrawPerTurn","수치":1}</t>
-  </si>
-  <si>
-    <t>매턴 드로우 +1</t>
+    <t>매턴 드로우 +1 (과부화 획득 +20%)</t>
   </si>
   <si>
     <t>기동 +1</t>
@@ -1801,9 +1789,6 @@
     <t>⑤ 열 차단</t>
   </si>
   <si>
-    <t>{"유형":"overloadGainMultiplier","multiplier":0.5}</t>
-  </si>
-  <si>
     <t>획득 과부화 50% 차감</t>
   </si>
   <si>
@@ -1813,10 +1798,16 @@
     <t>⑥ 산개 방출</t>
   </si>
   <si>
-    <t>{"유형":"turnStartAoeDamage","수치":3}</t>
-  </si>
-  <si>
-    <t>매턴 시작 광역 3 피해</t>
+    <t>매턴 시작 광역 3 피해 (과부화 획득 +15%)</t>
+  </si>
+  <si>
+    <t>implant7</t>
+  </si>
+  <si>
+    <t>⑦ 지도</t>
+  </si>
+  <si>
+    <t>현재 구역 핵심시설 위치를 화살표로 표시(그 노드를 확인하면 사라짐)</t>
   </si>
   <si>
     <t>몬스터 스펙</t>
@@ -2335,6 +2326,24 @@
     <t>CAMERA_STEALTH_THRESHOLD</t>
   </si>
   <si>
+    <t>기타</t>
+  </si>
+  <si>
+    <t>CONCEALMENT_ACTION_TIME_COST</t>
+  </si>
+  <si>
+    <t>CONCEALMENT_NODE_WEIGHTS</t>
+  </si>
+  <si>
+    <t>[{"수치":0,"weight":60},{"수치":1,"weight":16},{"수치":2,"weight":14},{"수치":3,"weight":10}]</t>
+  </si>
+  <si>
+    <t>CONTROL_ROOM_HACK_OVERLOAD</t>
+  </si>
+  <si>
+    <t>CONTROL_ROOM_HACK_TIME</t>
+  </si>
+  <si>
     <t>CROSS_SECTOR_SPECIAL_EDGES_MAX</t>
   </si>
   <si>
@@ -2353,9 +2362,6 @@
     <t>ENTRANCE_THREAT_MAX_GROUP_SIZE</t>
   </si>
   <si>
-    <t>기타</t>
-  </si>
-  <si>
     <t>EVIDENCE_TRACE_DURATION_LIGHT</t>
   </si>
   <si>
@@ -2504,6 +2510,9 @@
   </si>
   <si>
     <t>[["entrance","labs"],["labs","hangar"],["hangar","security"],["security","파워"],["파워","waste"],["waste","comms"],["comms","residential"],["residential","entrance"]]</t>
+  </si>
+  <si>
+    <t>SECTOR_ALERT_DECAY_INTERVAL</t>
   </si>
   <si>
     <t>SECTOR_ALERT_INVESTIGATE_INTERVAL</t>
@@ -3386,7 +3395,7 @@
         <v>62</v>
       </c>
       <c r="C22" s="6">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>63</v>
@@ -3513,7 +3522,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -3524,7 +3533,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3532,7 +3541,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3544,10 +3553,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>6</v>
@@ -3555,10 +3564,10 @@
     </row>
     <row r="5" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="C5" s="5">
         <v>0.16</v>
@@ -3569,10 +3578,10 @@
     </row>
     <row r="6" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C6" s="6">
         <v>20</v>
@@ -3583,13 +3592,13 @@
     </row>
     <row r="7" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>64</v>
@@ -3597,13 +3606,13 @@
     </row>
     <row r="8" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>64</v>
@@ -3611,10 +3620,10 @@
     </row>
     <row r="9" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="C9" s="5">
         <v>4</v>
@@ -3625,10 +3634,10 @@
     </row>
     <row r="10" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="C10" s="6">
         <v>2</v>
@@ -3639,10 +3648,10 @@
     </row>
     <row r="11" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="C11" s="5">
         <v>80</v>
@@ -3653,10 +3662,10 @@
     </row>
     <row r="12" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C12" s="6">
         <v>3</v>
@@ -3667,10 +3676,10 @@
     </row>
     <row r="13" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="C13" s="5">
         <v>2</v>
@@ -3681,10 +3690,10 @@
     </row>
     <row r="14" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="C14" s="6">
         <v>100</v>
@@ -3695,10 +3704,10 @@
     </row>
     <row r="15" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="C15" s="5">
         <v>300</v>
@@ -3709,10 +3718,10 @@
     </row>
     <row r="16" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>762</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>765</v>
       </c>
       <c r="C16" s="6">
         <v>6</v>
@@ -3723,13 +3732,13 @@
     </row>
     <row r="17" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>64</v>
@@ -3737,10 +3746,10 @@
     </row>
     <row r="18" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="C18" s="6">
         <v>100</v>
@@ -3751,10 +3760,10 @@
     </row>
     <row r="19" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="C19" s="5">
         <v>0.22</v>
@@ -3765,10 +3774,10 @@
     </row>
     <row r="20" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="C20" s="6">
         <v>3</v>
@@ -3779,13 +3788,13 @@
     </row>
     <row r="21" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>748</v>
+        <v>768</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C21" s="5">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>64</v>
@@ -3793,13 +3802,13 @@
     </row>
     <row r="22" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>772</v>
-      </c>
-      <c r="C22" s="6">
-        <v>2</v>
+        <v>770</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>771</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>64</v>
@@ -3807,13 +3816,13 @@
     </row>
     <row r="23" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>748</v>
+        <v>32</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C23" s="5">
-        <v>260</v>
+        <v>10</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>64</v>
@@ -3821,13 +3830,13 @@
     </row>
     <row r="24" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>748</v>
+        <v>768</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C24" s="6">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>64</v>
@@ -3835,13 +3844,13 @@
     </row>
     <row r="25" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C25" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>64</v>
@@ -3849,10 +3858,10 @@
     </row>
     <row r="26" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C26" s="6">
         <v>2</v>
@@ -3863,13 +3872,13 @@
     </row>
     <row r="27" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>777</v>
+        <v>745</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>778</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>280</v>
+        <v>776</v>
+      </c>
+      <c r="C27" s="5">
+        <v>260</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>64</v>
@@ -3877,13 +3886,13 @@
     </row>
     <row r="28" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>69</v>
+        <v>745</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C28" s="6">
-        <v>8600</v>
+        <v>40</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>64</v>
@@ -3891,13 +3900,13 @@
     </row>
     <row r="29" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>69</v>
+        <v>745</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C29" s="5">
-        <v>13400</v>
+        <v>2</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>64</v>
@@ -3905,13 +3914,13 @@
     </row>
     <row r="30" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>69</v>
+        <v>749</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>781</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>782</v>
+        <v>779</v>
+      </c>
+      <c r="C30" s="6">
+        <v>2</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>64</v>
@@ -3919,13 +3928,13 @@
     </row>
     <row r="31" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>69</v>
+        <v>768</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>784</v>
+        <v>280</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>64</v>
@@ -3936,10 +3945,10 @@
         <v>69</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C32" s="6">
-        <v>100</v>
+        <v>8600</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>64</v>
@@ -3950,10 +3959,10 @@
         <v>69</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="C33" s="5">
-        <v>50</v>
+        <v>13400</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>64</v>
@@ -3961,13 +3970,13 @@
     </row>
     <row r="34" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>777</v>
+        <v>69</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>787</v>
-      </c>
-      <c r="C34" s="6">
-        <v>256</v>
+        <v>783</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>784</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>64</v>
@@ -3975,13 +3984,13 @@
     </row>
     <row r="35" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>752</v>
+        <v>69</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>788</v>
-      </c>
-      <c r="C35" s="5">
-        <v>1</v>
+        <v>785</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>786</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>64</v>
@@ -3989,13 +3998,13 @@
     </row>
     <row r="36" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>750</v>
+        <v>69</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C36" s="6">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>64</v>
@@ -4003,13 +4012,13 @@
     </row>
     <row r="37" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>752</v>
+        <v>69</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C37" s="5">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>64</v>
@@ -4017,13 +4026,13 @@
     </row>
     <row r="38" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>750</v>
+        <v>768</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C38" s="6">
-        <v>100</v>
+        <v>256</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>64</v>
@@ -4031,13 +4040,13 @@
     </row>
     <row r="39" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C39" s="5">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>64</v>
@@ -4045,13 +4054,13 @@
     </row>
     <row r="40" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>762</v>
+        <v>747</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C40" s="6">
-        <v>5</v>
+        <v>140</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>64</v>
@@ -4059,10 +4068,10 @@
     </row>
     <row r="41" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C41" s="5">
         <v>2</v>
@@ -4073,10 +4082,10 @@
     </row>
     <row r="42" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>762</v>
+        <v>747</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C42" s="6">
         <v>100</v>
@@ -4087,13 +4096,13 @@
     </row>
     <row r="43" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>762</v>
+        <v>745</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C43" s="5">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>64</v>
@@ -4101,13 +4110,13 @@
     </row>
     <row r="44" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C44" s="6">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>64</v>
@@ -4115,13 +4124,13 @@
     </row>
     <row r="45" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>798</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>799</v>
+        <v>796</v>
+      </c>
+      <c r="C45" s="5">
+        <v>2</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>64</v>
@@ -4129,13 +4138,13 @@
     </row>
     <row r="46" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="C46" s="6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>64</v>
@@ -4143,13 +4152,13 @@
     </row>
     <row r="47" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>750</v>
+        <v>759</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="C47" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>64</v>
@@ -4157,13 +4166,13 @@
     </row>
     <row r="48" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>750</v>
+        <v>759</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C48" s="6">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>64</v>
@@ -4171,13 +4180,13 @@
     </row>
     <row r="49" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>803</v>
-      </c>
-      <c r="C49" s="5">
-        <v>300</v>
+        <v>800</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>801</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>64</v>
@@ -4185,13 +4194,13 @@
     </row>
     <row r="50" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>804</v>
+        <v>749</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="C50" s="6">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>64</v>
@@ -4199,13 +4208,13 @@
     </row>
     <row r="51" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>806</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>807</v>
+        <v>803</v>
+      </c>
+      <c r="C51" s="5">
+        <v>3</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>64</v>
@@ -4213,13 +4222,13 @@
     </row>
     <row r="52" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="C52" s="6">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>64</v>
@@ -4227,13 +4236,13 @@
     </row>
     <row r="53" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="C53" s="5">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>64</v>
@@ -4241,13 +4250,13 @@
     </row>
     <row r="54" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>750</v>
+        <v>806</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>810</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>811</v>
+        <v>807</v>
+      </c>
+      <c r="C54" s="6">
+        <v>0.01</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>64</v>
@@ -4255,13 +4264,13 @@
     </row>
     <row r="55" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>812</v>
-      </c>
-      <c r="C55" s="5">
-        <v>55</v>
+        <v>808</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>809</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>64</v>
@@ -4269,13 +4278,13 @@
     </row>
     <row r="56" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="C56" s="6">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>64</v>
@@ -4283,13 +4292,13 @@
     </row>
     <row r="57" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C57" s="5">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>64</v>
@@ -4297,13 +4306,13 @@
     </row>
     <row r="58" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>815</v>
-      </c>
-      <c r="C58" s="6">
-        <v>100</v>
+        <v>812</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>813</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>64</v>
@@ -4311,13 +4320,13 @@
     </row>
     <row r="59" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>816</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>817</v>
+        <v>814</v>
+      </c>
+      <c r="C59" s="5">
+        <v>55</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>64</v>
@@ -4325,13 +4334,13 @@
     </row>
     <row r="60" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>804</v>
+        <v>745</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>818</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>819</v>
+        <v>815</v>
+      </c>
+      <c r="C60" s="6">
+        <v>40</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>64</v>
@@ -4339,13 +4348,13 @@
     </row>
     <row r="61" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>804</v>
+        <v>745</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>820</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>821</v>
+        <v>816</v>
+      </c>
+      <c r="C61" s="5">
+        <v>30</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>64</v>
@@ -4353,10 +4362,10 @@
     </row>
     <row r="62" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>32</v>
+        <v>749</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="C62" s="6">
         <v>100</v>
@@ -4367,13 +4376,13 @@
     </row>
     <row r="63" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>32</v>
+        <v>749</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>823</v>
-      </c>
-      <c r="C63" s="5">
-        <v>0</v>
+        <v>818</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>819</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>64</v>
@@ -4381,13 +4390,13 @@
     </row>
     <row r="64" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>69</v>
+        <v>806</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>824</v>
-      </c>
-      <c r="C64" s="6">
-        <v>14000</v>
+        <v>820</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>821</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>64</v>
@@ -4395,13 +4404,13 @@
     </row>
     <row r="65" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>32</v>
+        <v>806</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>825</v>
-      </c>
-      <c r="C65" s="5">
-        <v>6</v>
+        <v>822</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>823</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>64</v>
@@ -4409,13 +4418,13 @@
     </row>
     <row r="66" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>748</v>
+        <v>32</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>826</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>827</v>
+        <v>824</v>
+      </c>
+      <c r="C66" s="6">
+        <v>100</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>64</v>
@@ -4423,13 +4432,13 @@
     </row>
     <row r="67" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>752</v>
+        <v>32</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>828</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>829</v>
+        <v>825</v>
+      </c>
+      <c r="C67" s="5">
+        <v>0</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>64</v>
@@ -4437,13 +4446,13 @@
     </row>
     <row r="68" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>752</v>
+        <v>69</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>830</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>831</v>
+        <v>826</v>
+      </c>
+      <c r="C68" s="6">
+        <v>14000</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>64</v>
@@ -4451,13 +4460,13 @@
     </row>
     <row r="69" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>748</v>
+        <v>32</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>832</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>833</v>
+        <v>827</v>
+      </c>
+      <c r="C69" s="5">
+        <v>6</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>64</v>
@@ -4465,13 +4474,13 @@
     </row>
     <row r="70" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>64</v>
@@ -4479,13 +4488,13 @@
     </row>
     <row r="71" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="C71" s="5">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>64</v>
@@ -4493,13 +4502,13 @@
     </row>
     <row r="72" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>837</v>
-      </c>
-      <c r="C72" s="6">
-        <v>900</v>
+        <v>831</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>832</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>64</v>
@@ -4507,13 +4516,13 @@
     </row>
     <row r="73" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>64</v>
@@ -4521,13 +4530,13 @@
     </row>
     <row r="74" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>840</v>
-      </c>
-      <c r="C74" s="6">
-        <v>0.3</v>
+        <v>835</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>836</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>64</v>
@@ -4535,13 +4544,13 @@
     </row>
     <row r="75" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>841</v>
-      </c>
-      <c r="C75" s="5">
-        <v>6</v>
+        <v>837</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>838</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>64</v>
@@ -4549,13 +4558,13 @@
     </row>
     <row r="76" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C76" s="6">
-        <v>4</v>
+        <v>280</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>64</v>
@@ -4563,13 +4572,13 @@
     </row>
     <row r="77" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="C77" s="5">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>64</v>
@@ -4577,13 +4586,13 @@
     </row>
     <row r="78" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>64</v>
@@ -4591,13 +4600,13 @@
     </row>
     <row r="79" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>846</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>847</v>
+        <v>843</v>
+      </c>
+      <c r="C79" s="5">
+        <v>0.3</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>64</v>
@@ -4605,13 +4614,13 @@
     </row>
     <row r="80" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="C80" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>64</v>
@@ -4619,13 +4628,13 @@
     </row>
     <row r="81" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="C81" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>64</v>
@@ -4633,13 +4642,13 @@
     </row>
     <row r="82" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>850</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>851</v>
+        <v>846</v>
+      </c>
+      <c r="C82" s="6">
+        <v>100</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>64</v>
@@ -4647,13 +4656,13 @@
     </row>
     <row r="83" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>852</v>
-      </c>
-      <c r="C83" s="5">
-        <v>4</v>
+        <v>847</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>848</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>64</v>
@@ -4661,13 +4670,13 @@
     </row>
     <row r="84" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>853</v>
-      </c>
-      <c r="C84" s="6">
-        <v>2</v>
+        <v>849</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>850</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>64</v>
@@ -4675,13 +4684,13 @@
     </row>
     <row r="85" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C85" s="5">
-        <v>160</v>
+        <v>2</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>64</v>
@@ -4689,20 +4698,90 @@
     </row>
     <row r="86" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>777</v>
+        <v>749</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="C86" s="6">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>64</v>
       </c>
     </row>
+    <row r="87" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>853</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>854</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="6" t="s">
+        <v>749</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="C88" s="6">
+        <v>4</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>856</v>
+      </c>
+      <c r="C89" s="5">
+        <v>2</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>857</v>
+      </c>
+      <c r="C90" s="6">
+        <v>240</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>858</v>
+      </c>
+      <c r="C91" s="5">
+        <v>10</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:D86"/>
+  <autoFilter ref="A4:D91"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -10184,7 +10263,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -10252,10 +10331,10 @@
         <v>10</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>575</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>576</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>280</v>
@@ -10266,22 +10345,22 @@
     </row>
     <row r="6" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>577</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="8">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>578</v>
       </c>
-      <c r="C6" s="8">
-        <v>20</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>579</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>580</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>581</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>280</v>
@@ -10289,19 +10368,19 @@
     </row>
     <row r="7" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C7" s="7">
         <v>5</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>584</v>
+        <v>280</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>280</v>
@@ -10312,22 +10391,22 @@
     </row>
     <row r="8" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="C8" s="8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>586</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>587</v>
-      </c>
-      <c r="C8" s="8">
-        <v>20</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>588</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>589</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>590</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>280</v>
@@ -10335,19 +10414,19 @@
     </row>
     <row r="9" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C9" s="7">
         <v>30</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>593</v>
+        <v>280</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>280</v>
@@ -10358,29 +10437,52 @@
     </row>
     <row r="10" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="C10" s="8">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="C11" s="7">
+        <v>15</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>596</v>
-      </c>
-      <c r="C10" s="8">
-        <v>15</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>597</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>598</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="G10" s="6" t="s">
+      <c r="F11" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>280</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G10"/>
+  <autoFilter ref="A4:G11"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
@@ -10410,7 +10512,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10424,7 +10526,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10439,42 +10541,42 @@
     <row r="3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>263</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>606</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>608</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>193</v>
@@ -10503,10 +10605,10 @@
     </row>
     <row r="6" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>193</v>
@@ -10535,10 +10637,10 @@
     </row>
     <row r="7" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>193</v>
@@ -10567,10 +10669,10 @@
     </row>
     <row r="8" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>193</v>
@@ -10599,10 +10701,10 @@
     </row>
     <row r="9" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>193</v>
@@ -10631,10 +10733,10 @@
     </row>
     <row r="10" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>193</v>
@@ -10663,10 +10765,10 @@
     </row>
     <row r="11" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>193</v>
@@ -10695,10 +10797,10 @@
     </row>
     <row r="12" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>193</v>
@@ -10727,10 +10829,10 @@
     </row>
     <row r="13" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>193</v>
@@ -10745,7 +10847,7 @@
         <v>280</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>280</v>
@@ -10759,10 +10861,10 @@
     </row>
     <row r="14" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>193</v>
@@ -10791,10 +10893,10 @@
     </row>
     <row r="15" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>193</v>
@@ -10823,10 +10925,10 @@
     </row>
     <row r="16" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>193</v>
@@ -10855,10 +10957,10 @@
     </row>
     <row r="17" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>193</v>
@@ -10887,10 +10989,10 @@
     </row>
     <row r="18" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>217</v>
@@ -10919,10 +11021,10 @@
     </row>
     <row r="19" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>217</v>
@@ -10951,10 +11053,10 @@
     </row>
     <row r="20" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>217</v>
@@ -10983,10 +11085,10 @@
     </row>
     <row r="21" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>134</v>
@@ -11015,10 +11117,10 @@
     </row>
     <row r="22" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>134</v>
@@ -11047,10 +11149,10 @@
     </row>
     <row r="23" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>134</v>
@@ -11079,10 +11181,10 @@
     </row>
     <row r="24" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>134</v>
@@ -11111,13 +11213,13 @@
     </row>
     <row r="25" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="D25" s="7">
         <v>6</v>
@@ -11177,7 +11279,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11198,7 +11300,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11220,25 +11322,25 @@
     <row r="3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>656</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>658</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>659</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>246</v>
@@ -11250,7 +11352,7 @@
         <v>150</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>136</v>
@@ -11273,10 +11375,10 @@
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>193</v>
@@ -11291,7 +11393,7 @@
         <v>280</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="H5" s="7">
         <v>12</v>
@@ -11326,10 +11428,10 @@
     </row>
     <row r="6" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>193</v>
@@ -11344,7 +11446,7 @@
         <v>280</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="H6" s="8">
         <v>6</v>
@@ -11356,7 +11458,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>280</v>
@@ -11379,10 +11481,10 @@
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>193</v>
@@ -11397,7 +11499,7 @@
         <v>280</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="H7" s="7">
         <v>0</v>
@@ -11409,7 +11511,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>280</v>
@@ -11432,10 +11534,10 @@
     </row>
     <row r="8" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>193</v>
@@ -11450,7 +11552,7 @@
         <v>280</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="H8" s="8">
         <v>0</v>
@@ -11462,7 +11564,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>280</v>
@@ -11485,10 +11587,10 @@
     </row>
     <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>193</v>
@@ -11503,7 +11605,7 @@
         <v>280</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="H9" s="7">
         <v>7</v>
@@ -11538,10 +11640,10 @@
     </row>
     <row r="10" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>193</v>
@@ -11556,7 +11658,7 @@
         <v>280</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="H10" s="8">
         <v>13</v>
@@ -11591,10 +11693,10 @@
     </row>
     <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>193</v>
@@ -11609,7 +11711,7 @@
         <v>280</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="H11" s="7">
         <v>3</v>
@@ -11644,10 +11746,10 @@
     </row>
     <row r="12" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>193</v>
@@ -11662,7 +11764,7 @@
         <v>50</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="H12" s="8">
         <v>10</v>
@@ -11697,10 +11799,10 @@
     </row>
     <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>193</v>
@@ -11715,7 +11817,7 @@
         <v>50</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="H13" s="7">
         <v>2</v>
@@ -11750,10 +11852,10 @@
     </row>
     <row r="14" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>193</v>
@@ -11768,7 +11870,7 @@
         <v>280</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="H14" s="8">
         <v>6</v>
@@ -11803,10 +11905,10 @@
     </row>
     <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>193</v>
@@ -11821,7 +11923,7 @@
         <v>280</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="H15" s="7">
         <v>8</v>
@@ -11833,7 +11935,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>280</v>
@@ -11856,10 +11958,10 @@
     </row>
     <row r="16" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>193</v>
@@ -11874,7 +11976,7 @@
         <v>280</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="H16" s="8">
         <v>16</v>
@@ -11909,10 +12011,10 @@
     </row>
     <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>193</v>
@@ -11927,7 +12029,7 @@
         <v>280</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="H17" s="7">
         <v>4</v>
@@ -11962,10 +12064,10 @@
     </row>
     <row r="18" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>193</v>
@@ -11980,7 +12082,7 @@
         <v>33</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="H18" s="8">
         <v>14</v>
@@ -12015,10 +12117,10 @@
     </row>
     <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>193</v>
@@ -12033,7 +12135,7 @@
         <v>33</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="H19" s="7">
         <v>0</v>
@@ -12045,7 +12147,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="L19" s="5" t="s">
         <v>280</v>
@@ -12068,10 +12170,10 @@
     </row>
     <row r="20" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>193</v>
@@ -12086,7 +12188,7 @@
         <v>34</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="H20" s="8">
         <v>4</v>
@@ -12121,10 +12223,10 @@
     </row>
     <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>193</v>
@@ -12139,7 +12241,7 @@
         <v>280</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="H21" s="7">
         <v>0</v>
@@ -12160,7 +12262,7 @@
         <v>280</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="O21" s="5" t="s">
         <v>175</v>
@@ -12174,10 +12276,10 @@
     </row>
     <row r="22" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>193</v>
@@ -12192,7 +12294,7 @@
         <v>40</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="H22" s="8">
         <v>8</v>
@@ -12204,7 +12306,7 @@
         <v>1</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>280</v>
@@ -12227,10 +12329,10 @@
     </row>
     <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>193</v>
@@ -12245,7 +12347,7 @@
         <v>60</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="H23" s="7">
         <v>14</v>
@@ -12280,10 +12382,10 @@
     </row>
     <row r="24" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>193</v>
@@ -12298,7 +12400,7 @@
         <v>280</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="H24" s="8">
         <v>3</v>
@@ -12310,7 +12412,7 @@
         <v>2</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="L24" s="6" t="s">
         <v>280</v>
@@ -12333,10 +12435,10 @@
     </row>
     <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>193</v>
@@ -12351,7 +12453,7 @@
         <v>280</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="H25" s="7">
         <v>0</v>
@@ -12363,7 +12465,7 @@
         <v>1</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>280</v>
@@ -12386,10 +12488,10 @@
     </row>
     <row r="26" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>193</v>
@@ -12404,7 +12506,7 @@
         <v>50</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="H26" s="8">
         <v>7</v>
@@ -12416,7 +12518,7 @@
         <v>1</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>280</v>
@@ -12439,10 +12541,10 @@
     </row>
     <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>193</v>
@@ -12457,7 +12559,7 @@
         <v>50</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="H27" s="7">
         <v>12</v>
@@ -12492,10 +12594,10 @@
     </row>
     <row r="28" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>193</v>
@@ -12510,7 +12612,7 @@
         <v>280</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="H28" s="8">
         <v>0</v>
@@ -12522,7 +12624,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>280</v>
@@ -12545,10 +12647,10 @@
     </row>
     <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>193</v>
@@ -12563,7 +12665,7 @@
         <v>280</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="H29" s="7">
         <v>7</v>
@@ -12575,7 +12677,7 @@
         <v>2</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>280</v>
@@ -12598,10 +12700,10 @@
     </row>
     <row r="30" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>193</v>
@@ -12616,7 +12718,7 @@
         <v>280</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="H30" s="8">
         <v>7</v>
@@ -12628,7 +12730,7 @@
         <v>2</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="L30" s="6" t="s">
         <v>280</v>
@@ -12651,10 +12753,10 @@
     </row>
     <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>193</v>
@@ -12669,7 +12771,7 @@
         <v>280</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="H31" s="7">
         <v>5</v>
@@ -12704,10 +12806,10 @@
     </row>
     <row r="32" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>193</v>
@@ -12722,7 +12824,7 @@
         <v>50</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="H32" s="8">
         <v>8</v>
@@ -12734,7 +12836,7 @@
         <v>1</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="L32" s="6" t="s">
         <v>280</v>
@@ -12757,10 +12859,10 @@
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>193</v>
@@ -12775,7 +12877,7 @@
         <v>50</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="H33" s="7">
         <v>11</v>
@@ -12810,10 +12912,10 @@
     </row>
     <row r="34" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>193</v>
@@ -12828,7 +12930,7 @@
         <v>280</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="H34" s="8">
         <v>0</v>
@@ -12840,7 +12942,7 @@
         <v>1</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="L34" s="6" t="s">
         <v>280</v>
@@ -12863,10 +12965,10 @@
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>193</v>
@@ -12881,7 +12983,7 @@
         <v>280</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="H35" s="7">
         <v>4</v>
@@ -12916,10 +13018,10 @@
     </row>
     <row r="36" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>193</v>
@@ -12934,7 +13036,7 @@
         <v>280</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="H36" s="8">
         <v>0</v>
@@ -12946,7 +13048,7 @@
         <v>0</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="L36" s="6" t="s">
         <v>280</v>
@@ -12969,10 +13071,10 @@
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>193</v>
@@ -12987,7 +13089,7 @@
         <v>280</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H37" s="7">
         <v>4</v>
@@ -13022,10 +13124,10 @@
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>193</v>
@@ -13040,7 +13142,7 @@
         <v>280</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="H38" s="8">
         <v>0</v>
@@ -13055,7 +13157,7 @@
         <v>387</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="M38" s="8" t="s">
         <v>280</v>
@@ -13075,10 +13177,10 @@
     </row>
     <row r="39" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>193</v>
@@ -13093,7 +13195,7 @@
         <v>280</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H39" s="7">
         <v>8</v>
@@ -13128,10 +13230,10 @@
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>193</v>
@@ -13146,7 +13248,7 @@
         <v>280</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="H40" s="8">
         <v>0</v>
@@ -13161,7 +13263,7 @@
         <v>387</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="M40" s="8" t="s">
         <v>280</v>
@@ -13181,10 +13283,10 @@
     </row>
     <row r="41" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>193</v>
@@ -13199,7 +13301,7 @@
         <v>50</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="H41" s="7">
         <v>11</v>
@@ -13234,10 +13336,10 @@
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>193</v>
@@ -13252,7 +13354,7 @@
         <v>50</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="H42" s="8">
         <v>0</v>
@@ -13267,7 +13369,7 @@
         <v>387</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="M42" s="8" t="s">
         <v>280</v>
@@ -13287,10 +13389,10 @@
     </row>
     <row r="43" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>217</v>
@@ -13305,7 +13407,7 @@
         <v>280</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="H43" s="7">
         <v>0</v>
@@ -13340,10 +13442,10 @@
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>217</v>
@@ -13358,7 +13460,7 @@
         <v>280</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="H44" s="8">
         <v>0</v>
@@ -13370,7 +13472,7 @@
         <v>0</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="L44" s="6" t="s">
         <v>280</v>
@@ -13393,10 +13495,10 @@
     </row>
     <row r="45" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>217</v>
@@ -13411,7 +13513,7 @@
         <v>280</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="H45" s="7">
         <v>13</v>
@@ -13446,10 +13548,10 @@
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>217</v>
@@ -13464,7 +13566,7 @@
         <v>280</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="H46" s="8">
         <v>0</v>
@@ -13499,10 +13601,10 @@
     </row>
     <row r="47" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>217</v>
@@ -13517,7 +13619,7 @@
         <v>280</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="H47" s="7">
         <v>13</v>
@@ -13552,10 +13654,10 @@
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>217</v>
@@ -13570,7 +13672,7 @@
         <v>280</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="H48" s="8">
         <v>17</v>
@@ -13605,10 +13707,10 @@
     </row>
     <row r="49" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>217</v>
@@ -13623,7 +13725,7 @@
         <v>280</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="H49" s="7">
         <v>3</v>
@@ -13658,10 +13760,10 @@
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>217</v>
@@ -13676,7 +13778,7 @@
         <v>280</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="H50" s="8">
         <v>0</v>
@@ -13691,7 +13793,7 @@
         <v>387</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="M50" s="8" t="s">
         <v>280</v>
@@ -13711,10 +13813,10 @@
     </row>
     <row r="51" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>217</v>
@@ -13729,7 +13831,7 @@
         <v>280</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="H51" s="7">
         <v>4</v>
@@ -13764,10 +13866,10 @@
     </row>
     <row r="52" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>134</v>
@@ -13782,7 +13884,7 @@
         <v>280</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="H52" s="8">
         <v>0</v>
@@ -13794,7 +13896,7 @@
         <v>1</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="L52" s="6" t="s">
         <v>280</v>
@@ -13817,10 +13919,10 @@
     </row>
     <row r="53" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>134</v>
@@ -13835,7 +13937,7 @@
         <v>280</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="H53" s="7">
         <v>18</v>
@@ -13847,7 +13949,7 @@
         <v>1</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="L53" s="5" t="s">
         <v>280</v>
@@ -13870,10 +13972,10 @@
     </row>
     <row r="54" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>134</v>
@@ -13888,7 +13990,7 @@
         <v>280</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="H54" s="8">
         <v>18</v>
@@ -13923,10 +14025,10 @@
     </row>
     <row r="55" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>134</v>
@@ -13941,7 +14043,7 @@
         <v>280</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="H55" s="7">
         <v>0</v>
@@ -13976,10 +14078,10 @@
     </row>
     <row r="56" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>134</v>
@@ -13994,7 +14096,7 @@
         <v>280</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="H56" s="8">
         <v>0</v>
@@ -14006,7 +14108,7 @@
         <v>2</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="L56" s="6" t="s">
         <v>280</v>
@@ -14029,10 +14131,10 @@
     </row>
     <row r="57" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>134</v>
@@ -14047,7 +14149,7 @@
         <v>280</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="H57" s="7">
         <v>15</v>
@@ -14082,10 +14184,10 @@
     </row>
     <row r="58" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>134</v>
@@ -14100,7 +14202,7 @@
         <v>280</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="H58" s="8">
         <v>17</v>
@@ -14112,7 +14214,7 @@
         <v>1</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="L58" s="6" t="s">
         <v>280</v>
@@ -14135,10 +14237,10 @@
     </row>
     <row r="59" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>134</v>
@@ -14153,7 +14255,7 @@
         <v>280</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="H59" s="7">
         <v>5</v>
@@ -14188,10 +14290,10 @@
     </row>
     <row r="60" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>134</v>
@@ -14206,7 +14308,7 @@
         <v>280</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="H60" s="8">
         <v>2</v>
@@ -14241,10 +14343,10 @@
     </row>
     <row r="61" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>134</v>
@@ -14259,7 +14361,7 @@
         <v>280</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="H61" s="7">
         <v>0</v>
@@ -14271,7 +14373,7 @@
         <v>0</v>
       </c>
       <c r="K61" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="L61" s="5" t="s">
         <v>280</v>
@@ -14294,10 +14396,10 @@
     </row>
     <row r="62" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>134</v>
@@ -14312,7 +14414,7 @@
         <v>280</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="H62" s="8">
         <v>8</v>
@@ -14324,7 +14426,7 @@
         <v>2</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="L62" s="6" t="s">
         <v>280</v>
@@ -14347,10 +14449,10 @@
     </row>
     <row r="63" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>134</v>
@@ -14365,7 +14467,7 @@
         <v>280</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="H63" s="7">
         <v>8</v>
@@ -14377,7 +14479,7 @@
         <v>2</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="L63" s="5" t="s">
         <v>280</v>
@@ -14400,10 +14502,10 @@
     </row>
     <row r="64" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>134</v>
@@ -14418,7 +14520,7 @@
         <v>280</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="H64" s="8">
         <v>3</v>
@@ -14453,10 +14555,10 @@
     </row>
     <row r="65" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>134</v>
@@ -14471,7 +14573,7 @@
         <v>280</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="H65" s="7">
         <v>0</v>
@@ -14483,7 +14585,7 @@
         <v>0</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="L65" s="5" t="s">
         <v>280</v>
@@ -14506,10 +14608,10 @@
     </row>
     <row r="66" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>134</v>
@@ -14524,7 +14626,7 @@
         <v>280</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="H66" s="8">
         <v>7</v>
@@ -14559,10 +14661,10 @@
     </row>
     <row r="67" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>134</v>
@@ -14577,7 +14679,7 @@
         <v>280</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="H67" s="7">
         <v>6</v>
@@ -14612,10 +14714,10 @@
     </row>
     <row r="68" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>134</v>
@@ -14630,7 +14732,7 @@
         <v>280</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="H68" s="8">
         <v>26</v>
@@ -14642,7 +14744,7 @@
         <v>1</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="L68" s="6" t="s">
         <v>280</v>
@@ -14665,10 +14767,10 @@
     </row>
     <row r="69" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>134</v>
@@ -14683,7 +14785,7 @@
         <v>280</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="H69" s="7">
         <v>0</v>
@@ -14695,7 +14797,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="L69" s="5" t="s">
         <v>280</v>
@@ -14718,13 +14820,13 @@
     </row>
     <row r="70" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="D70" s="8">
         <v>1</v>
@@ -14736,7 +14838,7 @@
         <v>280</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="H70" s="8">
         <v>0</v>
@@ -14751,7 +14853,7 @@
         <v>387</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="M70" s="8">
         <v>2</v>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2802" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2961" uniqueCount="920">
   <si>
     <t>현재 구현 규칙</t>
   </si>
@@ -211,7 +211,7 @@
     <t>총 노드</t>
   </si>
   <si>
-    <t>8구역 × 30노드</t>
+    <t>8구역, 구역별 34/28/14/24/26/30/18/32노드</t>
   </si>
   <si>
     <t>src/data/facilityLayout.js</t>
@@ -1375,6 +1375,15 @@
     <t>미장착 소모품</t>
   </si>
   <si>
+    <t>contract_goods_item</t>
+  </si>
+  <si>
+    <t>계약 물품</t>
+  </si>
+  <si>
+    <t>평소 사용 불가. 과적(짐) 상태일 때만 1코로 사용해 영구 소멸 — 버리면 회수 계약이 실패한다.</t>
+  </si>
+  <si>
     <t>sticky_status_card</t>
   </si>
   <si>
@@ -2263,6 +2272,12 @@
     <t>ACCESS_INTERFACE_NODE_CHANCE</t>
   </si>
   <si>
+    <t>ADJACENT_SECTOR_IDS</t>
+  </si>
+  <si>
+    <t>{"entrance":["residential","labs"],"labs":["entrance","hangar"],"hangar":["labs","security"],"security":["hangar","파워"],"파워":["security","waste"],"waste":["파워","comms"],"comms":["waste","residential"],"residential":["comms","entrance"]}</t>
+  </si>
+  <si>
     <t>행동</t>
   </si>
   <si>
@@ -2284,12 +2299,15 @@
     <t>{"신중":40,"일반":0,"돌진":-40}</t>
   </si>
   <si>
+    <t>ARCHITECTURAL_SPECIAL_EDGES_BY_SECTOR</t>
+  </si>
+  <si>
+    <t>{"comms":1}</t>
+  </si>
+  <si>
     <t>BASE_EDGE_DEGREE_HARD_CAP</t>
   </si>
   <si>
-    <t>BASE_EDGE_DEGREE_SOFT_CAP</t>
-  </si>
-  <si>
     <t>BASIC_RECON_TIME</t>
   </si>
   <si>
@@ -2329,13 +2347,73 @@
     <t>기타</t>
   </si>
   <si>
+    <t>CAPABILITY_STEP_DURABILITY_LOSS</t>
+  </si>
+  <si>
+    <t>{"surplus":0,"standard":0,"strained":0,"severe":1}</t>
+  </si>
+  <si>
+    <t>CAPABILITY_STEP_DURATION_MULTIPLIER</t>
+  </si>
+  <si>
+    <t>{"surplus":1.25,"standard":1,"strained":0.5,"severe":0.25}</t>
+  </si>
+  <si>
+    <t>CAPABILITY_STEP_HP_COST</t>
+  </si>
+  <si>
+    <t>{"surplus":0,"standard":0,"strained":3,"severe":8}</t>
+  </si>
+  <si>
+    <t>CAPABILITY_STEP_LEAVES_STRONG_TRACE</t>
+  </si>
+  <si>
+    <t>{"surplus":false,"standard":false,"strained":true,"severe":true}</t>
+  </si>
+  <si>
+    <t>CAPABILITY_STEP_NOISE_DELTA</t>
+  </si>
+  <si>
+    <t>{"surplus":-1,"standard":0,"strained":1,"severe":2}</t>
+  </si>
+  <si>
+    <t>CAPABILITY_STEP_OVERLOAD_DELTA</t>
+  </si>
+  <si>
+    <t>{"surplus":-3,"standard":0,"strained":6,"severe":14}</t>
+  </si>
+  <si>
+    <t>CAPABILITY_STEP_RAISES_ALERT</t>
+  </si>
+  <si>
+    <t>{"surplus":false,"standard":false,"strained":false,"severe":true}</t>
+  </si>
+  <si>
+    <t>CAPABILITY_STEP_TIME_MULTIPLIER</t>
+  </si>
+  <si>
+    <t>{"surplus":0.75,"standard":1,"strained":1.4,"severe":2}</t>
+  </si>
+  <si>
     <t>CONCEALMENT_ACTION_TIME_COST</t>
   </si>
   <si>
-    <t>CONCEALMENT_NODE_WEIGHTS</t>
-  </si>
-  <si>
-    <t>[{"수치":0,"weight":60},{"수치":1,"weight":16},{"수치":2,"weight":14},{"수치":3,"weight":10}]</t>
+    <t>CONTRACT_ACQUIRE_OVERLOAD</t>
+  </si>
+  <si>
+    <t>CONTRACT_ACQUIRE_TIME</t>
+  </si>
+  <si>
+    <t>CONTRACT_DESTROY_OVERLOAD</t>
+  </si>
+  <si>
+    <t>CONTRACT_DESTROY_TIME</t>
+  </si>
+  <si>
+    <t>CONTRACT_TRANSMIT_OVERLOAD</t>
+  </si>
+  <si>
+    <t>CONTRACT_TRANSMIT_TIME</t>
   </si>
   <si>
     <t>CONTROL_ROOM_HACK_OVERLOAD</t>
@@ -2344,12 +2422,18 @@
     <t>CONTROL_ROOM_HACK_TIME</t>
   </si>
   <si>
+    <t>CORPSE_DISPOSAL_TIME</t>
+  </si>
+  <si>
     <t>CROSS_SECTOR_SPECIAL_EDGES_MAX</t>
   </si>
   <si>
     <t>CROSS_SECTOR_SPECIAL_EDGES_MIN</t>
   </si>
   <si>
+    <t>DISCOVERY_NOISE_INTENSITY</t>
+  </si>
+  <si>
     <t>EDGE_TIME_MAX</t>
   </si>
   <si>
@@ -2362,6 +2446,9 @@
     <t>ENTRANCE_THREAT_MAX_GROUP_SIZE</t>
   </si>
   <si>
+    <t>EVIDENCE_TIER_RAISING_ALERT</t>
+  </si>
+  <si>
     <t>EVIDENCE_TRACE_DURATION_LIGHT</t>
   </si>
   <si>
@@ -2374,7 +2461,7 @@
     <t>EXIT_DISTANCE_RANGES</t>
   </si>
   <si>
-    <t>{"A":{"min":3200,"max":5000},"key":{"min":4600,"max":6700},"B":{"min":6000,"max":7600}}</t>
+    <t>{"A":{"min":2400,"max":4000},"key":{"min":3400,"max":5000},"B":{"min":4400,"max":5800}}</t>
   </si>
   <si>
     <t>EXIT_OPEN_WAIT_BY_HACKING</t>
@@ -2392,10 +2479,16 @@
     <t>FALLBACK_TOPOLOGY_SEED_SEARCH_LIMIT</t>
   </si>
   <si>
-    <t>FARM_NOISE</t>
-  </si>
-  <si>
-    <t>FARM_TIME</t>
+    <t>FALSE_BROADCAST_DURATION</t>
+  </si>
+  <si>
+    <t>FALSE_BROADCAST_INTENSITY</t>
+  </si>
+  <si>
+    <t>FALSE_BROADCAST_OVERLOAD</t>
+  </si>
+  <si>
+    <t>FALSE_BROADCAST_TIME</t>
   </si>
   <si>
     <t>FORCE_BASE_NOISE</t>
@@ -2437,6 +2530,9 @@
     <t>HACKING_TIER1_TIME</t>
   </si>
   <si>
+    <t>HALL_STEALTH_PENALTY</t>
+  </si>
+  <si>
     <t>INVESTIGATION_MEMORY_DURATION</t>
   </si>
   <si>
@@ -2446,12 +2542,24 @@
     <t>KEY_DROP_CHANCE</t>
   </si>
   <si>
+    <t>LANDMARK_CANDIDATE_MAX</t>
+  </si>
+  <si>
+    <t>LANDMARK_CANDIDATE_MIN</t>
+  </si>
+  <si>
     <t>LANDMARKS_BY_SECTOR</t>
   </si>
   <si>
     <t>{"entrance":{"id":"security_records_room","name":"보안 기록실","approaches":["지각","해킹","강행"]},"labs":{"id":"quarantine_vault","name":"격리 표본고","approaches":["은신","강행","해킹"]},"hangar":{"id":"cargo_bay","name":"화물 격납고","approaches":["강행","기동","해킹"]},"security":{"id":"central_control","name":"중앙 관제실","approaches":["해킹","기만","강행"]},"파워":{"id":"main_generator","name":"주 발전기","approaches":["강행","해킹","기동"]},"waste":{"id":"incinerator_core","name":"소각로 중심부","approaches":["강행","은신","해킹"]},"comms":{"id":"control_tower","name":"중앙 관제탑","approaches":["해킹","지각","기만"]},"residential":{"id":"staff_quarters_vault","name":"직원 숙소 금고","approaches":["은신","기만","해킹"]}}</t>
   </si>
   <si>
+    <t>LOCKDOWN_EXIT_CLOSE_WINDOW</t>
+  </si>
+  <si>
+    <t>LOCKDOWN_THREAT_SPEED_MULTIPLIER</t>
+  </si>
+  <si>
     <t>LONG_RANGE_SPECIAL_EDGES_MAX</t>
   </si>
   <si>
@@ -2467,10 +2575,19 @@
     <t>NODE_MIN_SEPARATION</t>
   </si>
   <si>
-    <t>NODE_PLACEMENT_MAX_ATTEMPTS</t>
-  </si>
-  <si>
-    <t>NODES_PER_SECTOR</t>
+    <t>NODE_SEPARATION_PASSES</t>
+  </si>
+  <si>
+    <t>NODE_TYPE_CONCEALMENT_WEIGHTS</t>
+  </si>
+  <si>
+    <t>{"corridor":[{"수치":0,"weight":100}],"hall":[{"수치":0,"weight":100}],"office":[{"수치":0,"weight":65},{"수치":1,"weight":20},{"수치":2,"weight":15}],"utility":[{"수치":0,"weight":55},{"수치":1,"weight":25},{"수치":2,"weight":20}],"watch":[{"수치":0,"weight":60},{"수치":1,"weight":25},{"수치":2,"weight":15}],"vault":[{"수치":0,"weight":40},{"수치":2,"weight":35},{"수치":3,"weight":25}],"crawlway":[{"수치":0,"weight":20},{"수치":2,"weight":45},{"수치":3,"weight":35}],"refuge":[{"수치":0,"weight":10},{"수치":2,"weight":40},{"수치":3,"weight":50}]}</t>
+  </si>
+  <si>
+    <t>NODE_TYPE_OPPORTUNITY_WEIGHTS</t>
+  </si>
+  <si>
+    <t>{"corridor":[{"수치":0,"weight":90},{"수치":1,"weight":10}],"crawlway":[{"수치":0,"weight":80},{"수치":1,"weight":20}],"watch":[{"수치":0,"weight":40},{"수치":1,"weight":45},{"수치":2,"weight":15}],"refuge":[{"수치":0,"weight":25},{"수치":1,"weight":55},{"수치":2,"weight":20}],"utility":[{"수치":0,"weight":20},{"수치":1,"weight":50},{"수치":2,"weight":30}],"hall":[{"수치":0,"weight":20},{"수치":1,"weight":40},{"수치":2,"weight":40}],"office":[{"수치":0,"weight":10},{"수치":1,"weight":50},{"수치":2,"weight":40}],"vault":[{"수치":0,"weight":5},{"수치":1,"weight":35},{"수치":2,"weight":60}]}</t>
   </si>
   <si>
     <t>NOISE_DURATION</t>
@@ -2482,12 +2599,6 @@
     <t>{"1":1,"2":2,"3":3,"4":"Infinity"}</t>
   </si>
   <si>
-    <t>OPPORTUNITY_COUNT_WEIGHTS</t>
-  </si>
-  <si>
-    <t>[{"수치":0,"weight":25},{"수치":1,"weight":50},{"수치":2,"weight":25}]</t>
-  </si>
-  <si>
     <t>OPPORTUNITY_USES_WEIGHTS</t>
   </si>
   <si>
@@ -2500,6 +2611,54 @@
     <t>OVERLOAD_MIN</t>
   </si>
   <si>
+    <t>POWER_CUT_DURATION</t>
+  </si>
+  <si>
+    <t>POWER_CUT_NOISE</t>
+  </si>
+  <si>
+    <t>POWER_CUT_TIME</t>
+  </si>
+  <si>
+    <t>PRIZE_AXIS_WEIGHTS</t>
+  </si>
+  <si>
+    <t>[{"수치":"combat","weight":35},{"수치":"infiltration","weight":35},{"수치":"resource","weight":30}]</t>
+  </si>
+  <si>
+    <t>PRIZE_FARM_NOISE</t>
+  </si>
+  <si>
+    <t>{"일반":2,"정예":3}</t>
+  </si>
+  <si>
+    <t>PRIZE_FARM_TIME</t>
+  </si>
+  <si>
+    <t>{"일반":200,"정예":260}</t>
+  </si>
+  <si>
+    <t>PRIZE_OPTION_COUNT</t>
+  </si>
+  <si>
+    <t>PRIZE_PROMOTION_CHANCE_BY_NODE_TYPE</t>
+  </si>
+  <si>
+    <t>{"vault":0.2,"office":0.2,"utility":0.2,"hall":0.18,"refuge":0.14,"watch":0.14,"crawlway":0.05,"corridor":0.02}</t>
+  </si>
+  <si>
+    <t>PRIZE_TIER_WEIGHTS</t>
+  </si>
+  <si>
+    <t>[{"수치":"일반","weight":70},{"수치":"정예","weight":30}]</t>
+  </si>
+  <si>
+    <t>REINFORCEMENT_INTERVAL</t>
+  </si>
+  <si>
+    <t>REINFORCEMENT_LOCKDOWN_MULTIPLIER</t>
+  </si>
+  <si>
     <t>RUN_COLLAPSE_TIME</t>
   </si>
   <si>
@@ -2512,9 +2671,6 @@
     <t>[["entrance","labs"],["labs","hangar"],["hangar","security"],["security","파워"],["파워","waste"],["waste","comms"],["comms","residential"],["residential","entrance"]]</t>
   </si>
   <si>
-    <t>SECTOR_ALERT_DECAY_INTERVAL</t>
-  </si>
-  <si>
     <t>SECTOR_ALERT_INVESTIGATE_INTERVAL</t>
   </si>
   <si>
@@ -2533,6 +2689,12 @@
     <t>["entrance","labs","hangar","security","파워","waste","comms","residential"]</t>
   </si>
   <si>
+    <t>SECTOR_LAYOUTS</t>
+  </si>
+  <si>
+    <t>{"entrance":{"archetype":"grid","nodeCount":34,"corridorRatio":0.45,"roomTypes":[{"수치":"office","weight":60},{"수치":"watch","weight":15},{"수치":"utility","weight":15},{"수치":"refuge","weight":10}]},"labs":{"archetype":"chain","nodeCount":28,"corridorRatio":0.3,"roomTypes":[{"수치":"vault","weight":45},{"수치":"office","weight":35},{"수치":"utility","weight":20}]},"hangar":{"archetype":"hall","nodeCount":14,"corridorRatio":0.25,"roomTypes":[{"수치":"office","weight":50},{"수치":"utility","weight":35},{"수치":"watch","weight":15}]},"security":{"archetype":"grid","nodeCount":24,"corridorRatio":0.35,"roomTypes":[{"수치":"watch","weight":40},{"수치":"office","weight":35},{"수치":"vault","weight":25}]},"파워":{"archetype":"radial","nodeCount":26,"corridorRatio":0.45,"roomTypes":[{"수치":"utility","weight":60},{"수치":"office","weight":25},{"수치":"vault","weight":15}]},"waste":{"archetype":"dual","nodeCount":30,"corridorRatio":0.4,"roomTypes":[{"수치":"utility","weight":50},{"수치":"office","weight":30},{"수치":"refuge","weight":20}]},"comms":{"archetype":"tower","nodeCount":18,"corridorRatio":0.35,"roomTypes":[{"수치":"watch","weight":45},{"수치":"office","weight":35},{"수치":"utility","weight":20}]},"residential":{"archetype":"chain","nodeCount":32,"corridorRatio":0.5,"roomTypes":[{"수치":"refuge","weight":45},{"수치":"office","weight":40},{"수치":"utility","weight":15}]}}</t>
+  </si>
+  <si>
     <t>SECTOR_NAMES</t>
   </si>
   <si>
@@ -2548,7 +2710,7 @@
     <t>SPECIAL_EDGE_CATEGORY_WEIGHTS</t>
   </si>
   <si>
-    <t>[{"수치":"oneWay","weight":3},{"수치":"blocked","weight":7},{"수치":"전자 장치","weight":5},{"수치":"highGround","weight":3}]</t>
+    <t>[{"수치":"oneWay","weight":3},{"수치":"blocked","weight":6},{"수치":"highGround","weight":3}]</t>
   </si>
   <si>
     <t>SPECIAL_EDGE_SECOND_TAG_CHANCE</t>
@@ -2563,6 +2725,12 @@
     <t>STANDARD_EDGE_TIME_COST</t>
   </si>
   <si>
+    <t>SUPPLY_FARM_NOISE</t>
+  </si>
+  <si>
+    <t>SUPPLY_FARM_TIME</t>
+  </si>
+  <si>
     <t>THREAT_COUNT_BY_SECTOR</t>
   </si>
   <si>
@@ -2594,6 +2762,21 @@
   </si>
   <si>
     <t>TOTAL_NODES</t>
+  </si>
+  <si>
+    <t>TOWER_ELEVATOR_REQUIREMENT</t>
+  </si>
+  <si>
+    <t>TOWER_LOBBY_ROOMS</t>
+  </si>
+  <si>
+    <t>TOWER_LOBBY_SPREAD</t>
+  </si>
+  <si>
+    <t>TRACE_CLEANUP_TIME_BY_PERCEPTION</t>
+  </si>
+  <si>
+    <t>[320,320,280,250,210,180,150]</t>
   </si>
   <si>
     <t>WORLD_TICK_INTERVAL</t>
@@ -3395,7 +3578,7 @@
         <v>62</v>
       </c>
       <c r="C22" s="6">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>63</v>
@@ -3522,7 +3705,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -3533,7 +3716,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3541,7 +3724,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3553,10 +3736,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>6</v>
@@ -3564,10 +3747,10 @@
     </row>
     <row r="5" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C5" s="5">
         <v>0.16</v>
@@ -3578,13 +3761,13 @@
     </row>
     <row r="6" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>748</v>
-      </c>
-      <c r="C6" s="6">
-        <v>20</v>
+        <v>750</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>751</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>64</v>
@@ -3592,13 +3775,13 @@
     </row>
     <row r="7" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>750</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>751</v>
+        <v>753</v>
+      </c>
+      <c r="C7" s="5">
+        <v>20</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>64</v>
@@ -3606,13 +3789,13 @@
     </row>
     <row r="8" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>64</v>
@@ -3620,13 +3803,13 @@
     </row>
     <row r="9" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="C9" s="5">
-        <v>4</v>
+        <v>757</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>758</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>64</v>
@@ -3634,13 +3817,13 @@
     </row>
     <row r="10" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>755</v>
-      </c>
-      <c r="C10" s="6">
-        <v>2</v>
+        <v>759</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>760</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>64</v>
@@ -3648,13 +3831,13 @@
     </row>
     <row r="11" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>756</v>
+        <v>761</v>
       </c>
       <c r="C11" s="5">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>64</v>
@@ -3662,13 +3845,13 @@
     </row>
     <row r="12" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="C12" s="6">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>64</v>
@@ -3676,13 +3859,13 @@
     </row>
     <row r="13" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>758</v>
+        <v>763</v>
       </c>
       <c r="C13" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>64</v>
@@ -3690,13 +3873,13 @@
     </row>
     <row r="14" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="C14" s="6">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>64</v>
@@ -3704,13 +3887,13 @@
     </row>
     <row r="15" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="C15" s="5">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>64</v>
@@ -3718,13 +3901,13 @@
     </row>
     <row r="16" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>762</v>
+        <v>767</v>
       </c>
       <c r="C16" s="6">
-        <v>6</v>
+        <v>300</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>64</v>
@@ -3732,13 +3915,13 @@
     </row>
     <row r="17" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>763</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>764</v>
+        <v>768</v>
+      </c>
+      <c r="C17" s="5">
+        <v>6</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>64</v>
@@ -3746,13 +3929,13 @@
     </row>
     <row r="18" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>765</v>
-      </c>
-      <c r="C18" s="6">
-        <v>100</v>
+        <v>769</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>770</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>64</v>
@@ -3760,13 +3943,13 @@
     </row>
     <row r="19" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>745</v>
+        <v>765</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>766</v>
+        <v>771</v>
       </c>
       <c r="C19" s="5">
-        <v>0.22</v>
+        <v>100</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>64</v>
@@ -3774,13 +3957,13 @@
     </row>
     <row r="20" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="C20" s="6">
-        <v>3</v>
+        <v>0.22</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>64</v>
@@ -3788,13 +3971,13 @@
     </row>
     <row r="21" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="C21" s="5">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>64</v>
@@ -3802,13 +3985,13 @@
     </row>
     <row r="22" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>745</v>
+        <v>774</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>64</v>
@@ -3816,13 +3999,13 @@
     </row>
     <row r="23" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>32</v>
+        <v>774</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>772</v>
-      </c>
-      <c r="C23" s="5">
-        <v>10</v>
+        <v>777</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>778</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>64</v>
@@ -3830,13 +4013,13 @@
     </row>
     <row r="24" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>773</v>
-      </c>
-      <c r="C24" s="6">
-        <v>150</v>
+        <v>779</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>780</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>64</v>
@@ -3844,13 +4027,13 @@
     </row>
     <row r="25" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>745</v>
+        <v>774</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>774</v>
-      </c>
-      <c r="C25" s="5">
-        <v>3</v>
+        <v>781</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>782</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>64</v>
@@ -3858,13 +4041,13 @@
     </row>
     <row r="26" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>745</v>
+        <v>754</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>775</v>
-      </c>
-      <c r="C26" s="6">
-        <v>2</v>
+        <v>783</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>784</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>64</v>
@@ -3872,13 +4055,13 @@
     </row>
     <row r="27" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>745</v>
+        <v>32</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>776</v>
-      </c>
-      <c r="C27" s="5">
-        <v>260</v>
+        <v>785</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>786</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>64</v>
@@ -3886,13 +4069,13 @@
     </row>
     <row r="28" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>745</v>
+        <v>754</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>777</v>
-      </c>
-      <c r="C28" s="6">
-        <v>40</v>
+        <v>787</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>788</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>64</v>
@@ -3900,13 +4083,13 @@
     </row>
     <row r="29" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>745</v>
+        <v>774</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>778</v>
-      </c>
-      <c r="C29" s="5">
-        <v>2</v>
+        <v>789</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>790</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>64</v>
@@ -3914,13 +4097,13 @@
     </row>
     <row r="30" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>749</v>
+        <v>774</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>779</v>
+        <v>791</v>
       </c>
       <c r="C30" s="6">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>64</v>
@@ -3928,13 +4111,13 @@
     </row>
     <row r="31" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>768</v>
+        <v>32</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>780</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>280</v>
+        <v>792</v>
+      </c>
+      <c r="C31" s="5">
+        <v>8</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>64</v>
@@ -3942,13 +4125,13 @@
     </row>
     <row r="32" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>69</v>
+        <v>774</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
       <c r="C32" s="6">
-        <v>8600</v>
+        <v>120</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>64</v>
@@ -3956,13 +4139,13 @@
     </row>
     <row r="33" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="C33" s="5">
-        <v>13400</v>
+        <v>15</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>64</v>
@@ -3970,13 +4153,13 @@
     </row>
     <row r="34" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>69</v>
+        <v>774</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>783</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>784</v>
+        <v>795</v>
+      </c>
+      <c r="C34" s="6">
+        <v>180</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>64</v>
@@ -3984,13 +4167,13 @@
     </row>
     <row r="35" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>785</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>786</v>
+        <v>796</v>
+      </c>
+      <c r="C35" s="5">
+        <v>10</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>64</v>
@@ -3998,10 +4181,10 @@
     </row>
     <row r="36" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>69</v>
+        <v>774</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>787</v>
+        <v>797</v>
       </c>
       <c r="C36" s="6">
         <v>100</v>
@@ -4012,13 +4195,13 @@
     </row>
     <row r="37" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>788</v>
+        <v>798</v>
       </c>
       <c r="C37" s="5">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>64</v>
@@ -4026,13 +4209,13 @@
     </row>
     <row r="38" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>768</v>
+        <v>774</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>789</v>
+        <v>799</v>
       </c>
       <c r="C38" s="6">
-        <v>256</v>
+        <v>150</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>64</v>
@@ -4040,13 +4223,13 @@
     </row>
     <row r="39" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>749</v>
+        <v>774</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>790</v>
+        <v>800</v>
       </c>
       <c r="C39" s="5">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>64</v>
@@ -4054,13 +4237,13 @@
     </row>
     <row r="40" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>791</v>
+        <v>801</v>
       </c>
       <c r="C40" s="6">
-        <v>140</v>
+        <v>3</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>64</v>
@@ -4068,10 +4251,10 @@
     </row>
     <row r="41" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>792</v>
+        <v>802</v>
       </c>
       <c r="C41" s="5">
         <v>2</v>
@@ -4082,13 +4265,13 @@
     </row>
     <row r="42" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>793</v>
+        <v>803</v>
       </c>
       <c r="C42" s="6">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>64</v>
@@ -4096,13 +4279,13 @@
     </row>
     <row r="43" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>794</v>
+        <v>804</v>
       </c>
       <c r="C43" s="5">
-        <v>64</v>
+        <v>260</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>64</v>
@@ -4110,13 +4293,13 @@
     </row>
     <row r="44" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>759</v>
+        <v>748</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>795</v>
+        <v>805</v>
       </c>
       <c r="C44" s="6">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>64</v>
@@ -4124,10 +4307,10 @@
     </row>
     <row r="45" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>796</v>
+        <v>806</v>
       </c>
       <c r="C45" s="5">
         <v>2</v>
@@ -4138,13 +4321,13 @@
     </row>
     <row r="46" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>797</v>
+        <v>807</v>
       </c>
       <c r="C46" s="6">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>64</v>
@@ -4152,13 +4335,13 @@
     </row>
     <row r="47" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>798</v>
+        <v>808</v>
       </c>
       <c r="C47" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>64</v>
@@ -4166,13 +4349,13 @@
     </row>
     <row r="48" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>759</v>
+        <v>774</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>799</v>
-      </c>
-      <c r="C48" s="6">
-        <v>100</v>
+        <v>809</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>280</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>64</v>
@@ -4180,13 +4363,13 @@
     </row>
     <row r="49" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>745</v>
+        <v>69</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>800</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>801</v>
+        <v>810</v>
+      </c>
+      <c r="C49" s="5">
+        <v>8600</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>64</v>
@@ -4194,13 +4377,13 @@
     </row>
     <row r="50" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>749</v>
+        <v>69</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>802</v>
+        <v>811</v>
       </c>
       <c r="C50" s="6">
-        <v>0</v>
+        <v>13400</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>64</v>
@@ -4208,13 +4391,13 @@
     </row>
     <row r="51" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>747</v>
+        <v>69</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>803</v>
-      </c>
-      <c r="C51" s="5">
-        <v>3</v>
+        <v>812</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>813</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>64</v>
@@ -4222,13 +4405,13 @@
     </row>
     <row r="52" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>747</v>
+        <v>69</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>804</v>
-      </c>
-      <c r="C52" s="6">
-        <v>80</v>
+        <v>814</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>815</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>64</v>
@@ -4236,13 +4419,13 @@
     </row>
     <row r="53" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>749</v>
+        <v>69</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>805</v>
+        <v>816</v>
       </c>
       <c r="C53" s="5">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>64</v>
@@ -4250,13 +4433,13 @@
     </row>
     <row r="54" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>806</v>
+        <v>69</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>807</v>
+        <v>817</v>
       </c>
       <c r="C54" s="6">
-        <v>0.01</v>
+        <v>50</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>64</v>
@@ -4264,13 +4447,13 @@
     </row>
     <row r="55" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>745</v>
+        <v>774</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>808</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>809</v>
+        <v>818</v>
+      </c>
+      <c r="C55" s="5">
+        <v>256</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>64</v>
@@ -4278,13 +4461,13 @@
     </row>
     <row r="56" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>745</v>
+        <v>774</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>810</v>
+        <v>819</v>
       </c>
       <c r="C56" s="6">
-        <v>3</v>
+        <v>300</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>64</v>
@@ -4292,10 +4475,10 @@
     </row>
     <row r="57" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>745</v>
+        <v>774</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>811</v>
+        <v>820</v>
       </c>
       <c r="C57" s="5">
         <v>2</v>
@@ -4306,13 +4489,13 @@
     </row>
     <row r="58" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>747</v>
+        <v>32</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>812</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>813</v>
+        <v>821</v>
+      </c>
+      <c r="C58" s="6">
+        <v>6</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>64</v>
@@ -4320,13 +4503,13 @@
     </row>
     <row r="59" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>745</v>
+        <v>774</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="C59" s="5">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>64</v>
@@ -4334,13 +4517,13 @@
     </row>
     <row r="60" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>745</v>
+        <v>754</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="C60" s="6">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>64</v>
@@ -4348,13 +4531,13 @@
     </row>
     <row r="61" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="C61" s="5">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>64</v>
@@ -4362,13 +4545,13 @@
     </row>
     <row r="62" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="C62" s="6">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>64</v>
@@ -4376,13 +4559,13 @@
     </row>
     <row r="63" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>749</v>
+        <v>765</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>818</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>819</v>
+        <v>826</v>
+      </c>
+      <c r="C63" s="5">
+        <v>5</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>64</v>
@@ -4390,13 +4573,13 @@
     </row>
     <row r="64" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>806</v>
+        <v>754</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>820</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>821</v>
+        <v>827</v>
+      </c>
+      <c r="C64" s="6">
+        <v>2</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>64</v>
@@ -4404,13 +4587,13 @@
     </row>
     <row r="65" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>806</v>
+        <v>765</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>822</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>823</v>
+        <v>828</v>
+      </c>
+      <c r="C65" s="5">
+        <v>100</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>64</v>
@@ -4418,13 +4601,13 @@
     </row>
     <row r="66" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>32</v>
+        <v>765</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>824</v>
+        <v>829</v>
       </c>
       <c r="C66" s="6">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>64</v>
@@ -4432,13 +4615,13 @@
     </row>
     <row r="67" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>32</v>
+        <v>765</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>825</v>
+        <v>830</v>
       </c>
       <c r="C67" s="5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>64</v>
@@ -4446,13 +4629,13 @@
     </row>
     <row r="68" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>69</v>
+        <v>748</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>826</v>
-      </c>
-      <c r="C68" s="6">
-        <v>14000</v>
+        <v>831</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>832</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>64</v>
@@ -4460,13 +4643,13 @@
     </row>
     <row r="69" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>32</v>
+        <v>754</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
       <c r="C69" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>64</v>
@@ -4474,13 +4657,13 @@
     </row>
     <row r="70" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>828</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>829</v>
+        <v>834</v>
+      </c>
+      <c r="C70" s="6">
+        <v>3</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>64</v>
@@ -4488,13 +4671,13 @@
     </row>
     <row r="71" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>830</v>
+        <v>835</v>
       </c>
       <c r="C71" s="5">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>64</v>
@@ -4502,13 +4685,13 @@
     </row>
     <row r="72" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>749</v>
+        <v>774</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>831</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>832</v>
+        <v>836</v>
+      </c>
+      <c r="C72" s="6">
+        <v>1</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>64</v>
@@ -4516,13 +4699,13 @@
     </row>
     <row r="73" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>833</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>834</v>
+        <v>837</v>
+      </c>
+      <c r="C73" s="5">
+        <v>300</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>64</v>
@@ -4530,13 +4713,13 @@
     </row>
     <row r="74" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>745</v>
+        <v>838</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>835</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>836</v>
+        <v>839</v>
+      </c>
+      <c r="C74" s="6">
+        <v>0.01</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>64</v>
@@ -4544,13 +4727,13 @@
     </row>
     <row r="75" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>745</v>
+        <v>838</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>837</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>838</v>
+        <v>840</v>
+      </c>
+      <c r="C75" s="5">
+        <v>4</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>64</v>
@@ -4558,13 +4741,13 @@
     </row>
     <row r="76" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>745</v>
+        <v>838</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C76" s="6">
-        <v>280</v>
+        <v>2</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>64</v>
@@ -4572,13 +4755,13 @@
     </row>
     <row r="77" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>840</v>
-      </c>
-      <c r="C77" s="5">
-        <v>900</v>
+        <v>842</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>843</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>64</v>
@@ -4586,13 +4769,13 @@
     </row>
     <row r="78" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>745</v>
+        <v>69</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>841</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>842</v>
+        <v>844</v>
+      </c>
+      <c r="C78" s="6">
+        <v>2500</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>64</v>
@@ -4600,13 +4783,13 @@
     </row>
     <row r="79" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>745</v>
+        <v>754</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C79" s="5">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>64</v>
@@ -4614,13 +4797,13 @@
     </row>
     <row r="80" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="C80" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>64</v>
@@ -4628,13 +4811,13 @@
     </row>
     <row r="81" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C81" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>64</v>
@@ -4642,13 +4825,13 @@
     </row>
     <row r="82" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>846</v>
-      </c>
-      <c r="C82" s="6">
-        <v>100</v>
+        <v>848</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>849</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>64</v>
@@ -4656,13 +4839,13 @@
     </row>
     <row r="83" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>847</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>848</v>
+        <v>850</v>
+      </c>
+      <c r="C83" s="5">
+        <v>0.17</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>64</v>
@@ -4670,13 +4853,13 @@
     </row>
     <row r="84" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>849</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>850</v>
+        <v>851</v>
+      </c>
+      <c r="C84" s="6">
+        <v>24</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>64</v>
@@ -4684,13 +4867,13 @@
     </row>
     <row r="85" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>851</v>
-      </c>
-      <c r="C85" s="5">
-        <v>2</v>
+        <v>852</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>853</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>64</v>
@@ -4698,13 +4881,13 @@
     </row>
     <row r="86" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>852</v>
-      </c>
-      <c r="C86" s="6">
-        <v>3</v>
+        <v>854</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>855</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>64</v>
@@ -4712,13 +4895,13 @@
     </row>
     <row r="87" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>853</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>854</v>
+        <v>856</v>
+      </c>
+      <c r="C87" s="5">
+        <v>100</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>64</v>
@@ -4726,13 +4909,13 @@
     </row>
     <row r="88" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>749</v>
+        <v>754</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>855</v>
-      </c>
-      <c r="C88" s="6">
-        <v>4</v>
+        <v>857</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>858</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>64</v>
@@ -4740,13 +4923,13 @@
     </row>
     <row r="89" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>749</v>
+        <v>838</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>856</v>
-      </c>
-      <c r="C89" s="5">
-        <v>2</v>
+        <v>859</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>860</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>64</v>
@@ -4754,13 +4937,13 @@
     </row>
     <row r="90" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>745</v>
+        <v>32</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="C90" s="6">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>64</v>
@@ -4768,20 +4951,594 @@
     </row>
     <row r="91" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>768</v>
+        <v>32</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="C91" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>64</v>
       </c>
     </row>
+    <row r="92" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>863</v>
+      </c>
+      <c r="C92" s="6">
+        <v>600</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>864</v>
+      </c>
+      <c r="C93" s="5">
+        <v>3</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>865</v>
+      </c>
+      <c r="C94" s="6">
+        <v>120</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="5" t="s">
+        <v>774</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>867</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>868</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>869</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>870</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>872</v>
+      </c>
+      <c r="C98" s="6">
+        <v>3</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>873</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>874</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>875</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>876</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>877</v>
+      </c>
+      <c r="C101" s="5">
+        <v>1800</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>878</v>
+      </c>
+      <c r="C102" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>879</v>
+      </c>
+      <c r="C103" s="5">
+        <v>14000</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>880</v>
+      </c>
+      <c r="C104" s="6">
+        <v>6</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>881</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>882</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>884</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>885</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>886</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>887</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>888</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>889</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>890</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>891</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>892</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>893</v>
+      </c>
+      <c r="C111" s="5">
+        <v>280</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>894</v>
+      </c>
+      <c r="C112" s="6">
+        <v>900</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>895</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>897</v>
+      </c>
+      <c r="C114" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>898</v>
+      </c>
+      <c r="C115" s="5">
+        <v>6</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>899</v>
+      </c>
+      <c r="C116" s="6">
+        <v>4</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>900</v>
+      </c>
+      <c r="C117" s="5">
+        <v>100</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>901</v>
+      </c>
+      <c r="C118" s="6">
+        <v>1</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>902</v>
+      </c>
+      <c r="C119" s="5">
+        <v>90</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>903</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>904</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>905</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="C122" s="6">
+        <v>2</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="C123" s="5">
+        <v>3</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>909</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>910</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>911</v>
+      </c>
+      <c r="C125" s="5">
+        <v>4</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>912</v>
+      </c>
+      <c r="C126" s="6">
+        <v>2</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="C127" s="5">
+        <v>206</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>914</v>
+      </c>
+      <c r="C128" s="6">
+        <v>3</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="5" t="s">
+        <v>774</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="C129" s="5">
+        <v>4</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>916</v>
+      </c>
+      <c r="C130" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="5" t="s">
+        <v>774</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="C132" s="6">
+        <v>10</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:D91"/>
+  <autoFilter ref="A4:D132"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -5584,7 +6341,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U62"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -8783,7 +9540,7 @@
         <v>452</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>280</v>
@@ -8804,7 +9561,7 @@
         <v>303</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>175</v>
@@ -8824,17 +9581,17 @@
       <c r="P52" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="Q52" s="8">
-        <v>0</v>
+      <c r="Q52" s="8" t="s">
+        <v>280</v>
       </c>
       <c r="R52" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="S52" s="8">
-        <v>0</v>
+      <c r="S52" s="8" t="s">
+        <v>280</v>
       </c>
       <c r="T52" s="6" t="s">
-        <v>387</v>
+        <v>441</v>
       </c>
       <c r="U52" s="6" t="s">
         <v>453</v>
@@ -8983,8 +9740,8 @@
       <c r="D55" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="E55" s="7" t="s">
-        <v>280</v>
+      <c r="E55" s="7">
+        <v>1</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>280</v>
@@ -8993,13 +9750,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="I55" s="5" t="s">
         <v>303</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K55" s="5" t="s">
         <v>175</v>
@@ -9019,14 +9776,14 @@
       <c r="P55" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="Q55" s="7" t="s">
-        <v>280</v>
+      <c r="Q55" s="7">
+        <v>0</v>
       </c>
       <c r="R55" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="S55" s="7" t="s">
-        <v>280</v>
+      <c r="S55" s="7">
+        <v>0</v>
       </c>
       <c r="T55" s="5" t="s">
         <v>387</v>
@@ -9138,7 +9895,7 @@
         <v>175</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="N57" s="5" t="s">
         <v>175</v>
@@ -9203,7 +9960,7 @@
         <v>175</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="N58" s="6" t="s">
         <v>175</v>
@@ -9292,39 +10049,39 @@
         <v>387</v>
       </c>
       <c r="U59" s="5" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="60" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>252</v>
+        <v>476</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="E60" s="8">
-        <v>1</v>
+      <c r="E60" s="8" t="s">
+        <v>280</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>280</v>
       </c>
       <c r="G60" s="8">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="I60" s="6" t="s">
         <v>303</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>175</v>
@@ -9344,20 +10101,20 @@
       <c r="P60" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="Q60" s="8">
-        <v>0</v>
+      <c r="Q60" s="8" t="s">
+        <v>280</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="S60" s="8">
-        <v>1</v>
+        <v>280</v>
+      </c>
+      <c r="S60" s="8" t="s">
+        <v>280</v>
       </c>
       <c r="T60" s="6" t="s">
-        <v>475</v>
+        <v>387</v>
       </c>
       <c r="U60" s="6" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="61" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -9365,13 +10122,13 @@
         <v>477</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>478</v>
+        <v>252</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>98</v>
+        <v>280</v>
       </c>
       <c r="E61" s="7">
         <v>1</v>
@@ -9380,13 +10137,13 @@
         <v>280</v>
       </c>
       <c r="G61" s="7">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="J61" s="5" t="s">
         <v>175</v>
@@ -9410,33 +10167,33 @@
         <v>282</v>
       </c>
       <c r="Q61" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R61" s="5" t="s">
-        <v>98</v>
+        <v>252</v>
       </c>
       <c r="S61" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="U61" s="5" t="s">
         <v>479</v>
-      </c>
-      <c r="U61" s="5" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="62" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="B62" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="B62" s="6" t="s">
-        <v>482</v>
-      </c>
       <c r="C62" s="6" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>280</v>
+        <v>98</v>
       </c>
       <c r="E62" s="8">
         <v>1</v>
@@ -9475,23 +10232,88 @@
         <v>282</v>
       </c>
       <c r="Q62" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>280</v>
+        <v>98</v>
       </c>
       <c r="S62" s="8">
         <v>0</v>
       </c>
       <c r="T62" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="U62" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="U62" s="6" t="s">
+    </row>
+    <row r="63" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
         <v>484</v>
       </c>
+      <c r="B63" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="E63" s="7">
+        <v>1</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="G63" s="7">
+        <v>0</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="K63" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="L63" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="M63" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="N63" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="O63" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="P63" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q63" s="7">
+        <v>0</v>
+      </c>
+      <c r="R63" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="S63" s="7">
+        <v>0</v>
+      </c>
+      <c r="T63" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="U63" s="5" t="s">
+        <v>487</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:U62"/>
+  <autoFilter ref="A4:U63"/>
   <mergeCells count="2">
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="A2:U2"/>
@@ -9520,7 +10342,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9532,7 +10354,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -9551,30 +10373,30 @@
         <v>263</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>120</v>
@@ -9586,10 +10408,10 @@
         <v>280</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>280</v>
@@ -9597,10 +10419,10 @@
     </row>
     <row r="6" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>120</v>
@@ -9612,7 +10434,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>280</v>
@@ -9623,10 +10445,10 @@
     </row>
     <row r="7" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>120</v>
@@ -9638,7 +10460,7 @@
         <v>280</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>280</v>
@@ -9649,10 +10471,10 @@
     </row>
     <row r="8" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>120</v>
@@ -9664,7 +10486,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>280</v>
@@ -9675,10 +10497,10 @@
     </row>
     <row r="9" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>120</v>
@@ -9690,7 +10512,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>280</v>
@@ -9701,10 +10523,10 @@
     </row>
     <row r="10" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>120</v>
@@ -9716,7 +10538,7 @@
         <v>6</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>280</v>
@@ -9727,10 +10549,10 @@
     </row>
     <row r="11" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>120</v>
@@ -9742,10 +10564,10 @@
         <v>5</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>280</v>
@@ -9753,10 +10575,10 @@
     </row>
     <row r="12" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>120</v>
@@ -9768,10 +10590,10 @@
         <v>5</v>
       </c>
       <c r="F12" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>518</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>515</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>280</v>
@@ -9779,10 +10601,10 @@
     </row>
     <row r="13" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>120</v>
@@ -9794,10 +10616,10 @@
         <v>4</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>280</v>
@@ -9833,7 +10655,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9845,7 +10667,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -9864,30 +10686,30 @@
         <v>263</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>138</v>
@@ -9899,10 +10721,10 @@
         <v>280</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>280</v>
@@ -9910,10 +10732,10 @@
     </row>
     <row r="6" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>138</v>
@@ -9925,10 +10747,10 @@
         <v>280</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>280</v>
@@ -9936,10 +10758,10 @@
     </row>
     <row r="7" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>250</v>
@@ -9951,10 +10773,10 @@
         <v>280</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>280</v>
@@ -9962,10 +10784,10 @@
     </row>
     <row r="8" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>250</v>
@@ -9977,10 +10799,10 @@
         <v>280</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>280</v>
@@ -10016,7 +10838,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10028,7 +10850,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10047,27 +10869,27 @@
         <v>263</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>169</v>
@@ -10082,7 +10904,7 @@
         <v>280</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>280</v>
@@ -10093,7 +10915,7 @@
     </row>
     <row r="6" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>173</v>
@@ -10108,10 +10930,10 @@
         <v>280</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>280</v>
@@ -10119,10 +10941,10 @@
     </row>
     <row r="7" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>116</v>
@@ -10134,18 +10956,18 @@
         <v>280</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>85</v>
@@ -10160,21 +10982,21 @@
         <v>280</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>116</v>
@@ -10186,21 +11008,21 @@
         <v>280</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>116</v>
@@ -10212,10 +11034,10 @@
         <v>280</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>280</v>
@@ -10223,10 +11045,10 @@
     </row>
     <row r="11" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>116</v>
@@ -10238,10 +11060,10 @@
         <v>280</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>280</v>
@@ -10276,7 +11098,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10287,7 +11109,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10299,33 +11121,33 @@
     <row r="3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>263</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>277</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C5" s="7">
         <v>10</v>
@@ -10334,7 +11156,7 @@
         <v>280</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>280</v>
@@ -10345,10 +11167,10 @@
     </row>
     <row r="6" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C6" s="8">
         <v>0</v>
@@ -10357,10 +11179,10 @@
         <v>280</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>280</v>
@@ -10368,10 +11190,10 @@
     </row>
     <row r="7" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C7" s="7">
         <v>5</v>
@@ -10380,7 +11202,7 @@
         <v>280</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>280</v>
@@ -10391,10 +11213,10 @@
     </row>
     <row r="8" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C8" s="8">
         <v>0</v>
@@ -10403,10 +11225,10 @@
         <v>280</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>280</v>
@@ -10414,10 +11236,10 @@
     </row>
     <row r="9" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C9" s="7">
         <v>30</v>
@@ -10426,7 +11248,7 @@
         <v>280</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>280</v>
@@ -10437,10 +11259,10 @@
     </row>
     <row r="10" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C10" s="8">
         <v>0</v>
@@ -10449,7 +11271,7 @@
         <v>280</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>280</v>
@@ -10460,10 +11282,10 @@
     </row>
     <row r="11" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C11" s="7">
         <v>15</v>
@@ -10472,7 +11294,7 @@
         <v>280</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>280</v>
@@ -10512,7 +11334,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10526,7 +11348,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10541,42 +11363,42 @@
     <row r="3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>263</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>193</v>
@@ -10605,10 +11427,10 @@
     </row>
     <row r="6" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>193</v>
@@ -10637,10 +11459,10 @@
     </row>
     <row r="7" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>193</v>
@@ -10669,10 +11491,10 @@
     </row>
     <row r="8" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>193</v>
@@ -10701,10 +11523,10 @@
     </row>
     <row r="9" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>193</v>
@@ -10733,10 +11555,10 @@
     </row>
     <row r="10" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>193</v>
@@ -10765,10 +11587,10 @@
     </row>
     <row r="11" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>193</v>
@@ -10797,10 +11619,10 @@
     </row>
     <row r="12" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>193</v>
@@ -10829,10 +11651,10 @@
     </row>
     <row r="13" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>193</v>
@@ -10847,7 +11669,7 @@
         <v>280</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>280</v>
@@ -10861,10 +11683,10 @@
     </row>
     <row r="14" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>193</v>
@@ -10893,10 +11715,10 @@
     </row>
     <row r="15" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>193</v>
@@ -10925,10 +11747,10 @@
     </row>
     <row r="16" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>193</v>
@@ -10957,10 +11779,10 @@
     </row>
     <row r="17" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>193</v>
@@ -10989,10 +11811,10 @@
     </row>
     <row r="18" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>217</v>
@@ -11021,10 +11843,10 @@
     </row>
     <row r="19" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>217</v>
@@ -11053,10 +11875,10 @@
     </row>
     <row r="20" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>217</v>
@@ -11085,10 +11907,10 @@
     </row>
     <row r="21" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>134</v>
@@ -11117,10 +11939,10 @@
     </row>
     <row r="22" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>134</v>
@@ -11149,10 +11971,10 @@
     </row>
     <row r="23" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>134</v>
@@ -11181,10 +12003,10 @@
     </row>
     <row r="24" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>134</v>
@@ -11213,13 +12035,13 @@
     </row>
     <row r="25" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="D25" s="7">
         <v>6</v>
@@ -11279,7 +12101,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11300,7 +12122,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11322,25 +12144,25 @@
     <row r="3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>246</v>
@@ -11352,7 +12174,7 @@
         <v>150</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>136</v>
@@ -11375,10 +12197,10 @@
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>193</v>
@@ -11393,7 +12215,7 @@
         <v>280</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="H5" s="7">
         <v>12</v>
@@ -11428,10 +12250,10 @@
     </row>
     <row r="6" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>193</v>
@@ -11446,7 +12268,7 @@
         <v>280</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="H6" s="8">
         <v>6</v>
@@ -11458,7 +12280,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>280</v>
@@ -11481,10 +12303,10 @@
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>193</v>
@@ -11499,7 +12321,7 @@
         <v>280</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="H7" s="7">
         <v>0</v>
@@ -11511,7 +12333,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>280</v>
@@ -11534,10 +12356,10 @@
     </row>
     <row r="8" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>193</v>
@@ -11552,7 +12374,7 @@
         <v>280</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="H8" s="8">
         <v>0</v>
@@ -11564,7 +12386,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>280</v>
@@ -11587,10 +12409,10 @@
     </row>
     <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>193</v>
@@ -11605,7 +12427,7 @@
         <v>280</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="H9" s="7">
         <v>7</v>
@@ -11640,10 +12462,10 @@
     </row>
     <row r="10" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>193</v>
@@ -11658,7 +12480,7 @@
         <v>280</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="H10" s="8">
         <v>13</v>
@@ -11693,10 +12515,10 @@
     </row>
     <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>193</v>
@@ -11711,7 +12533,7 @@
         <v>280</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="H11" s="7">
         <v>3</v>
@@ -11746,10 +12568,10 @@
     </row>
     <row r="12" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>193</v>
@@ -11764,7 +12586,7 @@
         <v>50</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="H12" s="8">
         <v>10</v>
@@ -11799,10 +12621,10 @@
     </row>
     <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>193</v>
@@ -11817,7 +12639,7 @@
         <v>50</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="H13" s="7">
         <v>2</v>
@@ -11852,10 +12674,10 @@
     </row>
     <row r="14" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>193</v>
@@ -11870,7 +12692,7 @@
         <v>280</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="H14" s="8">
         <v>6</v>
@@ -11905,10 +12727,10 @@
     </row>
     <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>193</v>
@@ -11923,7 +12745,7 @@
         <v>280</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="H15" s="7">
         <v>8</v>
@@ -11935,7 +12757,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>280</v>
@@ -11958,10 +12780,10 @@
     </row>
     <row r="16" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>193</v>
@@ -11976,7 +12798,7 @@
         <v>280</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="H16" s="8">
         <v>16</v>
@@ -12011,10 +12833,10 @@
     </row>
     <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>193</v>
@@ -12029,7 +12851,7 @@
         <v>280</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="H17" s="7">
         <v>4</v>
@@ -12064,10 +12886,10 @@
     </row>
     <row r="18" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>193</v>
@@ -12082,7 +12904,7 @@
         <v>33</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="H18" s="8">
         <v>14</v>
@@ -12117,10 +12939,10 @@
     </row>
     <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>193</v>
@@ -12135,7 +12957,7 @@
         <v>33</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="H19" s="7">
         <v>0</v>
@@ -12147,7 +12969,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="L19" s="5" t="s">
         <v>280</v>
@@ -12170,10 +12992,10 @@
     </row>
     <row r="20" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>193</v>
@@ -12188,7 +13010,7 @@
         <v>34</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="H20" s="8">
         <v>4</v>
@@ -12223,10 +13045,10 @@
     </row>
     <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>193</v>
@@ -12241,7 +13063,7 @@
         <v>280</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="H21" s="7">
         <v>0</v>
@@ -12262,7 +13084,7 @@
         <v>280</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="O21" s="5" t="s">
         <v>175</v>
@@ -12276,10 +13098,10 @@
     </row>
     <row r="22" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>193</v>
@@ -12294,7 +13116,7 @@
         <v>40</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="H22" s="8">
         <v>8</v>
@@ -12306,7 +13128,7 @@
         <v>1</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>280</v>
@@ -12329,10 +13151,10 @@
     </row>
     <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>193</v>
@@ -12347,7 +13169,7 @@
         <v>60</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="H23" s="7">
         <v>14</v>
@@ -12382,10 +13204,10 @@
     </row>
     <row r="24" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>193</v>
@@ -12400,7 +13222,7 @@
         <v>280</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="H24" s="8">
         <v>3</v>
@@ -12412,7 +13234,7 @@
         <v>2</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="L24" s="6" t="s">
         <v>280</v>
@@ -12435,10 +13257,10 @@
     </row>
     <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>193</v>
@@ -12453,7 +13275,7 @@
         <v>280</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="H25" s="7">
         <v>0</v>
@@ -12465,7 +13287,7 @@
         <v>1</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>280</v>
@@ -12488,10 +13310,10 @@
     </row>
     <row r="26" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>193</v>
@@ -12506,7 +13328,7 @@
         <v>50</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="H26" s="8">
         <v>7</v>
@@ -12518,7 +13340,7 @@
         <v>1</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>280</v>
@@ -12541,10 +13363,10 @@
     </row>
     <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>193</v>
@@ -12559,7 +13381,7 @@
         <v>50</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="H27" s="7">
         <v>12</v>
@@ -12594,10 +13416,10 @@
     </row>
     <row r="28" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>193</v>
@@ -12612,7 +13434,7 @@
         <v>280</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="H28" s="8">
         <v>0</v>
@@ -12624,7 +13446,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>280</v>
@@ -12647,10 +13469,10 @@
     </row>
     <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>193</v>
@@ -12665,7 +13487,7 @@
         <v>280</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="H29" s="7">
         <v>7</v>
@@ -12677,7 +13499,7 @@
         <v>2</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>280</v>
@@ -12700,10 +13522,10 @@
     </row>
     <row r="30" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>193</v>
@@ -12718,7 +13540,7 @@
         <v>280</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="H30" s="8">
         <v>7</v>
@@ -12730,7 +13552,7 @@
         <v>2</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="L30" s="6" t="s">
         <v>280</v>
@@ -12753,10 +13575,10 @@
     </row>
     <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>193</v>
@@ -12771,7 +13593,7 @@
         <v>280</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="H31" s="7">
         <v>5</v>
@@ -12806,10 +13628,10 @@
     </row>
     <row r="32" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>193</v>
@@ -12824,7 +13646,7 @@
         <v>50</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="H32" s="8">
         <v>8</v>
@@ -12836,7 +13658,7 @@
         <v>1</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="L32" s="6" t="s">
         <v>280</v>
@@ -12859,10 +13681,10 @@
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>193</v>
@@ -12877,7 +13699,7 @@
         <v>50</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="H33" s="7">
         <v>11</v>
@@ -12912,10 +13734,10 @@
     </row>
     <row r="34" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>193</v>
@@ -12930,7 +13752,7 @@
         <v>280</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="H34" s="8">
         <v>0</v>
@@ -12942,7 +13764,7 @@
         <v>1</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="L34" s="6" t="s">
         <v>280</v>
@@ -12965,10 +13787,10 @@
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>193</v>
@@ -12983,7 +13805,7 @@
         <v>280</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="H35" s="7">
         <v>4</v>
@@ -13018,10 +13840,10 @@
     </row>
     <row r="36" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>193</v>
@@ -13036,7 +13858,7 @@
         <v>280</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="H36" s="8">
         <v>0</v>
@@ -13048,7 +13870,7 @@
         <v>0</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="L36" s="6" t="s">
         <v>280</v>
@@ -13071,10 +13893,10 @@
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>193</v>
@@ -13089,7 +13911,7 @@
         <v>280</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="H37" s="7">
         <v>4</v>
@@ -13124,10 +13946,10 @@
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>193</v>
@@ -13142,7 +13964,7 @@
         <v>280</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="H38" s="8">
         <v>0</v>
@@ -13157,7 +13979,7 @@
         <v>387</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="M38" s="8" t="s">
         <v>280</v>
@@ -13177,10 +13999,10 @@
     </row>
     <row r="39" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>193</v>
@@ -13195,7 +14017,7 @@
         <v>280</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H39" s="7">
         <v>8</v>
@@ -13230,10 +14052,10 @@
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>193</v>
@@ -13248,7 +14070,7 @@
         <v>280</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="H40" s="8">
         <v>0</v>
@@ -13263,7 +14085,7 @@
         <v>387</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="M40" s="8" t="s">
         <v>280</v>
@@ -13283,10 +14105,10 @@
     </row>
     <row r="41" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>193</v>
@@ -13301,7 +14123,7 @@
         <v>50</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="H41" s="7">
         <v>11</v>
@@ -13336,10 +14158,10 @@
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>193</v>
@@ -13354,7 +14176,7 @@
         <v>50</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="H42" s="8">
         <v>0</v>
@@ -13369,7 +14191,7 @@
         <v>387</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="M42" s="8" t="s">
         <v>280</v>
@@ -13389,10 +14211,10 @@
     </row>
     <row r="43" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>217</v>
@@ -13407,7 +14229,7 @@
         <v>280</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="H43" s="7">
         <v>0</v>
@@ -13442,10 +14264,10 @@
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>217</v>
@@ -13460,7 +14282,7 @@
         <v>280</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="H44" s="8">
         <v>0</v>
@@ -13472,7 +14294,7 @@
         <v>0</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="L44" s="6" t="s">
         <v>280</v>
@@ -13495,10 +14317,10 @@
     </row>
     <row r="45" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>217</v>
@@ -13513,7 +14335,7 @@
         <v>280</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="H45" s="7">
         <v>13</v>
@@ -13548,10 +14370,10 @@
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>217</v>
@@ -13566,7 +14388,7 @@
         <v>280</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="H46" s="8">
         <v>0</v>
@@ -13601,10 +14423,10 @@
     </row>
     <row r="47" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>217</v>
@@ -13619,7 +14441,7 @@
         <v>280</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="H47" s="7">
         <v>13</v>
@@ -13654,10 +14476,10 @@
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>217</v>
@@ -13672,7 +14494,7 @@
         <v>280</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="H48" s="8">
         <v>17</v>
@@ -13707,10 +14529,10 @@
     </row>
     <row r="49" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>217</v>
@@ -13725,7 +14547,7 @@
         <v>280</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="H49" s="7">
         <v>3</v>
@@ -13760,10 +14582,10 @@
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>217</v>
@@ -13778,7 +14600,7 @@
         <v>280</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="H50" s="8">
         <v>0</v>
@@ -13793,7 +14615,7 @@
         <v>387</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="M50" s="8" t="s">
         <v>280</v>
@@ -13813,10 +14635,10 @@
     </row>
     <row r="51" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>217</v>
@@ -13831,7 +14653,7 @@
         <v>280</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="H51" s="7">
         <v>4</v>
@@ -13866,10 +14688,10 @@
     </row>
     <row r="52" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>134</v>
@@ -13884,7 +14706,7 @@
         <v>280</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="H52" s="8">
         <v>0</v>
@@ -13896,7 +14718,7 @@
         <v>1</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="L52" s="6" t="s">
         <v>280</v>
@@ -13919,10 +14741,10 @@
     </row>
     <row r="53" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>134</v>
@@ -13937,7 +14759,7 @@
         <v>280</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="H53" s="7">
         <v>18</v>
@@ -13949,7 +14771,7 @@
         <v>1</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="L53" s="5" t="s">
         <v>280</v>
@@ -13972,10 +14794,10 @@
     </row>
     <row r="54" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>134</v>
@@ -13990,7 +14812,7 @@
         <v>280</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="H54" s="8">
         <v>18</v>
@@ -14025,10 +14847,10 @@
     </row>
     <row r="55" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>134</v>
@@ -14043,7 +14865,7 @@
         <v>280</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="H55" s="7">
         <v>0</v>
@@ -14078,10 +14900,10 @@
     </row>
     <row r="56" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>134</v>
@@ -14096,7 +14918,7 @@
         <v>280</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="H56" s="8">
         <v>0</v>
@@ -14108,7 +14930,7 @@
         <v>2</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="L56" s="6" t="s">
         <v>280</v>
@@ -14131,10 +14953,10 @@
     </row>
     <row r="57" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>134</v>
@@ -14149,7 +14971,7 @@
         <v>280</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="H57" s="7">
         <v>15</v>
@@ -14184,10 +15006,10 @@
     </row>
     <row r="58" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>134</v>
@@ -14202,7 +15024,7 @@
         <v>280</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="H58" s="8">
         <v>17</v>
@@ -14214,7 +15036,7 @@
         <v>1</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="L58" s="6" t="s">
         <v>280</v>
@@ -14237,10 +15059,10 @@
     </row>
     <row r="59" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>134</v>
@@ -14255,7 +15077,7 @@
         <v>280</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="H59" s="7">
         <v>5</v>
@@ -14290,10 +15112,10 @@
     </row>
     <row r="60" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>134</v>
@@ -14308,7 +15130,7 @@
         <v>280</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="H60" s="8">
         <v>2</v>
@@ -14343,10 +15165,10 @@
     </row>
     <row r="61" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>134</v>
@@ -14361,7 +15183,7 @@
         <v>280</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="H61" s="7">
         <v>0</v>
@@ -14373,7 +15195,7 @@
         <v>0</v>
       </c>
       <c r="K61" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="L61" s="5" t="s">
         <v>280</v>
@@ -14396,10 +15218,10 @@
     </row>
     <row r="62" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>134</v>
@@ -14414,7 +15236,7 @@
         <v>280</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="H62" s="8">
         <v>8</v>
@@ -14426,7 +15248,7 @@
         <v>2</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="L62" s="6" t="s">
         <v>280</v>
@@ -14449,10 +15271,10 @@
     </row>
     <row r="63" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>134</v>
@@ -14467,7 +15289,7 @@
         <v>280</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="H63" s="7">
         <v>8</v>
@@ -14479,7 +15301,7 @@
         <v>2</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="L63" s="5" t="s">
         <v>280</v>
@@ -14502,10 +15324,10 @@
     </row>
     <row r="64" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>134</v>
@@ -14520,7 +15342,7 @@
         <v>280</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="H64" s="8">
         <v>3</v>
@@ -14555,10 +15377,10 @@
     </row>
     <row r="65" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>134</v>
@@ -14573,7 +15395,7 @@
         <v>280</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="H65" s="7">
         <v>0</v>
@@ -14585,7 +15407,7 @@
         <v>0</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="L65" s="5" t="s">
         <v>280</v>
@@ -14608,10 +15430,10 @@
     </row>
     <row r="66" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>134</v>
@@ -14626,7 +15448,7 @@
         <v>280</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="H66" s="8">
         <v>7</v>
@@ -14661,10 +15483,10 @@
     </row>
     <row r="67" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>134</v>
@@ -14679,7 +15501,7 @@
         <v>280</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H67" s="7">
         <v>6</v>
@@ -14714,10 +15536,10 @@
     </row>
     <row r="68" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>134</v>
@@ -14732,7 +15554,7 @@
         <v>280</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="H68" s="8">
         <v>26</v>
@@ -14744,7 +15566,7 @@
         <v>1</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="L68" s="6" t="s">
         <v>280</v>
@@ -14767,10 +15589,10 @@
     </row>
     <row r="69" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>134</v>
@@ -14785,7 +15607,7 @@
         <v>280</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="H69" s="7">
         <v>0</v>
@@ -14797,7 +15619,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="L69" s="5" t="s">
         <v>280</v>
@@ -14820,13 +15642,13 @@
     </row>
     <row r="70" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="D70" s="8">
         <v>1</v>
@@ -14838,7 +15660,7 @@
         <v>280</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="H70" s="8">
         <v>0</v>
@@ -14853,7 +15675,7 @@
         <v>387</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="M70" s="8">
         <v>2</v>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -259,7 +259,7 @@
     <t>구역 증원 주기</t>
   </si>
   <si>
-    <t>90 / 봉쇄 45</t>
+    <t>180 / 봉쇄 90</t>
   </si>
   <si>
     <t>구역별 독립 시계. 로스터의 빈자리만 채운다</t>
@@ -2974,7 +2974,7 @@
     <t>THREAT_COUNT_BY_SECTOR</t>
   </si>
   <si>
-    <t>{"entrance":3,"labs":5,"hangar":5,"security":6,"파워":7,"waste":6,"comms":4,"residential":4}</t>
+    <t>{"entrance":3,"labs":3,"hangar":3,"security":4,"파워":5,"waste":4,"comms":3,"residential":3}</t>
   </si>
   <si>
     <t>THREAT_GROUP_SIZE_WEIGHTS</t>
@@ -5914,7 +5914,7 @@
         <v>953</v>
       </c>
       <c r="C125" s="5">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>64</v>
@@ -5928,7 +5928,7 @@
         <v>954</v>
       </c>
       <c r="C126" s="6">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>64</v>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3175" uniqueCount="1001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3182" uniqueCount="1004">
   <si>
     <t>현재 구현 규칙</t>
   </si>
@@ -2605,6 +2605,12 @@
     <t>ENCOUNTER_DECEIVE_REQUIREMENT</t>
   </si>
   <si>
+    <t>ENCOUNTER_DECEIVE_STEP_PENALTY</t>
+  </si>
+  <si>
+    <t>{"surplus":{"successPenalty":0,"raisesThreatAlert":false},"standard":{"successPenalty":0,"raisesThreatAlert":false},"strained":{"successPenalty":1,"raisesThreatAlert":false},"severe":{"successPenalty":1,"raisesThreatAlert":true}}</t>
+  </si>
+  <si>
     <t>ENCOUNTER_EVADE_TIME</t>
   </si>
   <si>
@@ -2650,7 +2656,7 @@
     <t>FAKE_NOISE_RANGE_BY_DECEPTION</t>
   </si>
   <si>
-    <t>[0,0,0,1,2,3,3]</t>
+    <t>[0,1,1,1,2,3,3]</t>
   </si>
   <si>
     <t>FAKE_NOISE_REQUIREMENT</t>
@@ -2729,6 +2735,9 @@
   </si>
   <si>
     <t>HALL_STEALTH_PENALTY</t>
+  </si>
+  <si>
+    <t>HIGH_GROUND_MOBILITY_REQUIREMENT</t>
   </si>
   <si>
     <t>INVESTIGATE_DECAY_TICKS</t>
@@ -4186,7 +4195,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D163"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -4886,13 +4895,13 @@
     </row>
     <row r="52" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>801</v>
+        <v>824</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>861</v>
       </c>
-      <c r="C52" s="6">
-        <v>1</v>
+      <c r="C52" s="6" t="s">
+        <v>862</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>64</v>
@@ -4900,13 +4909,13 @@
     </row>
     <row r="53" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C53" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>64</v>
@@ -4917,7 +4926,7 @@
         <v>803</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C54" s="6">
         <v>2</v>
@@ -4928,13 +4937,13 @@
     </row>
     <row r="55" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>824</v>
+        <v>803</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>864</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>328</v>
+        <v>865</v>
+      </c>
+      <c r="C55" s="5">
+        <v>2</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>64</v>
@@ -4942,13 +4951,13 @@
     </row>
     <row r="56" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>81</v>
+        <v>824</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>865</v>
-      </c>
-      <c r="C56" s="6">
-        <v>430</v>
+        <v>866</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>328</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>64</v>
@@ -4959,10 +4968,10 @@
         <v>81</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C57" s="5">
-        <v>120</v>
+        <v>430</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>64</v>
@@ -4973,10 +4982,10 @@
         <v>81</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C58" s="6">
-        <v>670</v>
+        <v>120</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>64</v>
@@ -4987,10 +4996,10 @@
         <v>81</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>868</v>
-      </c>
-      <c r="C59" s="5" t="s">
         <v>869</v>
+      </c>
+      <c r="C59" s="5">
+        <v>670</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>64</v>
@@ -5003,8 +5012,8 @@
       <c r="B60" s="6" t="s">
         <v>870</v>
       </c>
-      <c r="C60" s="6">
-        <v>5</v>
+      <c r="C60" s="6" t="s">
+        <v>871</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>64</v>
@@ -5015,10 +5024,10 @@
         <v>81</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C61" s="5">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>64</v>
@@ -5029,10 +5038,10 @@
         <v>81</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C62" s="6">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>64</v>
@@ -5040,13 +5049,13 @@
     </row>
     <row r="63" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>803</v>
+        <v>81</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C63" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>64</v>
@@ -5057,10 +5066,10 @@
         <v>803</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C64" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>64</v>
@@ -5071,10 +5080,10 @@
         <v>803</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>875</v>
-      </c>
-      <c r="C65" s="5" t="s">
         <v>876</v>
+      </c>
+      <c r="C65" s="5">
+        <v>3</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>64</v>
@@ -5087,8 +5096,8 @@
       <c r="B66" s="6" t="s">
         <v>877</v>
       </c>
-      <c r="C66" s="6">
-        <v>1</v>
+      <c r="C66" s="6" t="s">
+        <v>878</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>64</v>
@@ -5099,10 +5108,10 @@
         <v>803</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C67" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>64</v>
@@ -5113,10 +5122,10 @@
         <v>803</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C68" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>64</v>
@@ -5127,10 +5136,10 @@
         <v>803</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C69" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>64</v>
@@ -5138,13 +5147,13 @@
     </row>
     <row r="70" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>824</v>
+        <v>803</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C70" s="6">
-        <v>256</v>
+        <v>3</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>64</v>
@@ -5152,13 +5161,13 @@
     </row>
     <row r="71" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>797</v>
+        <v>824</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C71" s="5">
-        <v>3</v>
+        <v>256</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>64</v>
@@ -5166,13 +5175,13 @@
     </row>
     <row r="72" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>824</v>
+        <v>797</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>883</v>
-      </c>
-      <c r="C72" s="6" t="s">
         <v>884</v>
+      </c>
+      <c r="C72" s="6">
+        <v>3</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>64</v>
@@ -5185,8 +5194,8 @@
       <c r="B73" s="5" t="s">
         <v>885</v>
       </c>
-      <c r="C73" s="5">
-        <v>2</v>
+      <c r="C73" s="5" t="s">
+        <v>886</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>64</v>
@@ -5194,13 +5203,13 @@
     </row>
     <row r="74" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>32</v>
+        <v>824</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C74" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>64</v>
@@ -5208,13 +5217,13 @@
     </row>
     <row r="75" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>824</v>
+        <v>32</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C75" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>64</v>
@@ -5222,13 +5231,13 @@
     </row>
     <row r="76" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>803</v>
+        <v>824</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C76" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>64</v>
@@ -5236,13 +5245,13 @@
     </row>
     <row r="77" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C77" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>64</v>
@@ -5250,13 +5259,13 @@
     </row>
     <row r="78" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>824</v>
+        <v>801</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C78" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>64</v>
@@ -5264,13 +5273,13 @@
     </row>
     <row r="79" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>797</v>
+        <v>824</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C79" s="5">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>64</v>
@@ -5278,13 +5287,13 @@
     </row>
     <row r="80" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>815</v>
+        <v>797</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C80" s="6">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>64</v>
@@ -5292,13 +5301,13 @@
     </row>
     <row r="81" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C81" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>64</v>
@@ -5306,13 +5315,13 @@
     </row>
     <row r="82" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>815</v>
+        <v>803</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C82" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>64</v>
@@ -5323,10 +5332,10 @@
         <v>815</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C83" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>64</v>
@@ -5337,10 +5346,10 @@
         <v>815</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C84" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>64</v>
@@ -5348,13 +5357,13 @@
     </row>
     <row r="85" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>797</v>
+        <v>815</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>897</v>
-      </c>
-      <c r="C85" s="5" t="s">
         <v>898</v>
+      </c>
+      <c r="C85" s="5">
+        <v>5</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>64</v>
@@ -5362,13 +5371,13 @@
     </row>
     <row r="86" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>899</v>
       </c>
-      <c r="C86" s="6">
-        <v>0</v>
+      <c r="C86" s="6" t="s">
+        <v>900</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>64</v>
@@ -5376,13 +5385,13 @@
     </row>
     <row r="87" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C87" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>64</v>
@@ -5393,10 +5402,10 @@
         <v>801</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C88" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>64</v>
@@ -5404,13 +5413,13 @@
     </row>
     <row r="89" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>824</v>
+        <v>801</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C89" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>64</v>
@@ -5421,10 +5430,10 @@
         <v>824</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C90" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>64</v>
@@ -5432,13 +5441,13 @@
     </row>
     <row r="91" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C91" s="5">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>64</v>
@@ -5446,13 +5455,13 @@
     </row>
     <row r="92" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>905</v>
+        <v>824</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>906</v>
       </c>
       <c r="C92" s="6">
-        <v>0.01</v>
+        <v>8</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>64</v>
@@ -5460,13 +5469,13 @@
     </row>
     <row r="93" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>905</v>
+        <v>803</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>907</v>
       </c>
       <c r="C93" s="5">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>64</v>
@@ -5474,13 +5483,13 @@
     </row>
     <row r="94" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C94" s="6">
-        <v>2</v>
+        <v>0.01</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>64</v>
@@ -5488,13 +5497,13 @@
     </row>
     <row r="95" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>797</v>
+        <v>908</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>909</v>
-      </c>
-      <c r="C95" s="5" t="s">
         <v>910</v>
+      </c>
+      <c r="C95" s="5">
+        <v>4</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>64</v>
@@ -5502,13 +5511,13 @@
     </row>
     <row r="96" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>81</v>
+        <v>908</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>911</v>
       </c>
       <c r="C96" s="6">
-        <v>125</v>
+        <v>2</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>64</v>
@@ -5516,7 +5525,7 @@
     </row>
     <row r="97" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>912</v>
@@ -5530,13 +5539,13 @@
     </row>
     <row r="98" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>803</v>
+        <v>81</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>914</v>
       </c>
-      <c r="C98" s="6" t="s">
-        <v>915</v>
+      <c r="C98" s="6">
+        <v>125</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>64</v>
@@ -5544,13 +5553,13 @@
     </row>
     <row r="99" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="B99" s="5" t="s">
+        <v>915</v>
+      </c>
+      <c r="C99" s="5" t="s">
         <v>916</v>
-      </c>
-      <c r="C99" s="5">
-        <v>3</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>64</v>
@@ -5558,13 +5567,13 @@
     </row>
     <row r="100" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>917</v>
       </c>
-      <c r="C100" s="6">
-        <v>2</v>
+      <c r="C100" s="6" t="s">
+        <v>918</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>64</v>
@@ -5572,13 +5581,13 @@
     </row>
     <row r="101" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>918</v>
-      </c>
-      <c r="C101" s="5" t="s">
         <v>919</v>
+      </c>
+      <c r="C101" s="5">
+        <v>3</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>64</v>
@@ -5586,7 +5595,7 @@
     </row>
     <row r="102" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>824</v>
+        <v>797</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>920</v>
@@ -5600,13 +5609,13 @@
     </row>
     <row r="103" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>921</v>
       </c>
-      <c r="C103" s="5">
-        <v>0.17</v>
+      <c r="C103" s="5" t="s">
+        <v>922</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>64</v>
@@ -5614,13 +5623,13 @@
     </row>
     <row r="104" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>797</v>
+        <v>824</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C104" s="6">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>64</v>
@@ -5631,10 +5640,10 @@
         <v>797</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>923</v>
-      </c>
-      <c r="C105" s="5" t="s">
         <v>924</v>
+      </c>
+      <c r="C105" s="5">
+        <v>0.17</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>64</v>
@@ -5647,8 +5656,8 @@
       <c r="B106" s="6" t="s">
         <v>925</v>
       </c>
-      <c r="C106" s="6" t="s">
-        <v>926</v>
+      <c r="C106" s="6">
+        <v>24</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>64</v>
@@ -5656,13 +5665,13 @@
     </row>
     <row r="107" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="B107" s="5" t="s">
+        <v>926</v>
+      </c>
+      <c r="C107" s="5" t="s">
         <v>927</v>
-      </c>
-      <c r="C107" s="5">
-        <v>5</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>64</v>
@@ -5670,7 +5679,7 @@
     </row>
     <row r="108" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>928</v>
@@ -5684,13 +5693,13 @@
     </row>
     <row r="109" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>905</v>
+        <v>803</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>930</v>
       </c>
-      <c r="C109" s="5" t="s">
-        <v>931</v>
+      <c r="C109" s="5">
+        <v>5</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>64</v>
@@ -5698,13 +5707,13 @@
     </row>
     <row r="110" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
-        <v>32</v>
+        <v>803</v>
       </c>
       <c r="B110" s="6" t="s">
+        <v>931</v>
+      </c>
+      <c r="C110" s="6" t="s">
         <v>932</v>
-      </c>
-      <c r="C110" s="6">
-        <v>100</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>64</v>
@@ -5712,13 +5721,13 @@
     </row>
     <row r="111" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>32</v>
+        <v>908</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>933</v>
       </c>
-      <c r="C111" s="5">
-        <v>0</v>
+      <c r="C111" s="5" t="s">
+        <v>934</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>64</v>
@@ -5726,13 +5735,13 @@
     </row>
     <row r="112" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
-        <v>824</v>
+        <v>32</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>934</v>
-      </c>
-      <c r="C112" s="6" t="s">
         <v>935</v>
+      </c>
+      <c r="C112" s="6">
+        <v>100</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>64</v>
@@ -5740,13 +5749,13 @@
     </row>
     <row r="113" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>801</v>
+        <v>32</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>936</v>
       </c>
       <c r="C113" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>64</v>
@@ -5759,8 +5768,8 @@
       <c r="B114" s="6" t="s">
         <v>937</v>
       </c>
-      <c r="C114" s="6">
-        <v>30</v>
+      <c r="C114" s="6" t="s">
+        <v>938</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>64</v>
@@ -5768,13 +5777,13 @@
     </row>
     <row r="115" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C115" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>64</v>
@@ -5785,10 +5794,10 @@
         <v>824</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C116" s="6">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>64</v>
@@ -5796,13 +5805,13 @@
     </row>
     <row r="117" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>824</v>
+        <v>803</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>940</v>
-      </c>
-      <c r="C117" s="5" t="s">
         <v>941</v>
+      </c>
+      <c r="C117" s="5">
+        <v>3</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>64</v>
@@ -5810,13 +5819,13 @@
     </row>
     <row r="118" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
-        <v>803</v>
+        <v>824</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>942</v>
       </c>
-      <c r="C118" s="6" t="s">
-        <v>943</v>
+      <c r="C118" s="6">
+        <v>6</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>64</v>
@@ -5824,13 +5833,13 @@
     </row>
     <row r="119" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>801</v>
+        <v>824</v>
       </c>
       <c r="B119" s="5" t="s">
+        <v>943</v>
+      </c>
+      <c r="C119" s="5" t="s">
         <v>944</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>945</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>64</v>
@@ -5838,13 +5847,13 @@
     </row>
     <row r="120" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
-        <v>824</v>
+        <v>803</v>
       </c>
       <c r="B120" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="C120" s="6" t="s">
         <v>946</v>
-      </c>
-      <c r="C120" s="6">
-        <v>3</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>64</v>
@@ -5852,7 +5861,7 @@
     </row>
     <row r="121" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>947</v>
@@ -5871,8 +5880,8 @@
       <c r="B122" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="C122" s="6" t="s">
-        <v>950</v>
+      <c r="C122" s="6">
+        <v>3</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>64</v>
@@ -5880,13 +5889,13 @@
     </row>
     <row r="123" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="B123" s="5" t="s">
+        <v>950</v>
+      </c>
+      <c r="C123" s="5" t="s">
         <v>951</v>
-      </c>
-      <c r="C123" s="5">
-        <v>2</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>64</v>
@@ -5899,8 +5908,8 @@
       <c r="B124" s="6" t="s">
         <v>952</v>
       </c>
-      <c r="C124" s="6">
-        <v>6</v>
+      <c r="C124" s="6" t="s">
+        <v>953</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>64</v>
@@ -5908,13 +5917,13 @@
     </row>
     <row r="125" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C125" s="5">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>64</v>
@@ -5922,13 +5931,13 @@
     </row>
     <row r="126" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
-        <v>801</v>
+        <v>824</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C126" s="6">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>64</v>
@@ -5936,13 +5945,13 @@
     </row>
     <row r="127" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>81</v>
+        <v>801</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C127" s="5">
-        <v>700</v>
+        <v>90</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>64</v>
@@ -5950,13 +5959,13 @@
     </row>
     <row r="128" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
-        <v>32</v>
+        <v>801</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C128" s="6">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>64</v>
@@ -5964,13 +5973,13 @@
     </row>
     <row r="129" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C129" s="5">
-        <v>2</v>
+        <v>700</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>64</v>
@@ -5978,13 +5987,13 @@
     </row>
     <row r="130" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
-        <v>797</v>
+        <v>32</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>958</v>
-      </c>
-      <c r="C130" s="6" t="s">
         <v>959</v>
+      </c>
+      <c r="C130" s="6">
+        <v>3</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>64</v>
@@ -5992,13 +6001,13 @@
     </row>
     <row r="131" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
-        <v>803</v>
+        <v>32</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>960</v>
       </c>
-      <c r="C131" s="5" t="s">
-        <v>961</v>
+      <c r="C131" s="5">
+        <v>2</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>64</v>
@@ -6006,13 +6015,13 @@
     </row>
     <row r="132" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="B132" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="C132" s="6" t="s">
         <v>962</v>
-      </c>
-      <c r="C132" s="6" t="s">
-        <v>963</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>64</v>
@@ -6020,13 +6029,13 @@
     </row>
     <row r="133" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="B133" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="C133" s="5" t="s">
         <v>964</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>965</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>64</v>
@@ -6034,13 +6043,13 @@
     </row>
     <row r="134" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="B134" s="6" t="s">
+        <v>965</v>
+      </c>
+      <c r="C134" s="6" t="s">
         <v>966</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>967</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>64</v>
@@ -6051,10 +6060,10 @@
         <v>797</v>
       </c>
       <c r="B135" s="5" t="s">
+        <v>967</v>
+      </c>
+      <c r="C135" s="5" t="s">
         <v>968</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>969</v>
       </c>
       <c r="D135" s="5" t="s">
         <v>64</v>
@@ -6065,10 +6074,10 @@
         <v>797</v>
       </c>
       <c r="B136" s="6" t="s">
+        <v>969</v>
+      </c>
+      <c r="C136" s="6" t="s">
         <v>970</v>
-      </c>
-      <c r="C136" s="6">
-        <v>280</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>64</v>
@@ -6081,8 +6090,8 @@
       <c r="B137" s="5" t="s">
         <v>971</v>
       </c>
-      <c r="C137" s="5">
-        <v>900</v>
+      <c r="C137" s="5" t="s">
+        <v>972</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>64</v>
@@ -6093,10 +6102,10 @@
         <v>797</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>972</v>
-      </c>
-      <c r="C138" s="6" t="s">
         <v>973</v>
+      </c>
+      <c r="C138" s="6">
+        <v>280</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>64</v>
@@ -6110,7 +6119,7 @@
         <v>974</v>
       </c>
       <c r="C139" s="5">
-        <v>0.4</v>
+        <v>900</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>64</v>
@@ -6123,8 +6132,8 @@
       <c r="B140" s="6" t="s">
         <v>975</v>
       </c>
-      <c r="C140" s="6">
-        <v>6</v>
+      <c r="C140" s="6" t="s">
+        <v>976</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>64</v>
@@ -6135,10 +6144,10 @@
         <v>797</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C141" s="5">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>64</v>
@@ -6149,10 +6158,10 @@
         <v>797</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C142" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>64</v>
@@ -6160,13 +6169,13 @@
     </row>
     <row r="143" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
-        <v>815</v>
+        <v>797</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C143" s="5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>64</v>
@@ -6174,13 +6183,13 @@
     </row>
     <row r="144" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
-        <v>824</v>
+        <v>797</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C144" s="6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>64</v>
@@ -6188,13 +6197,13 @@
     </row>
     <row r="145" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
-        <v>824</v>
+        <v>815</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C145" s="5">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>64</v>
@@ -6202,13 +6211,13 @@
     </row>
     <row r="146" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
-        <v>803</v>
+        <v>824</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C146" s="6">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>64</v>
@@ -6216,13 +6225,13 @@
     </row>
     <row r="147" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
-        <v>801</v>
+        <v>824</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C147" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>64</v>
@@ -6233,10 +6242,10 @@
         <v>803</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>983</v>
-      </c>
-      <c r="C148" s="6" t="s">
         <v>984</v>
+      </c>
+      <c r="C148" s="6">
+        <v>1</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>64</v>
@@ -6244,13 +6253,13 @@
     </row>
     <row r="149" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>985</v>
       </c>
-      <c r="C149" s="5" t="s">
-        <v>986</v>
+      <c r="C149" s="5">
+        <v>5</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>64</v>
@@ -6261,10 +6270,10 @@
         <v>803</v>
       </c>
       <c r="B150" s="6" t="s">
+        <v>986</v>
+      </c>
+      <c r="C150" s="6" t="s">
         <v>987</v>
-      </c>
-      <c r="C150" s="6">
-        <v>2</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>64</v>
@@ -6277,8 +6286,8 @@
       <c r="B151" s="5" t="s">
         <v>988</v>
       </c>
-      <c r="C151" s="5">
-        <v>3</v>
+      <c r="C151" s="5" t="s">
+        <v>989</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>64</v>
@@ -6289,10 +6298,10 @@
         <v>803</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>989</v>
-      </c>
-      <c r="C152" s="6" t="s">
         <v>990</v>
+      </c>
+      <c r="C152" s="6">
+        <v>2</v>
       </c>
       <c r="D152" s="6" t="s">
         <v>64</v>
@@ -6306,7 +6315,7 @@
         <v>991</v>
       </c>
       <c r="C153" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D153" s="5" t="s">
         <v>64</v>
@@ -6319,8 +6328,8 @@
       <c r="B154" s="6" t="s">
         <v>992</v>
       </c>
-      <c r="C154" s="6">
-        <v>2</v>
+      <c r="C154" s="6" t="s">
+        <v>993</v>
       </c>
       <c r="D154" s="6" t="s">
         <v>64</v>
@@ -6328,13 +6337,13 @@
     </row>
     <row r="155" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C155" s="5">
-        <v>206</v>
+        <v>4</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>64</v>
@@ -6342,13 +6351,13 @@
     </row>
     <row r="156" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
-        <v>824</v>
+        <v>803</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C156" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D156" s="6" t="s">
         <v>64</v>
@@ -6356,13 +6365,13 @@
     </row>
     <row r="157" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
-        <v>824</v>
+        <v>797</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C157" s="5">
-        <v>4</v>
+        <v>206</v>
       </c>
       <c r="D157" s="5" t="s">
         <v>64</v>
@@ -6373,10 +6382,10 @@
         <v>824</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C158" s="6">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="D158" s="6" t="s">
         <v>64</v>
@@ -6387,10 +6396,10 @@
         <v>824</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>997</v>
-      </c>
-      <c r="C159" s="5" t="s">
         <v>998</v>
+      </c>
+      <c r="C159" s="5">
+        <v>4</v>
       </c>
       <c r="D159" s="5" t="s">
         <v>64</v>
@@ -6398,13 +6407,13 @@
     </row>
     <row r="160" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
-        <v>801</v>
+        <v>824</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>999</v>
       </c>
       <c r="C160" s="6">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="D160" s="6" t="s">
         <v>64</v>
@@ -6412,20 +6421,48 @@
     </row>
     <row r="161" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
-        <v>801</v>
+        <v>824</v>
       </c>
       <c r="B161" s="5" t="s">
         <v>1000</v>
       </c>
-      <c r="C161" s="5">
-        <v>1</v>
+      <c r="C161" s="5" t="s">
+        <v>1001</v>
       </c>
       <c r="D161" s="5" t="s">
         <v>64</v>
       </c>
     </row>
+    <row r="162" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="6" t="s">
+        <v>801</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C162" s="6">
+        <v>5</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C163" s="5">
+        <v>1</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:D161"/>
+  <autoFilter ref="A4:D163"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -2827,7 +2827,7 @@
     <t>PERCEPTION_INFO_TABLE</t>
   </si>
   <si>
-    <t>[{"level":0,"reconHops":1,"threat":["presence"],"extra":[]},{"level":0,"reconHops":1,"threat":["presence"],"extra":[]},{"level":1,"reconHops":2,"threat":["presence","size"],"extra":["prizeGrade"]},{"level":2,"reconHops":2,"threat":["presence","size","mode"],"extra":["prizeGrade","prizeAxis"]},{"level":3,"reconHops":2,"threat":["presence","size","mode","alert","nextMove"],"extra":["prizeGrade","prizeAxis","concealment"]},{"level":4,"reconHops":3,"threat":["presence","size","mode","alert","nextMove","composition"],"extra":["prizeGrade","prizeAxis","concealment","cameras"]},{"level":5,"reconHops":3,"threat":["presence","size","mode","alert","nextMove","composition","patrolNext"],"extra":["prizeGrade","prizeAxis","concealment","cameras","evidence"]}]</t>
+    <t>[{"level":0,"reconHops":1,"threat":["presence"],"extra":[]},{"level":0,"reconHops":1,"threat":["presence"],"extra":[]},{"level":1,"reconHops":2,"threat":["presence","size"],"extra":["prizeGrade"]},{"level":2,"reconHops":2,"threat":["presence","size","mode"],"extra":["prizeGrade","prizeAxis"]},{"level":3,"reconHops":2,"threat":["presence","size","mode","alert","nextMove"],"extra":["prizeGrade","prizeAxis","concealment"]},{"level":4,"reconHops":3,"threat":["presence","size","mode","alert","nextMove","composition"],"extra":["prizeGrade","prizeAxis","concealment"]},{"level":5,"reconHops":3,"threat":["presence","size","mode","alert","nextMove","composition","patrolNext"],"extra":["prizeGrade","prizeAxis","concealment","evidence"]}]</t>
   </si>
   <si>
     <t>PERCEPTION_WAIT_OBSERVATION_MIN</t>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -3807,7 +3807,7 @@
         <v>72</v>
       </c>
       <c r="C24" s="6">
-        <v>700</v>
+        <v>490</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>73</v>
@@ -3892,7 +3892,7 @@
         <v>87</v>
       </c>
       <c r="C29" s="5">
-        <v>430</v>
+        <v>300</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>88</v>
@@ -3909,7 +3909,7 @@
         <v>89</v>
       </c>
       <c r="C30" s="6">
-        <v>670</v>
+        <v>470</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>90</v>
@@ -4889,7 +4889,7 @@
         <v>858</v>
       </c>
       <c r="C54" s="6">
-        <v>430</v>
+        <v>300</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>67</v>
@@ -4917,7 +4917,7 @@
         <v>860</v>
       </c>
       <c r="C56" s="6">
-        <v>670</v>
+        <v>470</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>67</v>
@@ -5813,7 +5813,7 @@
         <v>943</v>
       </c>
       <c r="C120" s="6">
-        <v>700</v>
+        <v>490</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>67</v>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3118" uniqueCount="986">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3133" uniqueCount="992">
   <si>
     <t>현재 구현 규칙</t>
   </si>
@@ -1759,6 +1759,9 @@
     <t>지각 +1, 기동 -1</t>
   </si>
   <si>
+    <t>{"유형":"camera_snipe","시간 비용":4,"재사용 대기시간":15,"지속 시간":null,"범위":2,"대상 종류":"전자 장치","deviceKinds":["camera"]}</t>
+  </si>
+  <si>
     <t>방어구 스펙</t>
   </si>
   <si>
@@ -2489,6 +2492,21 @@
   </si>
   <si>
     <t>CAMERA_NODE_CHANCE</t>
+  </si>
+  <si>
+    <t>CAMERA_SNIPE_AMMO_COST</t>
+  </si>
+  <si>
+    <t>CAMERA_SNIPE_NOISE</t>
+  </si>
+  <si>
+    <t>CAMERA_SNIPE_RANGE</t>
+  </si>
+  <si>
+    <t>CAMERA_SNIPE_REQUIREMENT</t>
+  </si>
+  <si>
+    <t>CAMERA_SNIPE_TIME</t>
   </si>
   <si>
     <t>CAMERA_STEALTH_THRESHOLD</t>
@@ -4175,7 +4193,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D148"/>
+  <dimension ref="A1:D153"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -4186,7 +4204,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4194,7 +4212,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4206,10 +4224,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>6</v>
@@ -4217,10 +4235,10 @@
     </row>
     <row r="5" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C5" s="5">
         <v>0.16</v>
@@ -4231,10 +4249,10 @@
     </row>
     <row r="6" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C6" s="6">
         <v>10</v>
@@ -4245,13 +4263,13 @@
     </row>
     <row r="7" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>67</v>
@@ -4259,13 +4277,13 @@
     </row>
     <row r="8" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>67</v>
@@ -4273,10 +4291,10 @@
     </row>
     <row r="9" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C9" s="5">
         <v>1</v>
@@ -4287,13 +4305,13 @@
     </row>
     <row r="10" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>67</v>
@@ -4301,13 +4319,13 @@
     </row>
     <row r="11" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>67</v>
@@ -4315,13 +4333,13 @@
     </row>
     <row r="12" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>67</v>
@@ -4329,10 +4347,10 @@
     </row>
     <row r="13" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C13" s="5">
         <v>4</v>
@@ -4343,10 +4361,10 @@
     </row>
     <row r="14" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C14" s="6">
         <v>2</v>
@@ -4357,10 +4375,10 @@
     </row>
     <row r="15" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C15" s="5">
         <v>4</v>
@@ -4371,10 +4389,10 @@
     </row>
     <row r="16" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C16" s="6">
         <v>3</v>
@@ -4385,10 +4403,10 @@
     </row>
     <row r="17" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C17" s="5">
         <v>2</v>
@@ -4399,10 +4417,10 @@
     </row>
     <row r="18" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C18" s="6">
         <v>5</v>
@@ -4413,10 +4431,10 @@
     </row>
     <row r="19" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C19" s="5">
         <v>15</v>
@@ -4427,13 +4445,13 @@
     </row>
     <row r="20" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>67</v>
@@ -4441,10 +4459,10 @@
     </row>
     <row r="21" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C21" s="5">
         <v>5</v>
@@ -4455,10 +4473,10 @@
     </row>
     <row r="22" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C22" s="6">
         <v>0.22</v>
@@ -4469,13 +4487,13 @@
     </row>
     <row r="23" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C23" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>67</v>
@@ -4483,13 +4501,13 @@
     </row>
     <row r="24" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>824</v>
+        <v>798</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>825</v>
       </c>
       <c r="C24" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>67</v>
@@ -4497,13 +4515,13 @@
     </row>
     <row r="25" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>826</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>827</v>
+      <c r="C25" s="5">
+        <v>2</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>67</v>
@@ -4511,13 +4529,13 @@
     </row>
     <row r="26" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>828</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>829</v>
+        <v>827</v>
+      </c>
+      <c r="C26" s="6">
+        <v>2</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>67</v>
@@ -4525,13 +4543,13 @@
     </row>
     <row r="27" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>830</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>831</v>
+        <v>828</v>
+      </c>
+      <c r="C27" s="5">
+        <v>4</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>67</v>
@@ -4539,13 +4557,13 @@
     </row>
     <row r="28" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>797</v>
+        <v>817</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>832</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>833</v>
+        <v>829</v>
+      </c>
+      <c r="C28" s="6">
+        <v>3</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>67</v>
@@ -4553,13 +4571,13 @@
     </row>
     <row r="29" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>797</v>
+        <v>830</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>834</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>835</v>
+        <v>831</v>
+      </c>
+      <c r="C29" s="5">
+        <v>1</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>67</v>
@@ -4567,13 +4585,13 @@
     </row>
     <row r="30" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>67</v>
@@ -4581,13 +4599,13 @@
     </row>
     <row r="31" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>22</v>
+        <v>830</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>838</v>
-      </c>
-      <c r="C31" s="5">
-        <v>3</v>
+        <v>834</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>835</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>67</v>
@@ -4595,13 +4613,13 @@
     </row>
     <row r="32" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>22</v>
+        <v>830</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>839</v>
-      </c>
-      <c r="C32" s="6">
-        <v>3</v>
+        <v>836</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>837</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>67</v>
@@ -4609,13 +4627,13 @@
     </row>
     <row r="33" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>824</v>
+        <v>798</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>840</v>
-      </c>
-      <c r="C33" s="5">
-        <v>1</v>
+        <v>838</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>839</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>67</v>
@@ -4623,13 +4641,13 @@
     </row>
     <row r="34" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>824</v>
+        <v>798</v>
       </c>
       <c r="B34" s="6" t="s">
+        <v>840</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>841</v>
-      </c>
-      <c r="C34" s="6">
-        <v>6</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>67</v>
@@ -4637,13 +4655,13 @@
     </row>
     <row r="35" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>842</v>
       </c>
-      <c r="C35" s="5">
-        <v>9</v>
+      <c r="C35" s="5" t="s">
+        <v>843</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>67</v>
@@ -4651,13 +4669,13 @@
     </row>
     <row r="36" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>824</v>
+        <v>22</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C36" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>67</v>
@@ -4665,13 +4683,13 @@
     </row>
     <row r="37" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>824</v>
+        <v>22</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C37" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>67</v>
@@ -4679,13 +4697,13 @@
     </row>
     <row r="38" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C38" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>67</v>
@@ -4693,13 +4711,13 @@
     </row>
     <row r="39" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C39" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>67</v>
@@ -4707,13 +4725,13 @@
     </row>
     <row r="40" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C40" s="6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>67</v>
@@ -4721,13 +4739,13 @@
     </row>
     <row r="41" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>795</v>
+        <v>830</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C41" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>67</v>
@@ -4735,10 +4753,10 @@
     </row>
     <row r="42" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>795</v>
+        <v>830</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C42" s="6">
         <v>2</v>
@@ -4749,13 +4767,13 @@
     </row>
     <row r="43" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>795</v>
+        <v>830</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>850</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>293</v>
+        <v>851</v>
+      </c>
+      <c r="C43" s="5">
+        <v>5</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>67</v>
@@ -4763,13 +4781,13 @@
     </row>
     <row r="44" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>797</v>
+        <v>830</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C44" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>67</v>
@@ -4777,13 +4795,13 @@
     </row>
     <row r="45" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>795</v>
+        <v>830</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C45" s="5">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>67</v>
@@ -4791,13 +4809,13 @@
     </row>
     <row r="46" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C46" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>67</v>
@@ -4805,13 +4823,13 @@
     </row>
     <row r="47" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C47" s="5">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>67</v>
@@ -4819,13 +4837,13 @@
     </row>
     <row r="48" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>824</v>
+        <v>796</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>855</v>
-      </c>
-      <c r="C48" s="6">
-        <v>2</v>
+        <v>856</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>293</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>67</v>
@@ -4833,13 +4851,13 @@
     </row>
     <row r="49" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>824</v>
+        <v>798</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>856</v>
-      </c>
-      <c r="C49" s="5" t="s">
         <v>857</v>
+      </c>
+      <c r="C49" s="5">
+        <v>2</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>67</v>
@@ -4847,13 +4865,13 @@
     </row>
     <row r="50" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>858</v>
       </c>
       <c r="C50" s="6">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>67</v>
@@ -4861,7 +4879,7 @@
     </row>
     <row r="51" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>859</v>
@@ -4875,13 +4893,13 @@
     </row>
     <row r="52" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>860</v>
       </c>
       <c r="C52" s="6">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>67</v>
@@ -4889,13 +4907,13 @@
     </row>
     <row r="53" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>861</v>
       </c>
-      <c r="C53" s="5" t="s">
-        <v>333</v>
+      <c r="C53" s="5">
+        <v>2</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>67</v>
@@ -4903,13 +4921,13 @@
     </row>
     <row r="54" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>86</v>
+        <v>830</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>862</v>
       </c>
-      <c r="C54" s="6">
-        <v>300</v>
+      <c r="C54" s="6" t="s">
+        <v>863</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>67</v>
@@ -4917,13 +4935,13 @@
     </row>
     <row r="55" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>86</v>
+        <v>804</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>863</v>
-      </c>
-      <c r="C55" s="5" t="s">
         <v>864</v>
+      </c>
+      <c r="C55" s="5">
+        <v>1</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>67</v>
@@ -4931,13 +4949,13 @@
     </row>
     <row r="56" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>86</v>
+        <v>798</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>865</v>
       </c>
       <c r="C56" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>67</v>
@@ -4945,13 +4963,13 @@
     </row>
     <row r="57" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>86</v>
+        <v>798</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>866</v>
       </c>
       <c r="C57" s="5">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>67</v>
@@ -4959,13 +4977,13 @@
     </row>
     <row r="58" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>86</v>
+        <v>830</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>867</v>
       </c>
-      <c r="C58" s="6">
-        <v>3</v>
+      <c r="C58" s="6" t="s">
+        <v>333</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>67</v>
@@ -4973,13 +4991,13 @@
     </row>
     <row r="59" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>797</v>
+        <v>86</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>868</v>
       </c>
       <c r="C59" s="5">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>67</v>
@@ -4987,7 +5005,7 @@
     </row>
     <row r="60" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>797</v>
+        <v>86</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>869</v>
@@ -5001,13 +5019,13 @@
     </row>
     <row r="61" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>797</v>
+        <v>86</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>871</v>
       </c>
       <c r="C61" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>67</v>
@@ -5015,13 +5033,13 @@
     </row>
     <row r="62" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>797</v>
+        <v>86</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>872</v>
       </c>
       <c r="C62" s="6">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>67</v>
@@ -5029,13 +5047,13 @@
     </row>
     <row r="63" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>797</v>
+        <v>86</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>873</v>
       </c>
       <c r="C63" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>67</v>
@@ -5043,13 +5061,13 @@
     </row>
     <row r="64" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>874</v>
       </c>
       <c r="C64" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>67</v>
@@ -5057,13 +5075,13 @@
     </row>
     <row r="65" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>824</v>
+        <v>798</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>875</v>
       </c>
-      <c r="C65" s="5">
-        <v>256</v>
+      <c r="C65" s="5" t="s">
+        <v>876</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>67</v>
@@ -5071,13 +5089,13 @@
     </row>
     <row r="66" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C66" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>67</v>
@@ -5085,13 +5103,13 @@
     </row>
     <row r="67" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>824</v>
+        <v>798</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>877</v>
-      </c>
-      <c r="C67" s="5" t="s">
         <v>878</v>
+      </c>
+      <c r="C67" s="5">
+        <v>3</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>67</v>
@@ -5099,7 +5117,7 @@
     </row>
     <row r="68" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>824</v>
+        <v>798</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>879</v>
@@ -5113,13 +5131,13 @@
     </row>
     <row r="69" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>824</v>
+        <v>798</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>880</v>
       </c>
       <c r="C69" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>67</v>
@@ -5127,13 +5145,13 @@
     </row>
     <row r="70" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>797</v>
+        <v>830</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>881</v>
       </c>
       <c r="C70" s="6">
-        <v>2</v>
+        <v>256</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>67</v>
@@ -5141,13 +5159,13 @@
     </row>
     <row r="71" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>882</v>
       </c>
       <c r="C71" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>67</v>
@@ -5155,13 +5173,13 @@
     </row>
     <row r="72" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>883</v>
       </c>
-      <c r="C72" s="6">
-        <v>1</v>
+      <c r="C72" s="6" t="s">
+        <v>884</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>67</v>
@@ -5169,13 +5187,13 @@
     </row>
     <row r="73" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>795</v>
+        <v>830</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C73" s="5">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>67</v>
@@ -5183,13 +5201,13 @@
     </row>
     <row r="74" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>816</v>
+        <v>830</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C74" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>67</v>
@@ -5197,10 +5215,10 @@
     </row>
     <row r="75" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C75" s="5">
         <v>2</v>
@@ -5211,10 +5229,10 @@
     </row>
     <row r="76" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>816</v>
+        <v>804</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C76" s="6">
         <v>5</v>
@@ -5225,13 +5243,13 @@
     </row>
     <row r="77" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>816</v>
+        <v>830</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C77" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>67</v>
@@ -5239,13 +5257,13 @@
     </row>
     <row r="78" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>889</v>
-      </c>
-      <c r="C78" s="6" t="s">
         <v>890</v>
+      </c>
+      <c r="C78" s="6">
+        <v>64</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>67</v>
@@ -5253,13 +5271,13 @@
     </row>
     <row r="79" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>797</v>
+        <v>817</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>891</v>
       </c>
       <c r="C79" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>67</v>
@@ -5267,13 +5285,13 @@
     </row>
     <row r="80" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>892</v>
       </c>
       <c r="C80" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>67</v>
@@ -5281,13 +5299,13 @@
     </row>
     <row r="81" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>893</v>
       </c>
       <c r="C81" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>67</v>
@@ -5295,13 +5313,13 @@
     </row>
     <row r="82" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>803</v>
+        <v>817</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>894</v>
       </c>
       <c r="C82" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>67</v>
@@ -5309,13 +5327,13 @@
     </row>
     <row r="83" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>824</v>
+        <v>796</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>895</v>
       </c>
-      <c r="C83" s="5">
-        <v>8</v>
+      <c r="C83" s="5" t="s">
+        <v>896</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>67</v>
@@ -5323,13 +5341,13 @@
     </row>
     <row r="84" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C84" s="6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>67</v>
@@ -5337,13 +5355,13 @@
     </row>
     <row r="85" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>897</v>
+        <v>804</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>898</v>
       </c>
       <c r="C85" s="5">
-        <v>0.01</v>
+        <v>4</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>67</v>
@@ -5351,13 +5369,13 @@
     </row>
     <row r="86" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>897</v>
+        <v>830</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>899</v>
       </c>
       <c r="C86" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>67</v>
@@ -5365,13 +5383,13 @@
     </row>
     <row r="87" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>897</v>
+        <v>804</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>900</v>
       </c>
       <c r="C87" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>67</v>
@@ -5379,13 +5397,13 @@
     </row>
     <row r="88" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>795</v>
+        <v>830</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>901</v>
       </c>
-      <c r="C88" s="6" t="s">
-        <v>902</v>
+      <c r="C88" s="6">
+        <v>8</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>67</v>
@@ -5393,13 +5411,13 @@
     </row>
     <row r="89" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>903</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>904</v>
+        <v>902</v>
+      </c>
+      <c r="C89" s="5">
+        <v>15</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>67</v>
@@ -5407,13 +5425,13 @@
     </row>
     <row r="90" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>797</v>
+        <v>903</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>905</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>906</v>
+        <v>904</v>
+      </c>
+      <c r="C90" s="6">
+        <v>0.01</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>67</v>
@@ -5421,13 +5439,13 @@
     </row>
     <row r="91" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>795</v>
+        <v>903</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C91" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>67</v>
@@ -5435,10 +5453,10 @@
     </row>
     <row r="92" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>795</v>
+        <v>903</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C92" s="6">
         <v>2</v>
@@ -5449,13 +5467,13 @@
     </row>
     <row r="93" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>67</v>
@@ -5463,13 +5481,13 @@
     </row>
     <row r="94" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>824</v>
+        <v>798</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>911</v>
-      </c>
-      <c r="C94" s="6">
-        <v>2</v>
+        <v>909</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>910</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>67</v>
@@ -5477,13 +5495,13 @@
     </row>
     <row r="95" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="B95" s="5" t="s">
+        <v>911</v>
+      </c>
+      <c r="C95" s="5" t="s">
         <v>912</v>
-      </c>
-      <c r="C95" s="5">
-        <v>0.17</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>67</v>
@@ -5491,13 +5509,13 @@
     </row>
     <row r="96" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>913</v>
       </c>
       <c r="C96" s="6">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>67</v>
@@ -5505,13 +5523,13 @@
     </row>
     <row r="97" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>914</v>
       </c>
-      <c r="C97" s="5" t="s">
-        <v>915</v>
+      <c r="C97" s="5">
+        <v>2</v>
       </c>
       <c r="D97" s="5" t="s">
         <v>67</v>
@@ -5519,13 +5537,13 @@
     </row>
     <row r="98" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>795</v>
+        <v>804</v>
       </c>
       <c r="B98" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="C98" s="6" t="s">
         <v>916</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>917</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>67</v>
@@ -5533,13 +5551,13 @@
     </row>
     <row r="99" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>797</v>
+        <v>830</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="C99" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>67</v>
@@ -5547,13 +5565,13 @@
     </row>
     <row r="100" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>919</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>920</v>
+        <v>918</v>
+      </c>
+      <c r="C100" s="6">
+        <v>0.17</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>67</v>
@@ -5561,13 +5579,13 @@
     </row>
     <row r="101" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>897</v>
+        <v>796</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>921</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>922</v>
+        <v>919</v>
+      </c>
+      <c r="C101" s="5">
+        <v>24</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>67</v>
@@ -5575,13 +5593,13 @@
     </row>
     <row r="102" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>824</v>
+        <v>796</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>67</v>
@@ -5589,13 +5607,13 @@
     </row>
     <row r="103" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>925</v>
-      </c>
-      <c r="C103" s="5">
-        <v>2</v>
+        <v>922</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>923</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>67</v>
@@ -5603,13 +5621,13 @@
     </row>
     <row r="104" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>824</v>
+        <v>798</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C104" s="6">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>67</v>
@@ -5617,13 +5635,13 @@
     </row>
     <row r="105" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>927</v>
-      </c>
-      <c r="C105" s="5">
-        <v>3</v>
+        <v>925</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>926</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>67</v>
@@ -5631,13 +5649,13 @@
     </row>
     <row r="106" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>824</v>
+        <v>903</v>
       </c>
       <c r="B106" s="6" t="s">
+        <v>927</v>
+      </c>
+      <c r="C106" s="6" t="s">
         <v>928</v>
-      </c>
-      <c r="C106" s="6">
-        <v>6</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>67</v>
@@ -5645,7 +5663,7 @@
     </row>
     <row r="107" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>929</v>
@@ -5659,13 +5677,13 @@
     </row>
     <row r="108" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>931</v>
       </c>
-      <c r="C108" s="6" t="s">
-        <v>932</v>
+      <c r="C108" s="6">
+        <v>2</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>67</v>
@@ -5673,13 +5691,13 @@
     </row>
     <row r="109" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>803</v>
+        <v>830</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>933</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>934</v>
+        <v>932</v>
+      </c>
+      <c r="C109" s="5">
+        <v>30</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>67</v>
@@ -5687,10 +5705,10 @@
     </row>
     <row r="110" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
-        <v>824</v>
+        <v>798</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C110" s="6">
         <v>3</v>
@@ -5701,13 +5719,13 @@
     </row>
     <row r="111" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>795</v>
+        <v>830</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>936</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>937</v>
+        <v>934</v>
+      </c>
+      <c r="C111" s="5">
+        <v>6</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>67</v>
@@ -5715,13 +5733,13 @@
     </row>
     <row r="112" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>67</v>
@@ -5729,13 +5747,13 @@
     </row>
     <row r="113" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>940</v>
-      </c>
-      <c r="C113" s="5">
-        <v>2</v>
+        <v>937</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>938</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>67</v>
@@ -5743,13 +5761,13 @@
     </row>
     <row r="114" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
-        <v>824</v>
+        <v>804</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>941</v>
-      </c>
-      <c r="C114" s="6">
-        <v>6</v>
+        <v>939</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>940</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>67</v>
@@ -5757,13 +5775,13 @@
     </row>
     <row r="115" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>803</v>
+        <v>830</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C115" s="5">
-        <v>180</v>
+        <v>3</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>67</v>
@@ -5771,13 +5789,13 @@
     </row>
     <row r="116" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="B116" s="6" t="s">
+        <v>942</v>
+      </c>
+      <c r="C116" s="6" t="s">
         <v>943</v>
-      </c>
-      <c r="C116" s="6">
-        <v>90</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>67</v>
@@ -5785,13 +5803,13 @@
     </row>
     <row r="117" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>86</v>
+        <v>830</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>944</v>
       </c>
-      <c r="C117" s="5">
-        <v>490</v>
+      <c r="C117" s="5" t="s">
+        <v>945</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>67</v>
@@ -5799,13 +5817,13 @@
     </row>
     <row r="118" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C118" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>67</v>
@@ -5813,13 +5831,13 @@
     </row>
     <row r="119" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>797</v>
+        <v>830</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>946</v>
-      </c>
-      <c r="C119" s="5" t="s">
         <v>947</v>
+      </c>
+      <c r="C119" s="5">
+        <v>6</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>67</v>
@@ -5827,13 +5845,13 @@
     </row>
     <row r="120" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>948</v>
       </c>
-      <c r="C120" s="6" t="s">
-        <v>949</v>
+      <c r="C120" s="6">
+        <v>180</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>67</v>
@@ -5841,13 +5859,13 @@
     </row>
     <row r="121" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>795</v>
+        <v>804</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>950</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>951</v>
+        <v>949</v>
+      </c>
+      <c r="C121" s="5">
+        <v>90</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>67</v>
@@ -5855,13 +5873,13 @@
     </row>
     <row r="122" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
-        <v>795</v>
+        <v>86</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>952</v>
-      </c>
-      <c r="C122" s="6" t="s">
-        <v>953</v>
+        <v>950</v>
+      </c>
+      <c r="C122" s="6">
+        <v>490</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>67</v>
@@ -5869,13 +5887,13 @@
     </row>
     <row r="123" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="C123" s="5">
-        <v>280</v>
+        <v>4</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>67</v>
@@ -5883,13 +5901,13 @@
     </row>
     <row r="124" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>955</v>
-      </c>
-      <c r="C124" s="6">
-        <v>900</v>
+        <v>952</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>953</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>67</v>
@@ -5897,13 +5915,13 @@
     </row>
     <row r="125" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>67</v>
@@ -5911,13 +5929,13 @@
     </row>
     <row r="126" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>958</v>
-      </c>
-      <c r="C126" s="6">
-        <v>0.4</v>
+        <v>956</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>957</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>67</v>
@@ -5925,13 +5943,13 @@
     </row>
     <row r="127" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B127" s="5" t="s">
+        <v>958</v>
+      </c>
+      <c r="C127" s="5" t="s">
         <v>959</v>
-      </c>
-      <c r="C127" s="5">
-        <v>6</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>67</v>
@@ -5939,13 +5957,13 @@
     </row>
     <row r="128" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>960</v>
       </c>
       <c r="C128" s="6">
-        <v>4</v>
+        <v>280</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>67</v>
@@ -5953,13 +5971,13 @@
     </row>
     <row r="129" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>961</v>
       </c>
       <c r="C129" s="5">
-        <v>5</v>
+        <v>900</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>67</v>
@@ -5967,7 +5985,7 @@
     </row>
     <row r="130" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>962</v>
@@ -5981,13 +5999,13 @@
     </row>
     <row r="131" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
-        <v>816</v>
+        <v>796</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>964</v>
       </c>
       <c r="C131" s="5">
-        <v>-1</v>
+        <v>0.4</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>67</v>
@@ -5995,13 +6013,13 @@
     </row>
     <row r="132" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
-        <v>824</v>
+        <v>796</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>965</v>
       </c>
       <c r="C132" s="6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>67</v>
@@ -6009,13 +6027,13 @@
     </row>
     <row r="133" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>824</v>
+        <v>796</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>966</v>
       </c>
       <c r="C133" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>67</v>
@@ -6023,13 +6041,13 @@
     </row>
     <row r="134" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>967</v>
       </c>
       <c r="C134" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>67</v>
@@ -6037,13 +6055,13 @@
     </row>
     <row r="135" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>968</v>
       </c>
-      <c r="C135" s="5">
-        <v>5</v>
+      <c r="C135" s="5" t="s">
+        <v>969</v>
       </c>
       <c r="D135" s="5" t="s">
         <v>67</v>
@@ -6051,13 +6069,13 @@
     </row>
     <row r="136" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
-        <v>797</v>
+        <v>817</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>969</v>
-      </c>
-      <c r="C136" s="6" t="s">
         <v>970</v>
+      </c>
+      <c r="C136" s="6">
+        <v>-1</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>67</v>
@@ -6065,13 +6083,13 @@
     </row>
     <row r="137" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>797</v>
+        <v>830</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>971</v>
       </c>
-      <c r="C137" s="5" t="s">
-        <v>972</v>
+      <c r="C137" s="5">
+        <v>-1</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>67</v>
@@ -6079,13 +6097,13 @@
     </row>
     <row r="138" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
-        <v>797</v>
+        <v>830</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C138" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>67</v>
@@ -6093,13 +6111,13 @@
     </row>
     <row r="139" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C139" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>67</v>
@@ -6107,13 +6125,13 @@
     </row>
     <row r="140" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>975</v>
-      </c>
-      <c r="C140" s="6" t="s">
-        <v>976</v>
+        <v>974</v>
+      </c>
+      <c r="C140" s="6">
+        <v>5</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>67</v>
@@ -6121,13 +6139,13 @@
     </row>
     <row r="141" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>977</v>
-      </c>
-      <c r="C141" s="5">
-        <v>4</v>
+        <v>975</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>976</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>67</v>
@@ -6135,13 +6153,13 @@
     </row>
     <row r="142" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B142" s="6" t="s">
+        <v>977</v>
+      </c>
+      <c r="C142" s="6" t="s">
         <v>978</v>
-      </c>
-      <c r="C142" s="6">
-        <v>2</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>67</v>
@@ -6149,13 +6167,13 @@
     </row>
     <row r="143" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
-        <v>824</v>
+        <v>798</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>979</v>
       </c>
       <c r="C143" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>67</v>
@@ -6163,13 +6181,13 @@
     </row>
     <row r="144" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
-        <v>824</v>
+        <v>798</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>980</v>
       </c>
       <c r="C144" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>67</v>
@@ -6177,13 +6195,13 @@
     </row>
     <row r="145" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
-        <v>824</v>
+        <v>798</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>981</v>
       </c>
-      <c r="C145" s="5">
-        <v>2.6</v>
+      <c r="C145" s="5" t="s">
+        <v>982</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>67</v>
@@ -6191,13 +6209,13 @@
     </row>
     <row r="146" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
-        <v>824</v>
+        <v>798</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>982</v>
-      </c>
-      <c r="C146" s="6" t="s">
         <v>983</v>
+      </c>
+      <c r="C146" s="6">
+        <v>4</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>67</v>
@@ -6205,13 +6223,13 @@
     </row>
     <row r="147" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>984</v>
       </c>
       <c r="C147" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>67</v>
@@ -6219,20 +6237,90 @@
     </row>
     <row r="148" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
-        <v>803</v>
+        <v>830</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>985</v>
       </c>
       <c r="C148" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>67</v>
       </c>
     </row>
+    <row r="149" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>986</v>
+      </c>
+      <c r="C149" s="5">
+        <v>4</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>987</v>
+      </c>
+      <c r="C150" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>988</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>989</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="6" t="s">
+        <v>804</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>990</v>
+      </c>
+      <c r="C152" s="6">
+        <v>5</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>991</v>
+      </c>
+      <c r="C153" s="5">
+        <v>1</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:D148"/>
+  <autoFilter ref="A4:D153"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -11123,13 +11211,13 @@
         <v>578</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>333</v>
+        <v>579</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>333</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>22</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -11164,7 +11252,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11225,10 +11313,10 @@
     </row>
     <row r="5" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>189</v>
@@ -11240,7 +11328,7 @@
         <v>333</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>571</v>
@@ -11257,10 +11345,10 @@
     </row>
     <row r="6" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>189</v>
@@ -11272,10 +11360,10 @@
         <v>333</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>333</v>
@@ -11289,10 +11377,10 @@
     </row>
     <row r="7" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>303</v>
@@ -11304,10 +11392,10 @@
         <v>333</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>333</v>
@@ -11321,10 +11409,10 @@
     </row>
     <row r="8" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>303</v>
@@ -11336,10 +11424,10 @@
         <v>333</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>333</v>
@@ -11383,7 +11471,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11397,7 +11485,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11444,7 +11532,7 @@
     </row>
     <row r="5" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>220</v>
@@ -11459,7 +11547,7 @@
         <v>333</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>333</v>
@@ -11476,7 +11564,7 @@
     </row>
     <row r="6" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>222</v>
@@ -11491,10 +11579,10 @@
         <v>333</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>333</v>
@@ -11508,10 +11596,10 @@
     </row>
     <row r="7" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>165</v>
@@ -11523,13 +11611,13 @@
         <v>333</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>333</v>
@@ -11540,7 +11628,7 @@
     </row>
     <row r="8" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>139</v>
@@ -11555,13 +11643,13 @@
         <v>333</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>333</v>
@@ -11572,10 +11660,10 @@
     </row>
     <row r="9" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>165</v>
@@ -11587,13 +11675,13 @@
         <v>333</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>333</v>
@@ -11604,7 +11692,7 @@
     </row>
     <row r="10" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>185</v>
@@ -11619,10 +11707,10 @@
         <v>333</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>333</v>
@@ -11636,10 +11724,10 @@
     </row>
     <row r="11" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>165</v>
@@ -11651,10 +11739,10 @@
         <v>333</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>333</v>
@@ -11696,7 +11784,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11708,7 +11796,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11721,13 +11809,13 @@
     <row r="3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>316</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>330</v>
@@ -11747,16 +11835,16 @@
     </row>
     <row r="5" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>333</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>333</v>
@@ -11773,19 +11861,19 @@
     </row>
     <row r="6" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>333</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>333</v>
@@ -11799,16 +11887,16 @@
     </row>
     <row r="7" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>333</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>333</v>
@@ -11825,19 +11913,19 @@
     </row>
     <row r="8" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>333</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>333</v>
@@ -11851,16 +11939,16 @@
     </row>
     <row r="9" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>333</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>333</v>
@@ -11877,16 +11965,16 @@
     </row>
     <row r="10" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>333</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>333</v>
@@ -11932,7 +12020,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11946,7 +12034,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11961,42 +12049,42 @@
     <row r="3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>316</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>244</v>
@@ -12025,10 +12113,10 @@
     </row>
     <row r="6" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>244</v>
@@ -12057,10 +12145,10 @@
     </row>
     <row r="7" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>244</v>
@@ -12089,10 +12177,10 @@
     </row>
     <row r="8" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>244</v>
@@ -12121,10 +12209,10 @@
     </row>
     <row r="9" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>244</v>
@@ -12153,10 +12241,10 @@
     </row>
     <row r="10" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>244</v>
@@ -12185,10 +12273,10 @@
     </row>
     <row r="11" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>244</v>
@@ -12217,10 +12305,10 @@
     </row>
     <row r="12" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>244</v>
@@ -12249,10 +12337,10 @@
     </row>
     <row r="13" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>244</v>
@@ -12267,7 +12355,7 @@
         <v>333</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>333</v>
@@ -12281,10 +12369,10 @@
     </row>
     <row r="14" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>244</v>
@@ -12313,10 +12401,10 @@
     </row>
     <row r="15" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>244</v>
@@ -12345,10 +12433,10 @@
     </row>
     <row r="16" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>244</v>
@@ -12377,10 +12465,10 @@
     </row>
     <row r="17" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>244</v>
@@ -12409,10 +12497,10 @@
     </row>
     <row r="18" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>268</v>
@@ -12441,10 +12529,10 @@
     </row>
     <row r="19" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>268</v>
@@ -12473,10 +12561,10 @@
     </row>
     <row r="20" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>268</v>
@@ -12505,10 +12593,10 @@
     </row>
     <row r="21" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>183</v>
@@ -12537,10 +12625,10 @@
     </row>
     <row r="22" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>183</v>
@@ -12569,10 +12657,10 @@
     </row>
     <row r="23" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>183</v>
@@ -12601,10 +12689,10 @@
     </row>
     <row r="24" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>183</v>
@@ -12633,13 +12721,13 @@
     </row>
     <row r="25" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D25" s="7">
         <v>6</v>
@@ -12699,7 +12787,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -12720,7 +12808,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -12742,25 +12830,25 @@
     <row r="3" ht="8" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" ht="24" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>299</v>
@@ -12772,7 +12860,7 @@
         <v>201</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>187</v>
@@ -12795,10 +12883,10 @@
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>244</v>
@@ -12813,7 +12901,7 @@
         <v>333</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H5" s="7">
         <v>12</v>
@@ -12848,10 +12936,10 @@
     </row>
     <row r="6" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>244</v>
@@ -12866,7 +12954,7 @@
         <v>333</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H6" s="8">
         <v>6</v>
@@ -12878,7 +12966,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>333</v>
@@ -12901,10 +12989,10 @@
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>244</v>
@@ -12919,7 +13007,7 @@
         <v>333</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H7" s="7">
         <v>0</v>
@@ -12931,7 +13019,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>333</v>
@@ -12954,10 +13042,10 @@
     </row>
     <row r="8" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>244</v>
@@ -12972,7 +13060,7 @@
         <v>333</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H8" s="8">
         <v>0</v>
@@ -12984,7 +13072,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>333</v>
@@ -13007,10 +13095,10 @@
     </row>
     <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>244</v>
@@ -13025,7 +13113,7 @@
         <v>333</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H9" s="7">
         <v>7</v>
@@ -13060,10 +13148,10 @@
     </row>
     <row r="10" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>244</v>
@@ -13078,7 +13166,7 @@
         <v>333</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H10" s="8">
         <v>13</v>
@@ -13113,10 +13201,10 @@
     </row>
     <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>244</v>
@@ -13131,7 +13219,7 @@
         <v>333</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H11" s="7">
         <v>3</v>
@@ -13166,10 +13254,10 @@
     </row>
     <row r="12" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>244</v>
@@ -13184,7 +13272,7 @@
         <v>50</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H12" s="8">
         <v>10</v>
@@ -13219,10 +13307,10 @@
     </row>
     <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>244</v>
@@ -13237,7 +13325,7 @@
         <v>50</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H13" s="7">
         <v>2</v>
@@ -13272,10 +13360,10 @@
     </row>
     <row r="14" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>244</v>
@@ -13290,7 +13378,7 @@
         <v>333</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H14" s="8">
         <v>6</v>
@@ -13325,10 +13413,10 @@
     </row>
     <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>244</v>
@@ -13343,7 +13431,7 @@
         <v>333</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H15" s="7">
         <v>8</v>
@@ -13355,7 +13443,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>333</v>
@@ -13378,10 +13466,10 @@
     </row>
     <row r="16" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>244</v>
@@ -13396,7 +13484,7 @@
         <v>333</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H16" s="8">
         <v>16</v>
@@ -13431,10 +13519,10 @@
     </row>
     <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>244</v>
@@ -13449,7 +13537,7 @@
         <v>333</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H17" s="7">
         <v>4</v>
@@ -13484,10 +13572,10 @@
     </row>
     <row r="18" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>244</v>
@@ -13502,7 +13590,7 @@
         <v>33</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H18" s="8">
         <v>14</v>
@@ -13537,10 +13625,10 @@
     </row>
     <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>244</v>
@@ -13555,7 +13643,7 @@
         <v>33</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H19" s="7">
         <v>0</v>
@@ -13567,7 +13655,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="L19" s="5" t="s">
         <v>333</v>
@@ -13590,10 +13678,10 @@
     </row>
     <row r="20" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>244</v>
@@ -13608,7 +13696,7 @@
         <v>34</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H20" s="8">
         <v>4</v>
@@ -13643,10 +13731,10 @@
     </row>
     <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>244</v>
@@ -13661,7 +13749,7 @@
         <v>333</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H21" s="7">
         <v>0</v>
@@ -13682,7 +13770,7 @@
         <v>333</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="O21" s="5" t="s">
         <v>224</v>
@@ -13696,10 +13784,10 @@
     </row>
     <row r="22" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>244</v>
@@ -13714,7 +13802,7 @@
         <v>40</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H22" s="8">
         <v>8</v>
@@ -13726,7 +13814,7 @@
         <v>1</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>333</v>
@@ -13749,10 +13837,10 @@
     </row>
     <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>244</v>
@@ -13767,7 +13855,7 @@
         <v>60</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H23" s="7">
         <v>14</v>
@@ -13802,10 +13890,10 @@
     </row>
     <row r="24" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>244</v>
@@ -13820,7 +13908,7 @@
         <v>333</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H24" s="8">
         <v>3</v>
@@ -13832,7 +13920,7 @@
         <v>2</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L24" s="6" t="s">
         <v>333</v>
@@ -13855,10 +13943,10 @@
     </row>
     <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>244</v>
@@ -13873,7 +13961,7 @@
         <v>333</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H25" s="7">
         <v>0</v>
@@ -13885,7 +13973,7 @@
         <v>1</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="L25" s="5" t="s">
         <v>333</v>
@@ -13908,10 +13996,10 @@
     </row>
     <row r="26" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>244</v>
@@ -13926,7 +14014,7 @@
         <v>50</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H26" s="8">
         <v>7</v>
@@ -13938,7 +14026,7 @@
         <v>1</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L26" s="6" t="s">
         <v>333</v>
@@ -13961,10 +14049,10 @@
     </row>
     <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>244</v>
@@ -13979,7 +14067,7 @@
         <v>50</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H27" s="7">
         <v>12</v>
@@ -14014,10 +14102,10 @@
     </row>
     <row r="28" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>244</v>
@@ -14032,7 +14120,7 @@
         <v>333</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H28" s="8">
         <v>0</v>
@@ -14044,7 +14132,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L28" s="6" t="s">
         <v>333</v>
@@ -14067,10 +14155,10 @@
     </row>
     <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>244</v>
@@ -14085,7 +14173,7 @@
         <v>333</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H29" s="7">
         <v>7</v>
@@ -14097,7 +14185,7 @@
         <v>2</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>333</v>
@@ -14120,10 +14208,10 @@
     </row>
     <row r="30" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>244</v>
@@ -14138,7 +14226,7 @@
         <v>333</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H30" s="8">
         <v>7</v>
@@ -14150,7 +14238,7 @@
         <v>2</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L30" s="6" t="s">
         <v>333</v>
@@ -14173,10 +14261,10 @@
     </row>
     <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>244</v>
@@ -14191,7 +14279,7 @@
         <v>333</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H31" s="7">
         <v>5</v>
@@ -14226,10 +14314,10 @@
     </row>
     <row r="32" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>244</v>
@@ -14244,7 +14332,7 @@
         <v>50</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H32" s="8">
         <v>8</v>
@@ -14256,7 +14344,7 @@
         <v>1</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="L32" s="6" t="s">
         <v>333</v>
@@ -14279,10 +14367,10 @@
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>244</v>
@@ -14297,7 +14385,7 @@
         <v>50</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H33" s="7">
         <v>11</v>
@@ -14332,10 +14420,10 @@
     </row>
     <row r="34" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>244</v>
@@ -14350,7 +14438,7 @@
         <v>333</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H34" s="8">
         <v>0</v>
@@ -14362,7 +14450,7 @@
         <v>1</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="L34" s="6" t="s">
         <v>333</v>
@@ -14385,10 +14473,10 @@
     </row>
     <row r="35" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>244</v>
@@ -14403,7 +14491,7 @@
         <v>333</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H35" s="7">
         <v>4</v>
@@ -14438,10 +14526,10 @@
     </row>
     <row r="36" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>244</v>
@@ -14456,7 +14544,7 @@
         <v>333</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H36" s="8">
         <v>0</v>
@@ -14468,7 +14556,7 @@
         <v>0</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="L36" s="6" t="s">
         <v>333</v>
@@ -14491,10 +14579,10 @@
     </row>
     <row r="37" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>244</v>
@@ -14509,7 +14597,7 @@
         <v>333</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H37" s="7">
         <v>4</v>
@@ -14544,10 +14632,10 @@
     </row>
     <row r="38" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>244</v>
@@ -14562,7 +14650,7 @@
         <v>333</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H38" s="8">
         <v>0</v>
@@ -14577,7 +14665,7 @@
         <v>440</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M38" s="8" t="s">
         <v>333</v>
@@ -14597,10 +14685,10 @@
     </row>
     <row r="39" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>244</v>
@@ -14615,7 +14703,7 @@
         <v>333</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H39" s="7">
         <v>8</v>
@@ -14650,10 +14738,10 @@
     </row>
     <row r="40" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>244</v>
@@ -14668,7 +14756,7 @@
         <v>333</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H40" s="8">
         <v>0</v>
@@ -14683,7 +14771,7 @@
         <v>440</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M40" s="8" t="s">
         <v>333</v>
@@ -14703,10 +14791,10 @@
     </row>
     <row r="41" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>244</v>
@@ -14721,7 +14809,7 @@
         <v>50</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H41" s="7">
         <v>11</v>
@@ -14756,10 +14844,10 @@
     </row>
     <row r="42" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>244</v>
@@ -14774,7 +14862,7 @@
         <v>50</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H42" s="8">
         <v>0</v>
@@ -14789,7 +14877,7 @@
         <v>440</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M42" s="8" t="s">
         <v>333</v>
@@ -14809,10 +14897,10 @@
     </row>
     <row r="43" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>268</v>
@@ -14827,7 +14915,7 @@
         <v>333</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H43" s="7">
         <v>0</v>
@@ -14862,10 +14950,10 @@
     </row>
     <row r="44" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>268</v>
@@ -14880,7 +14968,7 @@
         <v>333</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H44" s="8">
         <v>0</v>
@@ -14892,7 +14980,7 @@
         <v>0</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="L44" s="6" t="s">
         <v>333</v>
@@ -14915,10 +15003,10 @@
     </row>
     <row r="45" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>268</v>
@@ -14933,7 +15021,7 @@
         <v>333</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H45" s="7">
         <v>13</v>
@@ -14968,10 +15056,10 @@
     </row>
     <row r="46" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>268</v>
@@ -14986,7 +15074,7 @@
         <v>333</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H46" s="8">
         <v>0</v>
@@ -15021,10 +15109,10 @@
     </row>
     <row r="47" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>268</v>
@@ -15039,7 +15127,7 @@
         <v>333</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H47" s="7">
         <v>13</v>
@@ -15074,10 +15162,10 @@
     </row>
     <row r="48" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>268</v>
@@ -15092,7 +15180,7 @@
         <v>333</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H48" s="8">
         <v>17</v>
@@ -15127,10 +15215,10 @@
     </row>
     <row r="49" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>268</v>
@@ -15145,7 +15233,7 @@
         <v>333</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H49" s="7">
         <v>3</v>
@@ -15180,10 +15268,10 @@
     </row>
     <row r="50" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>268</v>
@@ -15198,7 +15286,7 @@
         <v>333</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H50" s="8">
         <v>0</v>
@@ -15213,7 +15301,7 @@
         <v>440</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="M50" s="8" t="s">
         <v>333</v>
@@ -15233,10 +15321,10 @@
     </row>
     <row r="51" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>268</v>
@@ -15251,7 +15339,7 @@
         <v>333</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H51" s="7">
         <v>4</v>
@@ -15286,10 +15374,10 @@
     </row>
     <row r="52" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>183</v>
@@ -15304,7 +15392,7 @@
         <v>333</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H52" s="8">
         <v>0</v>
@@ -15316,7 +15404,7 @@
         <v>1</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="L52" s="6" t="s">
         <v>333</v>
@@ -15339,10 +15427,10 @@
     </row>
     <row r="53" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>183</v>
@@ -15357,7 +15445,7 @@
         <v>333</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H53" s="7">
         <v>18</v>
@@ -15369,7 +15457,7 @@
         <v>1</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L53" s="5" t="s">
         <v>333</v>
@@ -15392,10 +15480,10 @@
     </row>
     <row r="54" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>183</v>
@@ -15410,7 +15498,7 @@
         <v>333</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H54" s="8">
         <v>18</v>
@@ -15445,10 +15533,10 @@
     </row>
     <row r="55" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>183</v>
@@ -15463,7 +15551,7 @@
         <v>333</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H55" s="7">
         <v>0</v>
@@ -15498,10 +15586,10 @@
     </row>
     <row r="56" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>183</v>
@@ -15516,7 +15604,7 @@
         <v>333</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H56" s="8">
         <v>0</v>
@@ -15528,7 +15616,7 @@
         <v>2</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="L56" s="6" t="s">
         <v>333</v>
@@ -15551,10 +15639,10 @@
     </row>
     <row r="57" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>183</v>
@@ -15569,7 +15657,7 @@
         <v>333</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H57" s="7">
         <v>15</v>
@@ -15604,10 +15692,10 @@
     </row>
     <row r="58" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>183</v>
@@ -15622,7 +15710,7 @@
         <v>333</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H58" s="8">
         <v>17</v>
@@ -15634,7 +15722,7 @@
         <v>1</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="L58" s="6" t="s">
         <v>333</v>
@@ -15657,10 +15745,10 @@
     </row>
     <row r="59" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>183</v>
@@ -15675,7 +15763,7 @@
         <v>333</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H59" s="7">
         <v>5</v>
@@ -15710,10 +15798,10 @@
     </row>
     <row r="60" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>183</v>
@@ -15728,7 +15816,7 @@
         <v>333</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H60" s="8">
         <v>2</v>
@@ -15763,10 +15851,10 @@
     </row>
     <row r="61" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>183</v>
@@ -15781,7 +15869,7 @@
         <v>333</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H61" s="7">
         <v>0</v>
@@ -15793,7 +15881,7 @@
         <v>0</v>
       </c>
       <c r="K61" s="5" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L61" s="5" t="s">
         <v>333</v>
@@ -15816,10 +15904,10 @@
     </row>
     <row r="62" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>183</v>
@@ -15834,7 +15922,7 @@
         <v>333</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H62" s="8">
         <v>8</v>
@@ -15846,7 +15934,7 @@
         <v>2</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="L62" s="6" t="s">
         <v>333</v>
@@ -15869,10 +15957,10 @@
     </row>
     <row r="63" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>183</v>
@@ -15887,7 +15975,7 @@
         <v>333</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H63" s="7">
         <v>8</v>
@@ -15899,7 +15987,7 @@
         <v>2</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="L63" s="5" t="s">
         <v>333</v>
@@ -15922,10 +16010,10 @@
     </row>
     <row r="64" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>183</v>
@@ -15940,7 +16028,7 @@
         <v>333</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H64" s="8">
         <v>3</v>
@@ -15975,10 +16063,10 @@
     </row>
     <row r="65" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>183</v>
@@ -15993,7 +16081,7 @@
         <v>333</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H65" s="7">
         <v>0</v>
@@ -16005,7 +16093,7 @@
         <v>0</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L65" s="5" t="s">
         <v>333</v>
@@ -16028,10 +16116,10 @@
     </row>
     <row r="66" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>183</v>
@@ -16046,7 +16134,7 @@
         <v>333</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H66" s="8">
         <v>7</v>
@@ -16081,10 +16169,10 @@
     </row>
     <row r="67" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>183</v>
@@ -16099,7 +16187,7 @@
         <v>333</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H67" s="7">
         <v>6</v>
@@ -16134,10 +16222,10 @@
     </row>
     <row r="68" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>183</v>
@@ -16152,7 +16240,7 @@
         <v>333</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H68" s="8">
         <v>26</v>
@@ -16164,7 +16252,7 @@
         <v>1</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="L68" s="6" t="s">
         <v>333</v>
@@ -16187,10 +16275,10 @@
     </row>
     <row r="69" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>183</v>
@@ -16205,7 +16293,7 @@
         <v>333</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H69" s="7">
         <v>0</v>
@@ -16217,7 +16305,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="5" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L69" s="5" t="s">
         <v>333</v>
@@ -16240,13 +16328,13 @@
     </row>
     <row r="70" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D70" s="8">
         <v>1</v>
@@ -16258,7 +16346,7 @@
         <v>333</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H70" s="8">
         <v>0</v>
@@ -16273,7 +16361,7 @@
         <v>440</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="M70" s="8">
         <v>2</v>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -2812,7 +2812,7 @@
     <t>PERCEPTION_INFO_TABLE</t>
   </si>
   <si>
-    <t>[{"level":0,"reconHops":1,"threat":["presence"],"extra":[]},{"level":0,"reconHops":1,"threat":["presence"],"extra":[]},{"level":1,"reconHops":2,"threat":["presence","size"],"extra":["prizeGrade"]},{"level":2,"reconHops":2,"threat":["presence","size","mode"],"extra":["prizeGrade","prizeAxis"]},{"level":3,"reconHops":2,"threat":["presence","size","mode","alert","nextMove"],"extra":["prizeGrade","prizeAxis","concealment"]},{"level":4,"reconHops":3,"threat":["presence","size","mode","alert","nextMove","composition"],"extra":["prizeGrade","prizeAxis","concealment"]},{"level":5,"reconHops":3,"threat":["presence","size","mode","alert","nextMove","composition","patrolNext"],"extra":["prizeGrade","prizeAxis","concealment","evidence"]}]</t>
+    <t>[{"level":0,"reconHops":1,"threat":["presence"],"extra":[]},{"level":0,"reconHops":1,"threat":["presence"],"extra":[]},{"level":1,"reconHops":1,"threat":["presence","size"],"extra":["prizeGrade"]},{"level":2,"reconHops":1,"threat":["presence","size","mode"],"extra":["prizeGrade","prizeAxis"]},{"level":3,"reconHops":1,"threat":["presence","size","mode","alert","nextMove"],"extra":["prizeGrade","prizeAxis","concealment"]},{"level":4,"reconHops":2,"threat":["presence","size","mode","alert","nextMove","composition"],"extra":["prizeGrade","prizeAxis","concealment"]},{"level":5,"reconHops":2,"threat":["presence","size","mode","alert","nextMove","composition","patrolNext"],"extra":["prizeGrade","prizeAxis","concealment","evidence"]}]</t>
   </si>
   <si>
     <t>PERCEPTION_WAIT_OBSERVATION_MIN</t>
@@ -4367,7 +4367,7 @@
         <v>813</v>
       </c>
       <c r="C14" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>67</v>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -1759,7 +1759,7 @@
     <t>지각 +1, 기동 -1</t>
   </si>
   <si>
-    <t>{"유형":"camera_snipe","시간 비용":4,"재사용 대기시간":15,"지속 시간":null,"범위":2,"대상 종류":"전자 장치","deviceKinds":["camera"]}</t>
+    <t>{"유형":"camera_snipe","시간 비용":4,"재사용 대기시간":30,"지속 시간":null,"범위":2,"대상 종류":"전자 장치","deviceKinds":["camera"]}</t>
   </si>
   <si>
     <t>방어구 스펙</t>
@@ -1843,7 +1843,7 @@
     <t>해킹 -1</t>
   </si>
   <si>
-    <t>{"유형":"임시 차단막","시간 비용":5,"재사용 대기시간":15,"지속 시간":10,"범위":1,"대상 종류":"통로"}</t>
+    <t>{"유형":"임시 차단막","시간 비용":5,"재사용 대기시간":30,"지속 시간":10,"범위":1,"대상 종류":"통로"}</t>
   </si>
   <si>
     <t>module_spatial</t>
@@ -1855,7 +1855,7 @@
     <t>지각 +2</t>
   </si>
   <si>
-    <t>{"유형":"스냅샷 스캔","시간 비용":5,"재사용 대기시간":15,"지속 시간":null,"범위":2,"대상 종류":"노드 내부"}</t>
+    <t>{"유형":"스냅샷 스캔","시간 비용":5,"재사용 대기시간":30,"지속 시간":null,"범위":2,"대상 종류":"노드 내부"}</t>
   </si>
   <si>
     <t>module_emp</t>
@@ -1870,7 +1870,7 @@
     <t>해킹 +2, 기만 +1, 지각 -1</t>
   </si>
   <si>
-    <t>{"유형":"원격 침투","시간 비용":5,"재사용 대기시간":15,"지속 시간":10,"범위":2,"대상 종류":"전자 장치"}</t>
+    <t>{"유형":"원격 침투","시간 비용":5,"재사용 대기시간":30,"지속 시간":10,"범위":2,"대상 종류":"전자 장치"}</t>
   </si>
   <si>
     <t>module_sandevistan</t>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -5281,7 +5281,7 @@
         <v>892</v>
       </c>
       <c r="C77" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>67</v>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3142" uniqueCount="997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3120" uniqueCount="987">
   <si>
     <t>현재 구현 규칙</t>
   </si>
@@ -244,13 +244,13 @@
     <t>이 시각에 도달하면 런 종료(마감과 같은 시각 도착은 늦은 것)</t>
   </si>
   <si>
-    <t>통로 비용</t>
-  </si>
-  <si>
-    <t>2~13칸</t>
-  </si>
-  <si>
-    <t>맵 생성 시 기하 거리로 한 번 정수화하고 이후 변하지 않는다</t>
+    <t>이동 비용</t>
+  </si>
+  <si>
+    <t>통로의 길이도 Mobility도 이동 시간을 바꾸지 않는다 — 맵의 모든 이동은 한 칸이다(ADR-0084)</t>
+  </si>
+  <si>
+    <t>src/engine/actionCosts.js</t>
   </si>
   <si>
     <t>위협 이동 간격</t>
@@ -259,7 +259,16 @@
     <t>순찰 5 / 조사·경계 4 / 추적 3</t>
   </si>
   <si>
-    <t>봉쇄 중에는 고정표로 각각 3/3/2</t>
+    <t>봉쇄 중에는 고정표로 각각 3/3/2. 이동이 1칸이 된 뒤로는 "내가 몇 홉 갈 동안 저쪽이 한 홉"으로 읽는다(ADR-0084)</t>
+  </si>
+  <si>
+    <t>경계도 2+ 이동 간격</t>
+  </si>
+  <si>
+    <t>순찰 3 / 조사·경계 3 / 추적 2</t>
+  </si>
+  <si>
+    <t>구역 경계도가 2 이상이면 그 구역의 위협이 모드를 가리지 않고 빨라진다. 봉쇄표와 함께 걸리면 둘 중 작은 값을 쓴다</t>
   </si>
   <si>
     <t>구역 경계 게이지</t>
@@ -295,7 +304,7 @@
     <t>A 비활성</t>
   </si>
   <si>
-    <t>요청·개방 여부와 무관하게 영구 폐쇄</t>
+    <t>이 시각 뒤로는 새 가동을 시작할 수 없다. 이미 시작된 가동 게이지와 열린 창은 끝까지 간다(ADR-0054)</t>
   </si>
   <si>
     <t>표준 출구 수</t>
@@ -316,19 +325,13 @@
     <t>봉쇄는 위협 이동·증원만 가속하고 출구 폐쇄 시각은 앞당기지 않는다(ADR-0083)</t>
   </si>
   <si>
-    <t>개방 요청 행동</t>
-  </si>
-  <si>
-    <t>요청 상호작용 시간</t>
-  </si>
-  <si>
-    <t>개방 대기</t>
-  </si>
-  <si>
-    <t>15/15/15/13/10/8/5</t>
-  </si>
-  <si>
-    <t>유효 Hacking -2~4별 요청 완료 후 개방까지</t>
+    <t>탈출구 가동</t>
+  </si>
+  <si>
+    <t>시작 1칸 + 게이지 18/18/18/16/13/11/8</t>
+  </si>
+  <si>
+    <t>유효 Hacking -2~4별 전체 소요 칸. 가동에 드는 것은 1칸이고 나머지는 그 노드에서 대기로 채운다. 자리를 뜨면 가동이 취소된다(ADR-0084)</t>
   </si>
   <si>
     <t>개방 유지</t>
@@ -340,22 +343,22 @@
     <t>맵 행동</t>
   </si>
   <si>
-    <t>작업 예약</t>
-  </si>
-  <si>
-    <t>완료 시 적용</t>
-  </si>
-  <si>
-    <t>현장 작업은 시작 시 대상·비용·자원을 예약만 하고, 보상·효과·쿨다운·경계도·소음을 완료 시각 C에 한 번에 확정한다</t>
+    <t>작업 가동</t>
+  </si>
+  <si>
+    <t>시작 1칸 + 게이지</t>
+  </si>
+  <si>
+    <t>현장 작업은 1칸으로 가동만 하고 남은 칸은 그 자리에서 대기로 채운다. 보상·효과·쿨다운·경계도·소음은 게이지가 차는 시각 C에 한 번에 확정된다(ADR-0084)</t>
   </si>
   <si>
     <t>작업 중단</t>
   </si>
   <si>
-    <t>적 접촉</t>
-  </si>
-  <si>
-    <t>완료 전에 새 위협이 도착하면 경과한 칸만 소모하고 미완료 효과는 하나도 적용하지 않는다. 임의 취소는 불가</t>
+    <t>적 접촉 · 자리를 떠남 · 붕괴</t>
+  </si>
+  <si>
+    <t>완료 전에 새 위협이 도착하거나 그 노드를 벗어나면 경과한 칸만 소모하고 미완료 효과는 하나도 적용하지 않는다. 그 자리에 선 채로의 임의 취소는 불가</t>
   </si>
   <si>
     <t>대기</t>
@@ -364,7 +367,7 @@
     <t>1 / 최대 5칸</t>
   </si>
   <si>
-    <t>아무것도 회복시키지 않는다. 묶음 대기는 새 조우·출구 개방/폐쇄·붕괴에서 즉시 멈춘다</t>
+    <t>아무것도 회복시키지 않는다. 진행 중인 작업이 있으면 그 게이지를 채운다. 묶음 대기는 새 조우·출구 개방/폐쇄·붕괴·작업 완료에서 즉시 멈춘다</t>
   </si>
   <si>
     <t>src/engine/facilityReducer.js</t>
@@ -391,10 +394,7 @@
     <t>장비 교체</t>
   </si>
   <si>
-    <t>장착·해제 각 1건마다. 예약해 두고 완료 시각에 적용되며, 중단되면 교체 없이 경과한 칸만 든다</t>
-  </si>
-  <si>
-    <t>src/engine/actionCosts.js</t>
+    <t>장착·해제 각 1건마다. 가동해 두고 게이지가 찰 때 적용되며, 중단되면 교체 없이 경과한 칸만 든다</t>
   </si>
   <si>
     <t>회복 소모품 사용</t>
@@ -2605,15 +2605,6 @@
     <t>DISCOVERY_NOISE_INTENSITY</t>
   </si>
   <si>
-    <t>EDGE_TIME_MAX</t>
-  </si>
-  <si>
-    <t>EDGE_TIME_MIN</t>
-  </si>
-  <si>
-    <t>EDGE_TIME_PER_LENGTH_UNIT</t>
-  </si>
-  <si>
     <t>ENCOUNTER_DECEIVE_REQUIREMENT</t>
   </si>
   <si>
@@ -2638,10 +2629,10 @@
     <t>EXIT_A_DISABLED_AT</t>
   </si>
   <si>
-    <t>EXIT_OPEN_WAIT_BY_HACKING</t>
-  </si>
-  <si>
-    <t>[15,15,15,13,10,8,5]</t>
+    <t>EXIT_ACTIVATE_TIME_BY_HACKING</t>
+  </si>
+  <si>
+    <t>[18,18,18,16,13,11,8]</t>
   </si>
   <si>
     <t>EXIT_OPEN_WINDOW</t>
@@ -2650,9 +2641,6 @@
     <t>EXIT_PLACEMENT_MAX_ATTEMPTS</t>
   </si>
   <si>
-    <t>EXIT_REQUEST_TIME</t>
-  </si>
-  <si>
     <t>FAKE_NOISE_INTENSITY</t>
   </si>
   <si>
@@ -2764,12 +2752,6 @@
     <t>{"entrance":{"id":"security_records_room","name":"보안 기록실","approaches":["지각","해킹","파괴"]},"labs":{"id":"quarantine_vault","name":"격리 표본고","approaches":["은신","파괴","해킹"]},"hangar":{"id":"cargo_bay","name":"화물 격납고","approaches":["파괴","기동","해킹"]},"security":{"id":"central_control","name":"중앙 관제실","approaches":["해킹","기만","파괴"]},"파워":{"id":"main_generator","name":"주 발전기","approaches":["파괴","해킹","기동"]},"waste":{"id":"incinerator_core","name":"소각로 중심부","approaches":["파괴","은신","해킹"]},"comms":{"id":"control_tower","name":"중앙 관제탑","approaches":["해킹","지각","기만"]},"residential":{"id":"staff_quarters_vault","name":"직원 숙소 금고","approaches":["은신","기만","해킹"]}}</t>
   </si>
   <si>
-    <t>LOCKDOWN_SECTOR_ALERT_INVESTIGATE_INTERVAL</t>
-  </si>
-  <si>
-    <t>{"2":2,"3":2}</t>
-  </si>
-  <si>
     <t>LOCKDOWN_THREAT_MOVE_INTERVAL</t>
   </si>
   <si>
@@ -2782,15 +2764,6 @@
     <t>LONG_RANGE_SPECIAL_EDGES_MIN</t>
   </si>
   <si>
-    <t>MOBILITY_MOVE_TIME_DELTA</t>
-  </si>
-  <si>
-    <t>[2,1,0,-1,-2,-3,-4]</t>
-  </si>
-  <si>
-    <t>MOVE_MIN_TIME</t>
-  </si>
-  <si>
     <t>NODE_MIN_SEPARATION</t>
   </si>
   <si>
@@ -2893,10 +2866,7 @@
     <t>RUN_SECTOR_COUNT</t>
   </si>
   <si>
-    <t>SECTOR_ALERT_INVESTIGATE_INTERVAL</t>
-  </si>
-  <si>
-    <t>{"2":3,"3":3}</t>
+    <t>SECTOR_ALERT_FAST_MOVE_LEVEL</t>
   </si>
   <si>
     <t>SECTOR_ALERT_MIN_ENEMY_ALERT</t>
@@ -2905,6 +2875,9 @@
     <t>{"0":0,"1":1,"2":2,"3":2}</t>
   </si>
   <si>
+    <t>SECTOR_ALERT_MOVE_INTERVAL</t>
+  </si>
+  <si>
     <t>SECTOR_LAYOUTS</t>
   </si>
   <si>
@@ -2936,9 +2909,6 @@
   </si>
   <si>
     <t>SPECIAL_EDGES_PER_SECTOR_MIN</t>
-  </si>
-  <si>
-    <t>STANDARD_EDGE_TIME_COST</t>
   </si>
   <si>
     <t>START_SECTOR_ID</t>
@@ -3843,7 +3813,7 @@
         <v>72</v>
       </c>
       <c r="C24" s="6">
-        <v>490</v>
+        <v>50</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>73</v>
@@ -3860,13 +3830,13 @@
         <v>74</v>
       </c>
       <c r="C25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -3939,13 +3909,13 @@
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="C30" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="C30" s="6">
-        <v>300</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>91</v>
@@ -3956,24 +3926,24 @@
     </row>
     <row r="31" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" s="5" t="s">
         <v>93</v>
+      </c>
+      <c r="C31" s="5">
+        <v>30</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>94</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>95</v>
@@ -3985,38 +3955,38 @@
         <v>97</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C33" s="5">
-        <v>3</v>
+      <c r="C33" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>67</v>
@@ -4024,16 +3994,16 @@
     </row>
     <row r="35" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C35" s="5">
         <v>5</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>67</v>
@@ -4041,16 +4011,16 @@
     </row>
     <row r="36" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>71</v>
@@ -4058,16 +4028,16 @@
     </row>
     <row r="37" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>71</v>
@@ -4075,33 +4045,33 @@
     </row>
     <row r="38" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C39" s="5">
         <v>1</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>71</v>
@@ -4109,41 +4079,41 @@
     </row>
     <row r="40" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C41" s="5">
         <v>3</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>124</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>125</v>
@@ -4155,7 +4125,7 @@
         <v>126</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>124</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -4225,7 +4195,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D154"/>
+  <dimension ref="A1:D147"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -4897,13 +4867,13 @@
     </row>
     <row r="50" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>799</v>
+        <v>833</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>861</v>
       </c>
       <c r="C50" s="6">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>67</v>
@@ -4911,13 +4881,13 @@
     </row>
     <row r="51" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>799</v>
+        <v>833</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>862</v>
       </c>
-      <c r="C51" s="5">
-        <v>2</v>
+      <c r="C51" s="5" t="s">
+        <v>863</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>67</v>
@@ -4925,13 +4895,13 @@
     </row>
     <row r="52" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C52" s="6">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>67</v>
@@ -4939,10 +4909,10 @@
     </row>
     <row r="53" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>833</v>
+        <v>801</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C53" s="5">
         <v>2</v>
@@ -4953,13 +4923,13 @@
     </row>
     <row r="54" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>833</v>
+        <v>801</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>865</v>
-      </c>
-      <c r="C54" s="6" t="s">
         <v>866</v>
+      </c>
+      <c r="C54" s="6">
+        <v>2</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>67</v>
@@ -4967,13 +4937,13 @@
     </row>
     <row r="55" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>807</v>
+        <v>833</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>867</v>
       </c>
-      <c r="C55" s="5">
-        <v>1</v>
+      <c r="C55" s="5" t="s">
+        <v>336</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>67</v>
@@ -4981,13 +4951,13 @@
     </row>
     <row r="56" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>801</v>
+        <v>92</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>868</v>
       </c>
       <c r="C56" s="6">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>67</v>
@@ -4995,13 +4965,13 @@
     </row>
     <row r="57" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>801</v>
+        <v>92</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>869</v>
       </c>
-      <c r="C57" s="5">
-        <v>2</v>
+      <c r="C57" s="5" t="s">
+        <v>870</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>67</v>
@@ -5009,13 +4979,13 @@
     </row>
     <row r="58" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>833</v>
+        <v>92</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>870</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>336</v>
+        <v>871</v>
+      </c>
+      <c r="C58" s="6">
+        <v>5</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>67</v>
@@ -5023,13 +4993,13 @@
     </row>
     <row r="59" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C59" s="5">
-        <v>300</v>
+        <v>24</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>67</v>
@@ -5037,13 +5007,13 @@
     </row>
     <row r="60" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>89</v>
+        <v>801</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>872</v>
-      </c>
-      <c r="C60" s="6" t="s">
         <v>873</v>
+      </c>
+      <c r="C60" s="6">
+        <v>1</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>67</v>
@@ -5051,13 +5021,13 @@
     </row>
     <row r="61" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>89</v>
+        <v>801</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>874</v>
       </c>
-      <c r="C61" s="5">
-        <v>5</v>
+      <c r="C61" s="5" t="s">
+        <v>875</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>67</v>
@@ -5065,13 +5035,13 @@
     </row>
     <row r="62" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>89</v>
+        <v>801</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C62" s="6">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>67</v>
@@ -5079,10 +5049,10 @@
     </row>
     <row r="63" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>89</v>
+        <v>801</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C63" s="5">
         <v>3</v>
@@ -5096,10 +5066,10 @@
         <v>801</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C64" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>67</v>
@@ -5110,10 +5080,10 @@
         <v>801</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>878</v>
-      </c>
-      <c r="C65" s="5" t="s">
         <v>879</v>
+      </c>
+      <c r="C65" s="5">
+        <v>3</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>67</v>
@@ -5121,13 +5091,13 @@
     </row>
     <row r="66" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>801</v>
+        <v>833</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>880</v>
       </c>
       <c r="C66" s="6">
-        <v>1</v>
+        <v>256</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>67</v>
@@ -5135,7 +5105,7 @@
     </row>
     <row r="67" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>881</v>
@@ -5149,13 +5119,13 @@
     </row>
     <row r="68" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>801</v>
+        <v>833</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>882</v>
       </c>
-      <c r="C68" s="6">
-        <v>2</v>
+      <c r="C68" s="6" t="s">
+        <v>883</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>67</v>
@@ -5163,13 +5133,13 @@
     </row>
     <row r="69" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>801</v>
+        <v>833</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C69" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>67</v>
@@ -5180,10 +5150,10 @@
         <v>833</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C70" s="6">
-        <v>256</v>
+        <v>7</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>67</v>
@@ -5191,13 +5161,13 @@
     </row>
     <row r="71" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C71" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>67</v>
@@ -5205,13 +5175,13 @@
     </row>
     <row r="72" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>833</v>
+        <v>807</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>886</v>
-      </c>
-      <c r="C72" s="6" t="s">
         <v>887</v>
+      </c>
+      <c r="C72" s="6">
+        <v>5</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>67</v>
@@ -5225,7 +5195,7 @@
         <v>888</v>
       </c>
       <c r="C73" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>67</v>
@@ -5233,13 +5203,13 @@
     </row>
     <row r="74" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>833</v>
+        <v>799</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>889</v>
       </c>
       <c r="C74" s="6">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>67</v>
@@ -5247,13 +5217,13 @@
     </row>
     <row r="75" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>801</v>
+        <v>820</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>890</v>
       </c>
       <c r="C75" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>67</v>
@@ -5261,13 +5231,13 @@
     </row>
     <row r="76" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>891</v>
       </c>
       <c r="C76" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>67</v>
@@ -5275,13 +5245,13 @@
     </row>
     <row r="77" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>892</v>
       </c>
       <c r="C77" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>67</v>
@@ -5289,13 +5259,13 @@
     </row>
     <row r="78" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>799</v>
+        <v>820</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>893</v>
       </c>
       <c r="C78" s="6">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>67</v>
@@ -5303,13 +5273,13 @@
     </row>
     <row r="79" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>820</v>
+        <v>799</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>894</v>
       </c>
-      <c r="C79" s="5">
-        <v>5</v>
+      <c r="C79" s="5" t="s">
+        <v>895</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>67</v>
@@ -5320,10 +5290,10 @@
         <v>801</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C80" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>67</v>
@@ -5331,13 +5301,13 @@
     </row>
     <row r="81" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>820</v>
+        <v>807</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C81" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>67</v>
@@ -5345,13 +5315,13 @@
     </row>
     <row r="82" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>820</v>
+        <v>833</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C82" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>67</v>
@@ -5359,13 +5329,13 @@
     </row>
     <row r="83" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>898</v>
-      </c>
-      <c r="C83" s="5" t="s">
         <v>899</v>
+      </c>
+      <c r="C83" s="5">
+        <v>3</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>67</v>
@@ -5373,13 +5343,13 @@
     </row>
     <row r="84" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>801</v>
+        <v>820</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>900</v>
       </c>
-      <c r="C84" s="6">
-        <v>0</v>
+      <c r="C84" s="6" t="s">
+        <v>901</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>67</v>
@@ -5387,13 +5357,13 @@
     </row>
     <row r="85" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>807</v>
+        <v>833</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C85" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>67</v>
@@ -5401,13 +5371,13 @@
     </row>
     <row r="86" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>833</v>
+        <v>801</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C86" s="6">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>67</v>
@@ -5415,13 +5385,13 @@
     </row>
     <row r="87" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>807</v>
+        <v>904</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C87" s="5">
-        <v>3</v>
+        <v>0.01</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>67</v>
@@ -5429,13 +5399,13 @@
     </row>
     <row r="88" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>820</v>
+        <v>904</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>904</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>905</v>
+        <v>906</v>
+      </c>
+      <c r="C88" s="6">
+        <v>4</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>67</v>
@@ -5443,13 +5413,13 @@
     </row>
     <row r="89" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>833</v>
+        <v>904</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C89" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>67</v>
@@ -5457,13 +5427,13 @@
     </row>
     <row r="90" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>907</v>
-      </c>
-      <c r="C90" s="6">
-        <v>15</v>
+        <v>908</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>909</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>67</v>
@@ -5471,13 +5441,13 @@
     </row>
     <row r="91" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>908</v>
+        <v>801</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>909</v>
-      </c>
-      <c r="C91" s="5">
-        <v>0.01</v>
+        <v>910</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>911</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>67</v>
@@ -5485,13 +5455,13 @@
     </row>
     <row r="92" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>908</v>
+        <v>799</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="C92" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>67</v>
@@ -5499,10 +5469,10 @@
     </row>
     <row r="93" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>908</v>
+        <v>799</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C93" s="5">
         <v>2</v>
@@ -5516,10 +5486,10 @@
         <v>799</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>912</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>913</v>
+        <v>914</v>
+      </c>
+      <c r="C94" s="6">
+        <v>0.17</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>67</v>
@@ -5527,13 +5497,13 @@
     </row>
     <row r="95" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>914</v>
-      </c>
-      <c r="C95" s="5" t="s">
         <v>915</v>
+      </c>
+      <c r="C95" s="5">
+        <v>24</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>67</v>
@@ -5541,7 +5511,7 @@
     </row>
     <row r="96" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>916</v>
@@ -5560,8 +5530,8 @@
       <c r="B97" s="5" t="s">
         <v>918</v>
       </c>
-      <c r="C97" s="5">
-        <v>3</v>
+      <c r="C97" s="5" t="s">
+        <v>919</v>
       </c>
       <c r="D97" s="5" t="s">
         <v>67</v>
@@ -5569,13 +5539,13 @@
     </row>
     <row r="98" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C98" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>67</v>
@@ -5583,13 +5553,13 @@
     </row>
     <row r="99" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>67</v>
@@ -5597,13 +5567,13 @@
     </row>
     <row r="100" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>833</v>
+        <v>904</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>922</v>
-      </c>
-      <c r="C100" s="6">
-        <v>2</v>
+        <v>923</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>924</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>67</v>
@@ -5611,13 +5581,13 @@
     </row>
     <row r="101" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>799</v>
+        <v>833</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>923</v>
-      </c>
-      <c r="C101" s="5">
-        <v>0.17</v>
+        <v>925</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>926</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>67</v>
@@ -5625,13 +5595,13 @@
     </row>
     <row r="102" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="C102" s="6">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>67</v>
@@ -5639,13 +5609,13 @@
     </row>
     <row r="103" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>799</v>
+        <v>833</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>925</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>926</v>
+        <v>928</v>
+      </c>
+      <c r="C103" s="5">
+        <v>30</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>67</v>
@@ -5653,13 +5623,13 @@
     </row>
     <row r="104" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>927</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>928</v>
+        <v>929</v>
+      </c>
+      <c r="C104" s="6">
+        <v>3</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>67</v>
@@ -5667,13 +5637,13 @@
     </row>
     <row r="105" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>801</v>
+        <v>833</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C105" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>67</v>
@@ -5681,13 +5651,13 @@
     </row>
     <row r="106" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>801</v>
+        <v>833</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>67</v>
@@ -5695,13 +5665,13 @@
     </row>
     <row r="107" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>908</v>
+        <v>801</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>67</v>
@@ -5709,13 +5679,13 @@
     </row>
     <row r="108" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>833</v>
+        <v>807</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>67</v>
@@ -5723,13 +5693,13 @@
     </row>
     <row r="109" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>807</v>
+        <v>833</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C109" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>67</v>
@@ -5737,13 +5707,13 @@
     </row>
     <row r="110" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
-        <v>833</v>
+        <v>799</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>937</v>
-      </c>
-      <c r="C110" s="6">
-        <v>30</v>
+        <v>938</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>939</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>67</v>
@@ -5751,13 +5721,13 @@
     </row>
     <row r="111" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>801</v>
+        <v>833</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>938</v>
-      </c>
-      <c r="C111" s="5">
-        <v>3</v>
+        <v>940</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>941</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>67</v>
@@ -5765,13 +5735,13 @@
     </row>
     <row r="112" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
-        <v>833</v>
+        <v>801</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="C112" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>67</v>
@@ -5782,10 +5752,10 @@
         <v>833</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>940</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>941</v>
+        <v>943</v>
+      </c>
+      <c r="C113" s="5">
+        <v>6</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>67</v>
@@ -5793,13 +5763,13 @@
     </row>
     <row r="114" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>942</v>
-      </c>
-      <c r="C114" s="6" t="s">
-        <v>943</v>
+        <v>944</v>
+      </c>
+      <c r="C114" s="6">
+        <v>180</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>67</v>
@@ -5810,10 +5780,10 @@
         <v>807</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>944</v>
-      </c>
-      <c r="C115" s="5" t="s">
         <v>945</v>
+      </c>
+      <c r="C115" s="5">
+        <v>90</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>67</v>
@@ -5821,13 +5791,13 @@
     </row>
     <row r="116" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
-        <v>833</v>
+        <v>92</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>946</v>
       </c>
       <c r="C116" s="6">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>67</v>
@@ -5840,8 +5810,8 @@
       <c r="B117" s="5" t="s">
         <v>947</v>
       </c>
-      <c r="C117" s="5" t="s">
-        <v>948</v>
+      <c r="C117" s="5">
+        <v>4</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>67</v>
@@ -5849,13 +5819,13 @@
     </row>
     <row r="118" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
-        <v>833</v>
+        <v>801</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>949</v>
-      </c>
-      <c r="C118" s="6" t="s">
-        <v>950</v>
+        <v>948</v>
+      </c>
+      <c r="C118" s="6">
+        <v>2</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>67</v>
@@ -5866,10 +5836,10 @@
         <v>801</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>951</v>
-      </c>
-      <c r="C119" s="5">
-        <v>2</v>
+        <v>949</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>950</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>67</v>
@@ -5877,13 +5847,13 @@
     </row>
     <row r="120" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
-        <v>833</v>
+        <v>801</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>952</v>
-      </c>
-      <c r="C120" s="6">
-        <v>6</v>
+        <v>951</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>911</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>67</v>
@@ -5891,13 +5861,13 @@
     </row>
     <row r="121" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="B121" s="5" t="s">
+        <v>952</v>
+      </c>
+      <c r="C121" s="5" t="s">
         <v>953</v>
-      </c>
-      <c r="C121" s="5">
-        <v>180</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>67</v>
@@ -5905,13 +5875,13 @@
     </row>
     <row r="122" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>954</v>
       </c>
-      <c r="C122" s="6">
-        <v>90</v>
+      <c r="C122" s="6" t="s">
+        <v>955</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>67</v>
@@ -5919,13 +5889,13 @@
     </row>
     <row r="123" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>89</v>
+        <v>799</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C123" s="5">
-        <v>490</v>
+        <v>280</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>67</v>
@@ -5936,10 +5906,10 @@
         <v>799</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C124" s="6">
-        <v>4</v>
+        <v>900</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>67</v>
@@ -5947,13 +5917,13 @@
     </row>
     <row r="125" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>67</v>
@@ -5961,13 +5931,13 @@
     </row>
     <row r="126" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>959</v>
-      </c>
-      <c r="C126" s="6" t="s">
         <v>960</v>
+      </c>
+      <c r="C126" s="6">
+        <v>0.4</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>67</v>
@@ -5980,8 +5950,8 @@
       <c r="B127" s="5" t="s">
         <v>961</v>
       </c>
-      <c r="C127" s="5" t="s">
-        <v>962</v>
+      <c r="C127" s="5">
+        <v>6</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>67</v>
@@ -5992,10 +5962,10 @@
         <v>799</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>963</v>
-      </c>
-      <c r="C128" s="6" t="s">
-        <v>964</v>
+        <v>962</v>
+      </c>
+      <c r="C128" s="6">
+        <v>4</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>67</v>
@@ -6006,10 +5976,10 @@
         <v>799</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>965</v>
-      </c>
-      <c r="C129" s="5">
-        <v>280</v>
+        <v>963</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>964</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>67</v>
@@ -6017,13 +5987,13 @@
     </row>
     <row r="130" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
-        <v>799</v>
+        <v>820</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C130" s="6">
-        <v>900</v>
+        <v>-1</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>67</v>
@@ -6031,13 +6001,13 @@
     </row>
     <row r="131" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
-        <v>799</v>
+        <v>833</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>967</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>968</v>
+        <v>966</v>
+      </c>
+      <c r="C131" s="5">
+        <v>-1</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>67</v>
@@ -6045,13 +6015,13 @@
     </row>
     <row r="132" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
-        <v>799</v>
+        <v>833</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C132" s="6">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>67</v>
@@ -6059,13 +6029,13 @@
     </row>
     <row r="133" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="C133" s="5">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>67</v>
@@ -6073,13 +6043,13 @@
     </row>
     <row r="134" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="C134" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>67</v>
@@ -6087,13 +6057,13 @@
     </row>
     <row r="135" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>972</v>
-      </c>
-      <c r="C135" s="5">
-        <v>5</v>
+        <v>970</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>971</v>
       </c>
       <c r="D135" s="5" t="s">
         <v>67</v>
@@ -6101,13 +6071,13 @@
     </row>
     <row r="136" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B136" s="6" t="s">
+        <v>972</v>
+      </c>
+      <c r="C136" s="6" t="s">
         <v>973</v>
-      </c>
-      <c r="C136" s="6" t="s">
-        <v>974</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>67</v>
@@ -6115,13 +6085,13 @@
     </row>
     <row r="137" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>820</v>
+        <v>801</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C137" s="5">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>67</v>
@@ -6129,13 +6099,13 @@
     </row>
     <row r="138" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
-        <v>833</v>
+        <v>801</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="C138" s="6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>67</v>
@@ -6143,13 +6113,13 @@
     </row>
     <row r="139" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
-        <v>833</v>
+        <v>801</v>
       </c>
       <c r="B139" s="5" t="s">
+        <v>976</v>
+      </c>
+      <c r="C139" s="5" t="s">
         <v>977</v>
-      </c>
-      <c r="C139" s="5">
-        <v>1</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>67</v>
@@ -6163,7 +6133,7 @@
         <v>978</v>
       </c>
       <c r="C140" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>67</v>
@@ -6171,13 +6141,13 @@
     </row>
     <row r="141" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>979</v>
       </c>
       <c r="C141" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>67</v>
@@ -6185,13 +6155,13 @@
     </row>
     <row r="142" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
-        <v>801</v>
+        <v>833</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>980</v>
       </c>
-      <c r="C142" s="6" t="s">
-        <v>981</v>
+      <c r="C142" s="6">
+        <v>3</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>67</v>
@@ -6199,13 +6169,13 @@
     </row>
     <row r="143" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
-        <v>801</v>
+        <v>833</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>982</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>983</v>
+        <v>981</v>
+      </c>
+      <c r="C143" s="5">
+        <v>4</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>67</v>
@@ -6213,13 +6183,13 @@
     </row>
     <row r="144" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
-        <v>801</v>
+        <v>833</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="C144" s="6">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>67</v>
@@ -6227,13 +6197,13 @@
     </row>
     <row r="145" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
-        <v>801</v>
+        <v>833</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>985</v>
-      </c>
-      <c r="C145" s="5">
-        <v>3</v>
+        <v>983</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>984</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>67</v>
@@ -6241,13 +6211,13 @@
     </row>
     <row r="146" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>986</v>
-      </c>
-      <c r="C146" s="6" t="s">
-        <v>987</v>
+        <v>985</v>
+      </c>
+      <c r="C146" s="6">
+        <v>5</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>67</v>
@@ -6255,118 +6225,20 @@
     </row>
     <row r="147" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
-        <v>801</v>
+        <v>807</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C147" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="148" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="6" t="s">
-        <v>801</v>
-      </c>
-      <c r="B148" s="6" t="s">
-        <v>989</v>
-      </c>
-      <c r="C148" s="6">
-        <v>2</v>
-      </c>
-      <c r="D148" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="5" t="s">
-        <v>833</v>
-      </c>
-      <c r="B149" s="5" t="s">
-        <v>990</v>
-      </c>
-      <c r="C149" s="5">
-        <v>3</v>
-      </c>
-      <c r="D149" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="6" t="s">
-        <v>833</v>
-      </c>
-      <c r="B150" s="6" t="s">
-        <v>991</v>
-      </c>
-      <c r="C150" s="6">
-        <v>4</v>
-      </c>
-      <c r="D150" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="5" t="s">
-        <v>833</v>
-      </c>
-      <c r="B151" s="5" t="s">
-        <v>992</v>
-      </c>
-      <c r="C151" s="5">
-        <v>2.6</v>
-      </c>
-      <c r="D151" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="6" t="s">
-        <v>833</v>
-      </c>
-      <c r="B152" s="6" t="s">
-        <v>993</v>
-      </c>
-      <c r="C152" s="6" t="s">
-        <v>994</v>
-      </c>
-      <c r="D152" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="5" t="s">
-        <v>807</v>
-      </c>
-      <c r="B153" s="5" t="s">
-        <v>995</v>
-      </c>
-      <c r="C153" s="5">
-        <v>5</v>
-      </c>
-      <c r="D153" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="6" t="s">
-        <v>807</v>
-      </c>
-      <c r="B154" s="6" t="s">
-        <v>996</v>
-      </c>
-      <c r="C154" s="6">
-        <v>1</v>
-      </c>
-      <c r="D154" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:D154"/>
+  <autoFilter ref="A4:D147"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
@@ -7035,7 +6907,7 @@
     </row>
     <row r="83" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>291</v>
@@ -9201,7 +9073,7 @@
         <v>0</v>
       </c>
       <c r="Q35" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="R35" s="7">
         <v>1</v>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -328,7 +328,7 @@
     <t>탈출구 가동</t>
   </si>
   <si>
-    <t>시작 1칸 + 게이지 18/18/18/16/13/11/8</t>
+    <t>시작 1칸 + 게이지 9/9/9/8/7/6/4</t>
   </si>
   <si>
     <t>유효 Hacking -2~4별 전체 소요 칸. 가동에 드는 것은 1칸이고 나머지는 그 노드에서 대기로 채운다. 자리를 뜨면 가동이 취소된다(ADR-0084)</t>
@@ -2632,7 +2632,7 @@
     <t>EXIT_ACTIVATE_TIME_BY_HACKING</t>
   </si>
   <si>
-    <t>[18,18,18,16,13,11,8]</t>
+    <t>[9,9,9,8,7,6,4]</t>
   </si>
   <si>
     <t>EXIT_OPEN_WINDOW</t>
@@ -3813,7 +3813,7 @@
         <v>72</v>
       </c>
       <c r="C24" s="6">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>73</v>
@@ -3932,7 +3932,7 @@
         <v>93</v>
       </c>
       <c r="C31" s="5">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>94</v>
@@ -4957,7 +4957,7 @@
         <v>868</v>
       </c>
       <c r="C56" s="6">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>67</v>
@@ -5797,7 +5797,7 @@
         <v>946</v>
       </c>
       <c r="C116" s="6">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>67</v>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -3490,7 +3490,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="5">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>9</v>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -1768,7 +1768,7 @@
     <t>지각 +1, 기동 -1</t>
   </si>
   <si>
-    <t>{"유형":"camera_snipe","시간 비용":4,"재사용 대기시간":30,"지속 시간":null,"범위":2,"대상 종류":"전자 장치","deviceKinds":["camera"]}</t>
+    <t>{"유형":"camera_snipe","시간 비용":4,"재사용 대기시간":20,"지속 시간":null,"범위":2,"대상 종류":"전자 장치","deviceKinds":["camera"]}</t>
   </si>
   <si>
     <t>방어구 스펙</t>
@@ -1852,7 +1852,7 @@
     <t>해킹 -1</t>
   </si>
   <si>
-    <t>{"유형":"임시 차단막","시간 비용":5,"재사용 대기시간":30,"지속 시간":10,"범위":1,"대상 종류":"통로"}</t>
+    <t>{"유형":"임시 차단막","시간 비용":5,"재사용 대기시간":20,"지속 시간":10,"범위":1,"대상 종류":"통로"}</t>
   </si>
   <si>
     <t>module_spatial</t>
@@ -1864,7 +1864,7 @@
     <t>지각 +2</t>
   </si>
   <si>
-    <t>{"유형":"스냅샷 스캔","시간 비용":5,"재사용 대기시간":30,"지속 시간":null,"범위":2,"대상 종류":"노드 내부"}</t>
+    <t>{"유형":"스냅샷 스캔","시간 비용":5,"재사용 대기시간":20,"지속 시간":null,"범위":2,"대상 종류":"노드 내부"}</t>
   </si>
   <si>
     <t>module_emp</t>
@@ -1879,7 +1879,7 @@
     <t>해킹 +2, 기만 +1, 지각 -1</t>
   </si>
   <si>
-    <t>{"유형":"원격 침투","시간 비용":5,"재사용 대기시간":30,"지속 시간":10,"범위":2,"대상 종류":"전자 장치"}</t>
+    <t>{"유형":"원격 침투","시간 비용":5,"재사용 대기시간":20,"지속 시간":10,"범위":2,"대상 종류":"전자 장치"}</t>
   </si>
   <si>
     <t>module_sandevistan</t>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -4006,7 +4006,7 @@
         <v>72</v>
       </c>
       <c r="C24" s="6">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>73</v>
@@ -4193,7 +4193,7 @@
         <v>105</v>
       </c>
       <c r="C35" s="5">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>106</v>
@@ -9019,7 +9019,7 @@
         <v>926</v>
       </c>
       <c r="C57" s="5">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>67</v>
@@ -9957,7 +9957,7 @@
         <v>1010</v>
       </c>
       <c r="C124" s="6">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>67</v>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -208,7 +208,7 @@
     <t>4구역 / 전체 8구역</t>
   </si>
   <si>
-    <t>계약 수락 시에 뽑는다. 입구·관리동과 수락한 계약의 목표 구역은 항상 포함되고 나머지를 균등 추첨. 링 정반대(가장 깊은 자리)는 동력·정비동이 뽑혔으면 동력·정비동, 아니면 계약 목표 구역이다(ADR-0083)</t>
+    <t>계약 제안마다 미리 뽑아 계약 화면에 보여주고, 수락은 그 목록을 그대로 쓴다(ADR-0089). 입구·관리동과 그 계약의 목표 구역은 항상 포함되고 나머지를 균등 추첨. 링 정반대(가장 깊은 자리)는 동력·정비동이 뽑혔으면 동력·정비동, 아니면 계약 목표 구역이다(ADR-0083)</t>
   </si>
   <si>
     <t>src/engine/facilityGraph.js</t>
@@ -1768,7 +1768,7 @@
     <t>지각 +1, 기동 -1</t>
   </si>
   <si>
-    <t>{"유형":"camera_snipe","시간 비용":4,"재사용 대기시간":20,"지속 시간":null,"범위":2,"대상 종류":"전자 장치","deviceKinds":["camera"]}</t>
+    <t>{"유형":"camera_snipe","시간 비용":4,"재사용 대기시간":30,"지속 시간":null,"범위":2,"대상 종류":"전자 장치","deviceKinds":["camera"]}</t>
   </si>
   <si>
     <t>방어구 스펙</t>
@@ -1852,7 +1852,7 @@
     <t>해킹 -1</t>
   </si>
   <si>
-    <t>{"유형":"임시 차단막","시간 비용":5,"재사용 대기시간":20,"지속 시간":10,"범위":1,"대상 종류":"통로"}</t>
+    <t>{"유형":"임시 차단막","시간 비용":5,"재사용 대기시간":30,"지속 시간":10,"범위":1,"대상 종류":"통로"}</t>
   </si>
   <si>
     <t>module_spatial</t>
@@ -1864,7 +1864,7 @@
     <t>지각 +2</t>
   </si>
   <si>
-    <t>{"유형":"스냅샷 스캔","시간 비용":5,"재사용 대기시간":20,"지속 시간":null,"범위":2,"대상 종류":"노드 내부"}</t>
+    <t>{"유형":"스냅샷 스캔","시간 비용":5,"재사용 대기시간":30,"지속 시간":null,"범위":2,"대상 종류":"노드 내부"}</t>
   </si>
   <si>
     <t>module_emp</t>
@@ -1879,7 +1879,7 @@
     <t>해킹 +2, 기만 +1, 지각 -1</t>
   </si>
   <si>
-    <t>{"유형":"원격 침투","시간 비용":5,"재사용 대기시간":20,"지속 시간":10,"범위":2,"대상 종류":"전자 장치"}</t>
+    <t>{"유형":"원격 침투","시간 비용":5,"재사용 대기시간":30,"지속 시간":10,"범위":2,"대상 종류":"전자 장치"}</t>
   </si>
   <si>
     <t>module_sandevistan</t>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -4153,7 +4153,7 @@
         <v>130</v>
       </c>
       <c r="C44" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>131</v>
@@ -4170,7 +4170,7 @@
         <v>132</v>
       </c>
       <c r="C45" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>133</v>
@@ -4677,7 +4677,7 @@
         <v>847</v>
       </c>
       <c r="C36" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>67</v>
@@ -4691,7 +4691,7 @@
         <v>848</v>
       </c>
       <c r="C37" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>67</v>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -329,7 +329,7 @@
     <t>탈출구 가동</t>
   </si>
   <si>
-    <t>시작 1칸 + 게이지 9/9/9/8/7/6/4</t>
+    <t>시작 1칸 + 게이지 5/5/5/4/4/3/2</t>
   </si>
   <si>
     <t>유효 Hacking -2~4별 전체 소요 칸. 가동에 드는 것은 1칸이고 나머지는 그 노드에서 대기로 채운다. 자리를 뜨면 가동이 취소된다(ADR-0084)</t>
@@ -1769,7 +1769,7 @@
     <t>지각 +1, 기동 -1</t>
   </si>
   <si>
-    <t>{"유형":"camera_snipe","시간 비용":4,"재사용 대기시간":20,"지속 시간":null,"범위":2,"대상 종류":"전자 장치","deviceKinds":["camera"]}</t>
+    <t>{"유형":"camera_snipe","시간 비용":2,"재사용 대기시간":20,"지속 시간":null,"범위":2,"대상 종류":"전자 장치","deviceKinds":["camera"]}</t>
   </si>
   <si>
     <t>방어구 스펙</t>
@@ -1853,7 +1853,7 @@
     <t>해킹 -1</t>
   </si>
   <si>
-    <t>{"유형":"임시 차단막","시간 비용":5,"재사용 대기시간":20,"지속 시간":10,"범위":1,"대상 종류":"통로"}</t>
+    <t>{"유형":"임시 차단막","시간 비용":3,"재사용 대기시간":20,"지속 시간":10,"범위":1,"대상 종류":"통로"}</t>
   </si>
   <si>
     <t>module_spatial</t>
@@ -1865,7 +1865,7 @@
     <t>지각 +2</t>
   </si>
   <si>
-    <t>{"유형":"스냅샷 스캔","시간 비용":5,"재사용 대기시간":20,"지속 시간":null,"범위":2,"대상 종류":"노드 내부"}</t>
+    <t>{"유형":"스냅샷 스캔","시간 비용":3,"재사용 대기시간":20,"지속 시간":null,"범위":2,"대상 종류":"노드 내부"}</t>
   </si>
   <si>
     <t>module_emp</t>
@@ -1880,7 +1880,7 @@
     <t>해킹 +2, 기만 +1, 지각 -1</t>
   </si>
   <si>
-    <t>{"유형":"원격 침투","시간 비용":5,"재사용 대기시간":20,"지속 시간":10,"범위":2,"대상 종류":"전자 장치"}</t>
+    <t>{"유형":"원격 침투","시간 비용":3,"재사용 대기시간":20,"지속 시간":10,"범위":2,"대상 종류":"전자 장치"}</t>
   </si>
   <si>
     <t>module_sandevistan</t>
@@ -2750,7 +2750,7 @@
     <t>EXIT_ACTIVATE_TIME_BY_HACKING</t>
   </si>
   <si>
-    <t>[9,9,9,8,7,6,4]</t>
+    <t>[5,5,5,4,4,3,2]</t>
   </si>
   <si>
     <t>EXIT_OPEN_WINDOW</t>
@@ -2948,7 +2948,7 @@
     <t>PRIZE_FARM_TIME</t>
   </si>
   <si>
-    <t>{"일반":10,"정예":13}</t>
+    <t>{"일반":5,"정예":7}</t>
   </si>
   <si>
     <t>PRIZE_OPTION_COUNT</t>
@@ -3092,7 +3092,7 @@
     <t>TRACE_CLEANUP_TIME_BY_PERCEPTION</t>
   </si>
   <si>
-    <t>[8,8,7,6,5,4,4]</t>
+    <t>[4,4,4,3,3,2,2]</t>
   </si>
   <si>
     <t>WAIT_BATCH_MAX_TICKS</t>
@@ -4220,7 +4220,7 @@
         <v>123</v>
       </c>
       <c r="C41" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>124</v>
@@ -4237,7 +4237,7 @@
         <v>125</v>
       </c>
       <c r="C42" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>126</v>
@@ -8129,7 +8129,7 @@
         <v>856</v>
       </c>
       <c r="C15" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>67</v>
@@ -8171,7 +8171,7 @@
         <v>860</v>
       </c>
       <c r="C18" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>67</v>
@@ -8213,7 +8213,7 @@
         <v>864</v>
       </c>
       <c r="C21" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>67</v>
@@ -8297,7 +8297,7 @@
         <v>870</v>
       </c>
       <c r="C27" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>67</v>
@@ -8465,7 +8465,7 @@
         <v>889</v>
       </c>
       <c r="C39" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>67</v>
@@ -8479,7 +8479,7 @@
         <v>890</v>
       </c>
       <c r="C40" s="6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>67</v>
@@ -8507,7 +8507,7 @@
         <v>892</v>
       </c>
       <c r="C42" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>67</v>
@@ -8521,7 +8521,7 @@
         <v>893</v>
       </c>
       <c r="C43" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>67</v>
@@ -8535,7 +8535,7 @@
         <v>894</v>
       </c>
       <c r="C44" s="6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>67</v>
@@ -8549,7 +8549,7 @@
         <v>895</v>
       </c>
       <c r="C45" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>67</v>
@@ -8829,7 +8829,7 @@
         <v>918</v>
       </c>
       <c r="C65" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>67</v>
@@ -8899,7 +8899,7 @@
         <v>924</v>
       </c>
       <c r="C70" s="6">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>67</v>
@@ -8927,7 +8927,7 @@
         <v>926</v>
       </c>
       <c r="C72" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>67</v>
@@ -8997,7 +8997,7 @@
         <v>931</v>
       </c>
       <c r="C77" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>67</v>
@@ -9011,7 +9011,7 @@
         <v>932</v>
       </c>
       <c r="C78" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>67</v>
@@ -9053,7 +9053,7 @@
         <v>936</v>
       </c>
       <c r="C81" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>67</v>
@@ -9389,7 +9389,7 @@
         <v>969</v>
       </c>
       <c r="C105" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>67</v>
@@ -9795,7 +9795,7 @@
         <v>1008</v>
       </c>
       <c r="C134" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>67</v>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -218,10 +218,10 @@
     <t>총 노드</t>
   </si>
   <si>
-    <t>90~124</t>
-  </si>
-  <si>
-    <t>뽑힌 구역 합. 구역별 입구·관리동 34 / 실험동 28 / 격납고·물류창고 14 / 보안·격리동 24 / 동력·정비동 26 / 폐기물 처리장 30 / 통신·관제탑 18 / 거주동 32</t>
+    <t>180~248</t>
+  </si>
+  <si>
+    <t>뽑힌 구역 합. 구역별 입구·관리동 68 / 실험동 56 / 격납고·물류창고 28 / 보안·격리동 48 / 동력·정비동 52 / 폐기물 처리장 60 / 통신·관제탑 36 / 거주동 64</t>
   </si>
   <si>
     <t>src/data/facilityLayout.js</t>
@@ -3074,7 +3074,7 @@
     <t>SECTOR_LAYOUTS</t>
   </si>
   <si>
-    <t>{"entrance":{"archetype":"grid","nodeCount":34,"corridorRatio":0.45,"roomTypes":[{"수치":"office","weight":60},{"수치":"watch","weight":15},{"수치":"utility","weight":15},{"수치":"refuge","weight":10}]},"labs":{"archetype":"chain","nodeCount":28,"corridorRatio":0.3,"roomTypes":[{"수치":"vault","weight":45},{"수치":"office","weight":35},{"수치":"utility","weight":20}]},"hangar":{"archetype":"hall","nodeCount":14,"corridorRatio":0.25,"roomTypes":[{"수치":"office","weight":50},{"수치":"utility","weight":35},{"수치":"watch","weight":15}]},"security":{"archetype":"grid","nodeCount":24,"corridorRatio":0.35,"roomTypes":[{"수치":"watch","weight":40},{"수치":"office","weight":35},{"수치":"vault","weight":25}]},"파워":{"archetype":"radial","nodeCount":26,"corridorRatio":0.45,"roomTypes":[{"수치":"utility","weight":60},{"수치":"office","weight":25},{"수치":"vault","weight":15}]},"waste":{"archetype":"dual","nodeCount":30,"corridorRatio":0.4,"roomTypes":[{"수치":"utility","weight":50},{"수치":"office","weight":30},{"수치":"refuge","weight":20}]},"comms":{"archetype":"tower","nodeCount":18,"corridorRatio":0.35,"roomTypes":[{"수치":"watch","weight":45},{"수치":"office","weight":35},{"수치":"utility","weight":20}]},"residential":{"archetype":"chain","nodeCount":32,"corridorRatio":0.5,"roomTypes":[{"수치":"refuge","weight":45},{"수치":"office","weight":40},{"수치":"utility","weight":15}]}}</t>
+    <t>{"entrance":{"archetype":"grid","nodeCount":68,"corridorRatio":0.45,"roomTypes":[{"수치":"office","weight":60},{"수치":"watch","weight":15},{"수치":"utility","weight":15},{"수치":"refuge","weight":10}]},"labs":{"archetype":"chain","nodeCount":56,"corridorRatio":0.3,"roomTypes":[{"수치":"vault","weight":45},{"수치":"office","weight":35},{"수치":"utility","weight":20}]},"hangar":{"archetype":"hall","nodeCount":28,"corridorRatio":0.25,"roomTypes":[{"수치":"office","weight":50},{"수치":"utility","weight":35},{"수치":"watch","weight":15}]},"security":{"archetype":"grid","nodeCount":48,"corridorRatio":0.35,"roomTypes":[{"수치":"watch","weight":40},{"수치":"office","weight":35},{"수치":"vault","weight":25}]},"파워":{"archetype":"radial","nodeCount":52,"corridorRatio":0.45,"roomTypes":[{"수치":"utility","weight":60},{"수치":"office","weight":25},{"수치":"vault","weight":15}]},"waste":{"archetype":"dual","nodeCount":60,"corridorRatio":0.4,"roomTypes":[{"수치":"utility","weight":50},{"수치":"office","weight":30},{"수치":"refuge","weight":20}]},"comms":{"archetype":"tower","nodeCount":36,"corridorRatio":0.35,"roomTypes":[{"수치":"watch","weight":45},{"수치":"office","weight":35},{"수치":"utility","weight":20}]},"residential":{"archetype":"chain","nodeCount":64,"corridorRatio":0.5,"roomTypes":[{"수치":"refuge","weight":45},{"수치":"office","weight":40},{"수치":"utility","weight":15}]}}</t>
   </si>
   <si>
     <t>SECTOR_NAMES</t>
@@ -3128,7 +3128,7 @@
     <t>THREAT_COUNT_BY_SECTOR</t>
   </si>
   <si>
-    <t>{"entrance":3,"labs":3,"hangar":3,"security":4,"파워":5,"waste":4,"comms":3,"residential":3}</t>
+    <t>{"entrance":6,"labs":6,"hangar":6,"security":8,"파워":10,"waste":8,"comms":6,"residential":6}</t>
   </si>
   <si>
     <t>THREAT_GROUP_SIZE_WEIGHTS</t>
@@ -9635,7 +9635,7 @@
         <v>977</v>
       </c>
       <c r="C101" s="5">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>67</v>
@@ -10055,7 +10055,7 @@
         <v>1020</v>
       </c>
       <c r="C131" s="5">
-        <v>280</v>
+        <v>396</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>67</v>
@@ -10069,7 +10069,7 @@
         <v>1021</v>
       </c>
       <c r="C132" s="6">
-        <v>900</v>
+        <v>1273</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>67</v>
@@ -10111,7 +10111,7 @@
         <v>1025</v>
       </c>
       <c r="C135" s="5">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D135" s="5" t="s">
         <v>67</v>
@@ -10125,7 +10125,7 @@
         <v>1026</v>
       </c>
       <c r="C136" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>67</v>
@@ -10335,7 +10335,7 @@
         <v>1045</v>
       </c>
       <c r="C151" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>67</v>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3235" uniqueCount="1044">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3247" uniqueCount="1048">
   <si>
     <t>현재 구현 규칙</t>
   </si>
@@ -2756,6 +2756,9 @@
     <t>CROSS_SECTOR_SPECIAL_EDGES_MIN</t>
   </si>
   <si>
+    <t>CURRENT_NODE_DETAIL_LEVEL</t>
+  </si>
+  <si>
     <t>DEEPEST_SECTOR_ID</t>
   </si>
   <si>
@@ -2843,6 +2846,12 @@
     <t>FORCE_TIER1_TIME</t>
   </si>
   <si>
+    <t>FREE_FAR_OBSERVATION_DETAIL_LEVEL</t>
+  </si>
+  <si>
+    <t>FREE_FAR_VIEW_HOPS</t>
+  </si>
+  <si>
     <t>FREE_OBSERVATION_DETAIL_LEVEL</t>
   </si>
   <si>
@@ -2969,10 +2978,13 @@
     <t>[{"수치":1,"weight":45},{"수치":2,"weight":35},{"수치":3,"weight":20}]</t>
   </si>
   <si>
+    <t>PERCEPTION_FREE_FAR_VIEW_MIN</t>
+  </si>
+  <si>
     <t>PERCEPTION_INFO_TABLE</t>
   </si>
   <si>
-    <t>[{"level":0,"reconHops":1,"threat":["presence"],"extra":[]},{"level":0,"reconHops":1,"threat":["presence"],"extra":[]},{"level":1,"reconHops":1,"threat":["presence","size"],"extra":["prizeGrade"]},{"level":2,"reconHops":1,"threat":["presence","size","mode"],"extra":["prizeGrade","prizeAxis"]},{"level":3,"reconHops":1,"threat":["presence","size","mode","alert","nextMove"],"extra":["prizeGrade","prizeAxis","concealment"]},{"level":4,"reconHops":2,"threat":["presence","size","mode","alert","nextMove","composition"],"extra":["prizeGrade","prizeAxis","concealment"]},{"level":5,"reconHops":2,"threat":["presence","size","mode","alert","nextMove","composition","patrolNext"],"extra":["prizeGrade","prizeAxis","concealment","evidence"]}]</t>
+    <t>[{"level":1,"reconHops":1,"threat":["presence","횟수","mode"],"extra":[]},{"level":1,"reconHops":1,"threat":["presence","횟수","mode"],"extra":[]},{"level":2,"reconHops":1,"threat":["presence","횟수","mode","size"],"extra":["prizeGrade"]},{"level":3,"reconHops":1,"threat":["presence","횟수","mode","size"],"extra":["prizeGrade","prizeAxis"]},{"level":4,"reconHops":1,"threat":["presence","횟수","mode","size","alert","nextMove"],"extra":["prizeGrade","prizeAxis","concealment"]},{"level":5,"reconHops":2,"threat":["presence","횟수","mode","size","alert","nextMove","composition"],"extra":["prizeGrade","prizeAxis","concealment"]},{"level":6,"reconHops":2,"threat":["presence","횟수","mode","size","alert","nextMove","composition","patrolNext"],"extra":["prizeGrade","prizeAxis","concealment","evidence"]}]</t>
   </si>
   <si>
     <t>PERCEPTION_WAIT_OBSERVATION_MIN</t>
@@ -8188,7 +8200,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D152"/>
+  <dimension ref="A1:D156"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -8837,8 +8849,8 @@
       <c r="B48" s="6" t="s">
         <v>911</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>303</v>
+      <c r="C48" s="6">
+        <v>2</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>67</v>
@@ -8846,13 +8858,13 @@
     </row>
     <row r="49" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>912</v>
       </c>
-      <c r="C49" s="5">
-        <v>2</v>
+      <c r="C49" s="5" t="s">
+        <v>303</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>67</v>
@@ -8860,7 +8872,7 @@
     </row>
     <row r="50" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>885</v>
+        <v>853</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>913</v>
@@ -8879,8 +8891,8 @@
       <c r="B51" s="5" t="s">
         <v>914</v>
       </c>
-      <c r="C51" s="5" t="s">
-        <v>915</v>
+      <c r="C51" s="5">
+        <v>2</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>67</v>
@@ -8888,13 +8900,13 @@
     </row>
     <row r="52" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>859</v>
+        <v>885</v>
       </c>
       <c r="B52" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="C52" s="6" t="s">
         <v>916</v>
-      </c>
-      <c r="C52" s="6">
-        <v>1</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>67</v>
@@ -8902,13 +8914,13 @@
     </row>
     <row r="53" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>917</v>
       </c>
       <c r="C53" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>67</v>
@@ -8930,13 +8942,13 @@
     </row>
     <row r="55" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>885</v>
+        <v>853</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>919</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>343</v>
+      <c r="C55" s="5">
+        <v>2</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>67</v>
@@ -8944,13 +8956,13 @@
     </row>
     <row r="56" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>99</v>
+        <v>885</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>920</v>
       </c>
-      <c r="C56" s="6">
-        <v>50</v>
+      <c r="C56" s="6" t="s">
+        <v>343</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>67</v>
@@ -8963,8 +8975,8 @@
       <c r="B57" s="5" t="s">
         <v>921</v>
       </c>
-      <c r="C57" s="5" t="s">
-        <v>922</v>
+      <c r="C57" s="5">
+        <v>50</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>67</v>
@@ -8975,10 +8987,10 @@
         <v>99</v>
       </c>
       <c r="B58" s="6" t="s">
+        <v>922</v>
+      </c>
+      <c r="C58" s="6" t="s">
         <v>923</v>
-      </c>
-      <c r="C58" s="6">
-        <v>5</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>67</v>
@@ -8992,7 +9004,7 @@
         <v>924</v>
       </c>
       <c r="C59" s="5">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>67</v>
@@ -9000,13 +9012,13 @@
     </row>
     <row r="60" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>853</v>
+        <v>99</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>925</v>
       </c>
       <c r="C60" s="6">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>67</v>
@@ -9019,8 +9031,8 @@
       <c r="B61" s="5" t="s">
         <v>926</v>
       </c>
-      <c r="C61" s="5" t="s">
-        <v>927</v>
+      <c r="C61" s="5">
+        <v>1</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>67</v>
@@ -9031,10 +9043,10 @@
         <v>853</v>
       </c>
       <c r="B62" s="6" t="s">
+        <v>927</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>928</v>
-      </c>
-      <c r="C62" s="6">
-        <v>1</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>67</v>
@@ -9048,7 +9060,7 @@
         <v>929</v>
       </c>
       <c r="C63" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>67</v>
@@ -9062,7 +9074,7 @@
         <v>930</v>
       </c>
       <c r="C64" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>67</v>
@@ -9084,13 +9096,13 @@
     </row>
     <row r="66" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>885</v>
+        <v>853</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>932</v>
       </c>
       <c r="C66" s="6">
-        <v>256</v>
+        <v>2</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>67</v>
@@ -9098,13 +9110,13 @@
     </row>
     <row r="67" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>851</v>
+        <v>885</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>933</v>
       </c>
       <c r="C67" s="5">
-        <v>3</v>
+        <v>256</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>67</v>
@@ -9112,13 +9124,13 @@
     </row>
     <row r="68" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>885</v>
+        <v>851</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>934</v>
       </c>
-      <c r="C68" s="6" t="s">
-        <v>935</v>
+      <c r="C68" s="6">
+        <v>3</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>67</v>
@@ -9129,10 +9141,10 @@
         <v>885</v>
       </c>
       <c r="B69" s="5" t="s">
+        <v>935</v>
+      </c>
+      <c r="C69" s="5" t="s">
         <v>936</v>
-      </c>
-      <c r="C69" s="5">
-        <v>2</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>67</v>
@@ -9146,7 +9158,7 @@
         <v>937</v>
       </c>
       <c r="C70" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>67</v>
@@ -9154,13 +9166,13 @@
     </row>
     <row r="71" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>853</v>
+        <v>885</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>938</v>
       </c>
       <c r="C71" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>67</v>
@@ -9168,13 +9180,13 @@
     </row>
     <row r="72" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>939</v>
       </c>
       <c r="C72" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>67</v>
@@ -9182,13 +9194,13 @@
     </row>
     <row r="73" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>885</v>
+        <v>859</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>940</v>
       </c>
       <c r="C73" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>67</v>
@@ -9196,13 +9208,13 @@
     </row>
     <row r="74" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>851</v>
+        <v>885</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>941</v>
       </c>
       <c r="C74" s="6">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>67</v>
@@ -9210,13 +9222,13 @@
     </row>
     <row r="75" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>872</v>
+        <v>885</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>942</v>
       </c>
       <c r="C75" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>67</v>
@@ -9224,13 +9236,13 @@
     </row>
     <row r="76" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>853</v>
+        <v>885</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>943</v>
       </c>
       <c r="C76" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>67</v>
@@ -9238,13 +9250,13 @@
     </row>
     <row r="77" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>872</v>
+        <v>851</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>944</v>
       </c>
       <c r="C77" s="5">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>67</v>
@@ -9258,7 +9270,7 @@
         <v>945</v>
       </c>
       <c r="C78" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>67</v>
@@ -9266,13 +9278,13 @@
     </row>
     <row r="79" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>946</v>
       </c>
-      <c r="C79" s="5" t="s">
-        <v>947</v>
+      <c r="C79" s="5">
+        <v>2</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>67</v>
@@ -9280,13 +9292,13 @@
     </row>
     <row r="80" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>853</v>
+        <v>872</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C80" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>67</v>
@@ -9294,13 +9306,13 @@
     </row>
     <row r="81" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>859</v>
+        <v>872</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C81" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>67</v>
@@ -9308,13 +9320,13 @@
     </row>
     <row r="82" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>885</v>
+        <v>851</v>
       </c>
       <c r="B82" s="6" t="s">
+        <v>949</v>
+      </c>
+      <c r="C82" s="6" t="s">
         <v>950</v>
-      </c>
-      <c r="C82" s="6">
-        <v>1</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>67</v>
@@ -9322,13 +9334,13 @@
     </row>
     <row r="83" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>951</v>
       </c>
       <c r="C83" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>67</v>
@@ -9336,13 +9348,13 @@
     </row>
     <row r="84" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>885</v>
+        <v>859</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>952</v>
       </c>
       <c r="C84" s="6">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>67</v>
@@ -9356,7 +9368,7 @@
         <v>953</v>
       </c>
       <c r="C85" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>67</v>
@@ -9364,7 +9376,7 @@
     </row>
     <row r="86" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>885</v>
+        <v>859</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>954</v>
@@ -9384,7 +9396,7 @@
         <v>955</v>
       </c>
       <c r="C87" s="5">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>67</v>
@@ -9398,7 +9410,7 @@
         <v>956</v>
       </c>
       <c r="C88" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>67</v>
@@ -9406,13 +9418,13 @@
     </row>
     <row r="89" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>872</v>
+        <v>885</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>957</v>
       </c>
-      <c r="C89" s="5" t="s">
-        <v>958</v>
+      <c r="C89" s="5">
+        <v>3</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>67</v>
@@ -9423,10 +9435,10 @@
         <v>885</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C90" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>67</v>
@@ -9434,13 +9446,13 @@
     </row>
     <row r="91" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>853</v>
+        <v>885</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C91" s="5">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>67</v>
@@ -9448,13 +9460,13 @@
     </row>
     <row r="92" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
+        <v>872</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>960</v>
+      </c>
+      <c r="C92" s="6" t="s">
         <v>961</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>962</v>
-      </c>
-      <c r="C92" s="6">
-        <v>0.01</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>67</v>
@@ -9462,13 +9474,13 @@
     </row>
     <row r="93" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>961</v>
+        <v>885</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="C93" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>67</v>
@@ -9476,13 +9488,13 @@
     </row>
     <row r="94" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>961</v>
+        <v>853</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C94" s="6">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>67</v>
@@ -9490,13 +9502,13 @@
     </row>
     <row r="95" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>851</v>
+        <v>964</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>965</v>
       </c>
-      <c r="C95" s="5" t="s">
-        <v>966</v>
+      <c r="C95" s="5">
+        <v>0.01</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>67</v>
@@ -9504,13 +9516,13 @@
     </row>
     <row r="96" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>853</v>
+        <v>964</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>967</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>968</v>
+        <v>966</v>
+      </c>
+      <c r="C96" s="6">
+        <v>4</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>67</v>
@@ -9518,13 +9530,13 @@
     </row>
     <row r="97" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>851</v>
+        <v>964</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C97" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D97" s="5" t="s">
         <v>67</v>
@@ -9535,10 +9547,10 @@
         <v>851</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>970</v>
-      </c>
-      <c r="C98" s="6">
-        <v>2</v>
+        <v>968</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>969</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>67</v>
@@ -9546,13 +9558,13 @@
     </row>
     <row r="99" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B99" s="5" t="s">
+        <v>970</v>
+      </c>
+      <c r="C99" s="5" t="s">
         <v>971</v>
-      </c>
-      <c r="C99" s="5">
-        <v>0.17</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>67</v>
@@ -9566,7 +9578,7 @@
         <v>972</v>
       </c>
       <c r="C100" s="6">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>67</v>
@@ -9579,8 +9591,8 @@
       <c r="B101" s="5" t="s">
         <v>973</v>
       </c>
-      <c r="C101" s="5" t="s">
-        <v>974</v>
+      <c r="C101" s="5">
+        <v>2</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>67</v>
@@ -9591,10 +9603,10 @@
         <v>851</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>975</v>
-      </c>
-      <c r="C102" s="6" t="s">
-        <v>976</v>
+        <v>974</v>
+      </c>
+      <c r="C102" s="6">
+        <v>0.17</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>67</v>
@@ -9602,13 +9614,13 @@
     </row>
     <row r="103" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C103" s="5">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>67</v>
@@ -9616,13 +9628,13 @@
     </row>
     <row r="104" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>67</v>
@@ -9630,13 +9642,13 @@
     </row>
     <row r="105" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>961</v>
+        <v>851</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>67</v>
@@ -9644,13 +9656,13 @@
     </row>
     <row r="106" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>885</v>
+        <v>853</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>982</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>983</v>
+        <v>980</v>
+      </c>
+      <c r="C106" s="6">
+        <v>5</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>67</v>
@@ -9658,13 +9670,13 @@
     </row>
     <row r="107" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>984</v>
-      </c>
-      <c r="C107" s="5">
-        <v>2</v>
+        <v>981</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>982</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>67</v>
@@ -9672,13 +9684,13 @@
     </row>
     <row r="108" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>885</v>
+        <v>964</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>985</v>
-      </c>
-      <c r="C108" s="6">
-        <v>30</v>
+        <v>983</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>984</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>67</v>
@@ -9686,13 +9698,13 @@
     </row>
     <row r="109" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>853</v>
+        <v>885</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C109" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>67</v>
@@ -9703,10 +9715,10 @@
         <v>885</v>
       </c>
       <c r="B110" s="6" t="s">
+        <v>986</v>
+      </c>
+      <c r="C110" s="6" t="s">
         <v>987</v>
-      </c>
-      <c r="C110" s="6">
-        <v>3</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>67</v>
@@ -9714,13 +9726,13 @@
     </row>
     <row r="111" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>885</v>
+        <v>859</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>988</v>
       </c>
-      <c r="C111" s="5" t="s">
-        <v>989</v>
+      <c r="C111" s="5">
+        <v>2</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>67</v>
@@ -9728,13 +9740,13 @@
     </row>
     <row r="112" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
-        <v>853</v>
+        <v>885</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>990</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>991</v>
+        <v>989</v>
+      </c>
+      <c r="C112" s="6">
+        <v>30</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>67</v>
@@ -9742,13 +9754,13 @@
     </row>
     <row r="113" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>992</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>993</v>
+        <v>990</v>
+      </c>
+      <c r="C113" s="5">
+        <v>3</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>67</v>
@@ -9759,7 +9771,7 @@
         <v>885</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="C114" s="6">
         <v>3</v>
@@ -9770,13 +9782,13 @@
     </row>
     <row r="115" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>851</v>
+        <v>885</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>67</v>
@@ -9784,13 +9796,13 @@
     </row>
     <row r="116" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
-        <v>885</v>
+        <v>853</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>67</v>
@@ -9798,13 +9810,13 @@
     </row>
     <row r="117" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>999</v>
-      </c>
-      <c r="C117" s="5">
-        <v>2</v>
+        <v>996</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>997</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>67</v>
@@ -9815,10 +9827,10 @@
         <v>885</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="C118" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>67</v>
@@ -9826,13 +9838,13 @@
     </row>
     <row r="119" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>1001</v>
-      </c>
-      <c r="C119" s="5">
-        <v>180</v>
+        <v>999</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>1000</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>67</v>
@@ -9840,13 +9852,13 @@
     </row>
     <row r="120" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
-        <v>859</v>
+        <v>885</v>
       </c>
       <c r="B120" s="6" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C120" s="6" t="s">
         <v>1002</v>
-      </c>
-      <c r="C120" s="6">
-        <v>90</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>67</v>
@@ -9854,13 +9866,13 @@
     </row>
     <row r="121" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>99</v>
+        <v>853</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>1003</v>
       </c>
       <c r="C121" s="5">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>67</v>
@@ -9868,13 +9880,13 @@
     </row>
     <row r="122" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
-        <v>851</v>
+        <v>885</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>1004</v>
       </c>
       <c r="C122" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>67</v>
@@ -9882,13 +9894,13 @@
     </row>
     <row r="123" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>1005</v>
       </c>
       <c r="C123" s="5">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>67</v>
@@ -9896,13 +9908,13 @@
     </row>
     <row r="124" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>1006</v>
       </c>
-      <c r="C124" s="6" t="s">
-        <v>1007</v>
+      <c r="C124" s="6">
+        <v>90</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>67</v>
@@ -9910,13 +9922,13 @@
     </row>
     <row r="125" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>853</v>
+        <v>99</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>1008</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>968</v>
+        <v>1007</v>
+      </c>
+      <c r="C125" s="5">
+        <v>80</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>67</v>
@@ -9927,10 +9939,10 @@
         <v>851</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C126" s="6" t="s">
-        <v>1010</v>
+        <v>1008</v>
+      </c>
+      <c r="C126" s="6">
+        <v>4</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>67</v>
@@ -9938,13 +9950,13 @@
     </row>
     <row r="127" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>1012</v>
+        <v>1009</v>
+      </c>
+      <c r="C127" s="5">
+        <v>2</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>67</v>
@@ -9952,13 +9964,13 @@
     </row>
     <row r="128" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>1013</v>
-      </c>
-      <c r="C128" s="6">
-        <v>280</v>
+        <v>1010</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>1011</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>67</v>
@@ -9966,13 +9978,13 @@
     </row>
     <row r="129" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C129" s="5">
-        <v>900</v>
+        <v>1012</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>971</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>67</v>
@@ -9983,10 +9995,10 @@
         <v>851</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>67</v>
@@ -9997,10 +10009,10 @@
         <v>851</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C131" s="5">
-        <v>0.4</v>
+        <v>1015</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>1016</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>67</v>
@@ -10011,10 +10023,10 @@
         <v>851</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="C132" s="6">
-        <v>6</v>
+        <v>280</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>67</v>
@@ -10025,10 +10037,10 @@
         <v>851</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="C133" s="5">
-        <v>4</v>
+        <v>900</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>67</v>
@@ -10039,10 +10051,10 @@
         <v>851</v>
       </c>
       <c r="B134" s="6" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C134" s="6" t="s">
         <v>1020</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>1021</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>67</v>
@@ -10050,13 +10062,13 @@
     </row>
     <row r="135" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
-        <v>872</v>
+        <v>851</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="C135" s="5">
-        <v>-1</v>
+        <v>0.4</v>
       </c>
       <c r="D135" s="5" t="s">
         <v>67</v>
@@ -10064,13 +10076,13 @@
     </row>
     <row r="136" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
-        <v>885</v>
+        <v>851</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C136" s="6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>67</v>
@@ -10078,13 +10090,13 @@
     </row>
     <row r="137" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>885</v>
+        <v>851</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C137" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>67</v>
@@ -10092,13 +10104,13 @@
     </row>
     <row r="138" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B138" s="6" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C138" s="6" t="s">
         <v>1025</v>
-      </c>
-      <c r="C138" s="6">
-        <v>1</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>67</v>
@@ -10106,13 +10118,13 @@
     </row>
     <row r="139" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
-        <v>859</v>
+        <v>872</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>1026</v>
       </c>
       <c r="C139" s="5">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>67</v>
@@ -10120,13 +10132,13 @@
     </row>
     <row r="140" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
-        <v>853</v>
+        <v>885</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>1027</v>
       </c>
-      <c r="C140" s="6" t="s">
-        <v>1028</v>
+      <c r="C140" s="6">
+        <v>-1</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>67</v>
@@ -10134,13 +10146,13 @@
     </row>
     <row r="141" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
-        <v>853</v>
+        <v>885</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>1030</v>
+        <v>1028</v>
+      </c>
+      <c r="C141" s="5">
+        <v>1</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>67</v>
@@ -10151,10 +10163,10 @@
         <v>853</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C142" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>67</v>
@@ -10162,10 +10174,10 @@
     </row>
     <row r="143" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
-        <v>853</v>
+        <v>859</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="C143" s="5">
         <v>3</v>
@@ -10179,10 +10191,10 @@
         <v>853</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>67</v>
@@ -10193,10 +10205,10 @@
         <v>853</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C145" s="5">
-        <v>4</v>
+        <v>1033</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>1034</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>67</v>
@@ -10207,7 +10219,7 @@
         <v>853</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="C146" s="6">
         <v>2</v>
@@ -10218,10 +10230,10 @@
     </row>
     <row r="147" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="s">
-        <v>885</v>
+        <v>853</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C147" s="5">
         <v>3</v>
@@ -10232,13 +10244,13 @@
     </row>
     <row r="148" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
-        <v>885</v>
+        <v>853</v>
       </c>
       <c r="B148" s="6" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C148" s="6" t="s">
         <v>1038</v>
-      </c>
-      <c r="C148" s="6">
-        <v>4</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>67</v>
@@ -10246,13 +10258,13 @@
     </row>
     <row r="149" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
-        <v>885</v>
+        <v>853</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>1039</v>
       </c>
       <c r="C149" s="5">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>67</v>
@@ -10260,13 +10272,13 @@
     </row>
     <row r="150" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
-        <v>885</v>
+        <v>853</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>1040</v>
       </c>
-      <c r="C150" s="6" t="s">
-        <v>1041</v>
+      <c r="C150" s="6">
+        <v>2</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>67</v>
@@ -10274,13 +10286,13 @@
     </row>
     <row r="151" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
-        <v>859</v>
+        <v>885</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C151" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>67</v>
@@ -10288,20 +10300,76 @@
     </row>
     <row r="152" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
-        <v>859</v>
+        <v>885</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="C152" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D152" s="6" t="s">
         <v>67</v>
       </c>
     </row>
+    <row r="153" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="5" t="s">
+        <v>885</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C153" s="5">
+        <v>2.6</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="6" t="s">
+        <v>885</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D154" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="5" t="s">
+        <v>859</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C155" s="5">
+        <v>5</v>
+      </c>
+      <c r="D155" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="6" t="s">
+        <v>859</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C156" s="6">
+        <v>1</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:D152"/>
+  <autoFilter ref="A4:D156"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -341,7 +341,7 @@
     <t>A 비활성</t>
   </si>
   <si>
-    <t>이 시각 뒤로는 새 가동을 시작할 수 없다. 이미 시작된 가동 게이지와 열린 창은 끝까지 간다(ADR-0054)</t>
+    <t>이 시각 뒤로는 새 가동을 시작할 수 없다. 이미 시작된 가동 게이지와 열린 창은 끝까지 간다(ADR-0087)</t>
   </si>
   <si>
     <t>표준 출구 수</t>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3252" uniqueCount="1051">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3249" uniqueCount="1050">
   <si>
     <t>현재 구현 규칙</t>
   </si>
@@ -2862,9 +2862,6 @@
   </si>
   <si>
     <t>FREE_FAR_OBSERVATION_DETAIL_LEVEL</t>
-  </si>
-  <si>
-    <t>FREE_FAR_VIEW_HOPS</t>
   </si>
   <si>
     <t>FREE_OBSERVATION_DETAIL_LEVEL</t>
@@ -8243,7 +8240,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D155"/>
+  <dimension ref="A1:D154"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -9271,7 +9268,7 @@
         <v>947</v>
       </c>
       <c r="C75" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>67</v>
@@ -9279,13 +9276,13 @@
     </row>
     <row r="76" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>890</v>
+        <v>856</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>948</v>
       </c>
       <c r="C76" s="6">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>67</v>
@@ -9293,13 +9290,13 @@
     </row>
     <row r="77" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>856</v>
+        <v>877</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>949</v>
       </c>
       <c r="C77" s="5">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>67</v>
@@ -9307,13 +9304,13 @@
     </row>
     <row r="78" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>877</v>
+        <v>858</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>950</v>
       </c>
       <c r="C78" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>67</v>
@@ -9321,13 +9318,13 @@
     </row>
     <row r="79" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>951</v>
       </c>
       <c r="C79" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>67</v>
@@ -9349,13 +9346,13 @@
     </row>
     <row r="81" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>877</v>
+        <v>856</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>953</v>
       </c>
-      <c r="C81" s="5">
-        <v>3</v>
+      <c r="C81" s="5" t="s">
+        <v>954</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>67</v>
@@ -9363,13 +9360,13 @@
     </row>
     <row r="82" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>954</v>
-      </c>
-      <c r="C82" s="6" t="s">
         <v>955</v>
+      </c>
+      <c r="C82" s="6">
+        <v>0</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>67</v>
@@ -9377,13 +9374,13 @@
     </row>
     <row r="83" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>956</v>
       </c>
       <c r="C83" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>67</v>
@@ -9391,13 +9388,13 @@
     </row>
     <row r="84" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>864</v>
+        <v>890</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>957</v>
       </c>
       <c r="C84" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>67</v>
@@ -9405,13 +9402,13 @@
     </row>
     <row r="85" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>890</v>
+        <v>864</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>958</v>
       </c>
       <c r="C85" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>67</v>
@@ -9419,13 +9416,13 @@
     </row>
     <row r="86" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>864</v>
+        <v>890</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>959</v>
       </c>
       <c r="C86" s="6">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>67</v>
@@ -9439,7 +9436,7 @@
         <v>960</v>
       </c>
       <c r="C87" s="5">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>67</v>
@@ -9453,7 +9450,7 @@
         <v>961</v>
       </c>
       <c r="C88" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>67</v>
@@ -9467,7 +9464,7 @@
         <v>962</v>
       </c>
       <c r="C89" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>67</v>
@@ -9481,7 +9478,7 @@
         <v>963</v>
       </c>
       <c r="C90" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>67</v>
@@ -9495,7 +9492,7 @@
         <v>964</v>
       </c>
       <c r="C91" s="5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>67</v>
@@ -9503,13 +9500,13 @@
     </row>
     <row r="92" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
-        <v>890</v>
+        <v>858</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>965</v>
       </c>
       <c r="C92" s="6">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>67</v>
@@ -9517,13 +9514,13 @@
     </row>
     <row r="93" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>858</v>
+        <v>966</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C93" s="5">
-        <v>15</v>
+        <v>0.01</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>67</v>
@@ -9531,13 +9528,13 @@
     </row>
     <row r="94" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>968</v>
       </c>
       <c r="C94" s="6">
-        <v>0.01</v>
+        <v>4</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>67</v>
@@ -9545,13 +9542,13 @@
     </row>
     <row r="95" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>969</v>
       </c>
       <c r="C95" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>67</v>
@@ -9559,13 +9556,13 @@
     </row>
     <row r="96" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
-        <v>967</v>
+        <v>856</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>970</v>
       </c>
-      <c r="C96" s="6">
-        <v>2</v>
+      <c r="C96" s="6" t="s">
+        <v>971</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>67</v>
@@ -9573,13 +9570,13 @@
     </row>
     <row r="97" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="D97" s="5" t="s">
         <v>67</v>
@@ -9587,13 +9584,13 @@
     </row>
     <row r="98" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>973</v>
-      </c>
-      <c r="C98" s="6" t="s">
         <v>974</v>
+      </c>
+      <c r="C98" s="6">
+        <v>3</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>67</v>
@@ -9607,7 +9604,7 @@
         <v>975</v>
       </c>
       <c r="C99" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>67</v>
@@ -9621,7 +9618,7 @@
         <v>976</v>
       </c>
       <c r="C100" s="6">
-        <v>2</v>
+        <v>0.12</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>67</v>
@@ -9635,7 +9632,7 @@
         <v>977</v>
       </c>
       <c r="C101" s="5">
-        <v>0.12</v>
+        <v>24</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>67</v>
@@ -9648,8 +9645,8 @@
       <c r="B102" s="6" t="s">
         <v>978</v>
       </c>
-      <c r="C102" s="6">
-        <v>24</v>
+      <c r="C102" s="6" t="s">
+        <v>979</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>67</v>
@@ -9660,10 +9657,10 @@
         <v>856</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>67</v>
@@ -9671,13 +9668,13 @@
     </row>
     <row r="104" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>981</v>
-      </c>
-      <c r="C104" s="6" t="s">
         <v>982</v>
+      </c>
+      <c r="C104" s="6">
+        <v>5</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>67</v>
@@ -9690,8 +9687,8 @@
       <c r="B105" s="5" t="s">
         <v>983</v>
       </c>
-      <c r="C105" s="5">
-        <v>5</v>
+      <c r="C105" s="5" t="s">
+        <v>984</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>67</v>
@@ -9699,13 +9696,13 @@
     </row>
     <row r="106" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>858</v>
+        <v>966</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>67</v>
@@ -9713,13 +9710,13 @@
     </row>
     <row r="107" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>967</v>
+        <v>890</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>986</v>
-      </c>
-      <c r="C107" s="5" t="s">
         <v>987</v>
+      </c>
+      <c r="C107" s="5">
+        <v>2</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>67</v>
@@ -9732,8 +9729,8 @@
       <c r="B108" s="6" t="s">
         <v>988</v>
       </c>
-      <c r="C108" s="6">
-        <v>2</v>
+      <c r="C108" s="6" t="s">
+        <v>989</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>67</v>
@@ -9741,13 +9738,13 @@
     </row>
     <row r="109" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>890</v>
+        <v>864</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>989</v>
-      </c>
-      <c r="C109" s="5" t="s">
         <v>990</v>
+      </c>
+      <c r="C109" s="5">
+        <v>2</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>67</v>
@@ -9755,13 +9752,13 @@
     </row>
     <row r="110" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
-        <v>864</v>
+        <v>890</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>991</v>
       </c>
       <c r="C110" s="6">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>67</v>
@@ -9769,13 +9766,13 @@
     </row>
     <row r="111" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>890</v>
+        <v>858</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>992</v>
       </c>
       <c r="C111" s="5">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>67</v>
@@ -9783,7 +9780,7 @@
     </row>
     <row r="112" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
-        <v>858</v>
+        <v>890</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>993</v>
@@ -9802,8 +9799,8 @@
       <c r="B113" s="5" t="s">
         <v>994</v>
       </c>
-      <c r="C113" s="5">
-        <v>3</v>
+      <c r="C113" s="5" t="s">
+        <v>995</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>67</v>
@@ -9811,13 +9808,13 @@
     </row>
     <row r="114" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
-        <v>890</v>
+        <v>858</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>67</v>
@@ -9825,13 +9822,13 @@
     </row>
     <row r="115" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>67</v>
@@ -9839,13 +9836,13 @@
     </row>
     <row r="116" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
-        <v>864</v>
+        <v>890</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>999</v>
-      </c>
-      <c r="C116" s="6" t="s">
         <v>1000</v>
+      </c>
+      <c r="C116" s="6">
+        <v>3</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>67</v>
@@ -9853,13 +9850,13 @@
     </row>
     <row r="117" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>890</v>
+        <v>856</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>1001</v>
       </c>
-      <c r="C117" s="5">
-        <v>3</v>
+      <c r="C117" s="5" t="s">
+        <v>1002</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>67</v>
@@ -9867,13 +9864,13 @@
     </row>
     <row r="118" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
-        <v>856</v>
+        <v>890</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>67</v>
@@ -9881,13 +9878,13 @@
     </row>
     <row r="119" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>890</v>
+        <v>858</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C119" s="5" t="s">
         <v>1005</v>
+      </c>
+      <c r="C119" s="5">
+        <v>2</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>67</v>
@@ -9895,13 +9892,13 @@
     </row>
     <row r="120" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
-        <v>858</v>
+        <v>890</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>1006</v>
       </c>
       <c r="C120" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>67</v>
@@ -9909,13 +9906,13 @@
     </row>
     <row r="121" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>890</v>
+        <v>864</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>1007</v>
       </c>
       <c r="C121" s="5">
-        <v>6</v>
+        <v>180</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>67</v>
@@ -9929,7 +9926,7 @@
         <v>1008</v>
       </c>
       <c r="C122" s="6">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>67</v>
@@ -9937,13 +9934,13 @@
     </row>
     <row r="123" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>864</v>
+        <v>104</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>1009</v>
       </c>
       <c r="C123" s="5">
-        <v>90</v>
+        <v>240</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>67</v>
@@ -9951,13 +9948,13 @@
     </row>
     <row r="124" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
-        <v>104</v>
+        <v>856</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>1010</v>
       </c>
       <c r="C124" s="6">
-        <v>240</v>
+        <v>4</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>67</v>
@@ -9965,13 +9962,13 @@
     </row>
     <row r="125" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>1011</v>
       </c>
       <c r="C125" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>67</v>
@@ -9984,8 +9981,8 @@
       <c r="B126" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="C126" s="6">
-        <v>2</v>
+      <c r="C126" s="6" t="s">
+        <v>1013</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>67</v>
@@ -9996,10 +9993,10 @@
         <v>858</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>1014</v>
+        <v>973</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>67</v>
@@ -10007,13 +10004,13 @@
     </row>
     <row r="128" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>1015</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>974</v>
+        <v>1016</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>67</v>
@@ -10024,10 +10021,10 @@
         <v>856</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>67</v>
@@ -10038,10 +10035,10 @@
         <v>856</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C130" s="6" t="s">
         <v>1019</v>
+      </c>
+      <c r="C130" s="6">
+        <v>396</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>67</v>
@@ -10055,7 +10052,7 @@
         <v>1020</v>
       </c>
       <c r="C131" s="5">
-        <v>396</v>
+        <v>1273</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>67</v>
@@ -10068,8 +10065,8 @@
       <c r="B132" s="6" t="s">
         <v>1021</v>
       </c>
-      <c r="C132" s="6">
-        <v>1273</v>
+      <c r="C132" s="6" t="s">
+        <v>1022</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>67</v>
@@ -10080,10 +10077,10 @@
         <v>856</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C133" s="5" t="s">
         <v>1023</v>
+      </c>
+      <c r="C133" s="5">
+        <v>0.4</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>67</v>
@@ -10097,7 +10094,7 @@
         <v>1024</v>
       </c>
       <c r="C134" s="6">
-        <v>0.4</v>
+        <v>12</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>67</v>
@@ -10111,7 +10108,7 @@
         <v>1025</v>
       </c>
       <c r="C135" s="5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D135" s="5" t="s">
         <v>67</v>
@@ -10124,8 +10121,8 @@
       <c r="B136" s="6" t="s">
         <v>1026</v>
       </c>
-      <c r="C136" s="6">
-        <v>8</v>
+      <c r="C136" s="6" t="s">
+        <v>1027</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>67</v>
@@ -10133,13 +10130,13 @@
     </row>
     <row r="137" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>856</v>
+        <v>877</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C137" s="5" t="s">
         <v>1028</v>
+      </c>
+      <c r="C137" s="5">
+        <v>-1</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>67</v>
@@ -10147,7 +10144,7 @@
     </row>
     <row r="138" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
-        <v>877</v>
+        <v>890</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>1029</v>
@@ -10167,7 +10164,7 @@
         <v>1030</v>
       </c>
       <c r="C139" s="5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>67</v>
@@ -10175,7 +10172,7 @@
     </row>
     <row r="140" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
-        <v>890</v>
+        <v>858</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>1031</v>
@@ -10189,13 +10186,13 @@
     </row>
     <row r="141" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>1032</v>
       </c>
       <c r="C141" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>67</v>
@@ -10203,13 +10200,13 @@
     </row>
     <row r="142" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>1033</v>
       </c>
-      <c r="C142" s="6">
-        <v>3</v>
+      <c r="C142" s="6" t="s">
+        <v>1034</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>67</v>
@@ -10220,10 +10217,10 @@
         <v>858</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>67</v>
@@ -10234,10 +10231,10 @@
         <v>858</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C144" s="6" t="s">
         <v>1037</v>
+      </c>
+      <c r="C144" s="6">
+        <v>2</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>67</v>
@@ -10251,7 +10248,7 @@
         <v>1038</v>
       </c>
       <c r="C145" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>67</v>
@@ -10264,8 +10261,8 @@
       <c r="B146" s="6" t="s">
         <v>1039</v>
       </c>
-      <c r="C146" s="6">
-        <v>3</v>
+      <c r="C146" s="6" t="s">
+        <v>1040</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>67</v>
@@ -10276,10 +10273,10 @@
         <v>858</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C147" s="5" t="s">
         <v>1041</v>
+      </c>
+      <c r="C147" s="5">
+        <v>4</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>67</v>
@@ -10293,7 +10290,7 @@
         <v>1042</v>
       </c>
       <c r="C148" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>67</v>
@@ -10301,13 +10298,13 @@
     </row>
     <row r="149" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
-        <v>858</v>
+        <v>890</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>1043</v>
       </c>
       <c r="C149" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>67</v>
@@ -10321,7 +10318,7 @@
         <v>1044</v>
       </c>
       <c r="C150" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>67</v>
@@ -10335,7 +10332,7 @@
         <v>1045</v>
       </c>
       <c r="C151" s="5">
-        <v>8</v>
+        <v>2.6</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>67</v>
@@ -10348,8 +10345,8 @@
       <c r="B152" s="6" t="s">
         <v>1046</v>
       </c>
-      <c r="C152" s="6">
-        <v>2.6</v>
+      <c r="C152" s="6" t="s">
+        <v>1047</v>
       </c>
       <c r="D152" s="6" t="s">
         <v>67</v>
@@ -10357,13 +10354,13 @@
     </row>
     <row r="153" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
-        <v>890</v>
+        <v>864</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C153" s="5" t="s">
         <v>1048</v>
+      </c>
+      <c r="C153" s="5">
+        <v>5</v>
       </c>
       <c r="D153" s="5" t="s">
         <v>67</v>
@@ -10377,28 +10374,14 @@
         <v>1049</v>
       </c>
       <c r="C154" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D154" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="155" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="5" t="s">
-        <v>864</v>
-      </c>
-      <c r="B155" s="5" t="s">
-        <v>1050</v>
-      </c>
-      <c r="C155" s="5">
-        <v>1</v>
-      </c>
-      <c r="D155" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:D155"/>
+  <autoFilter ref="A4:D154"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>

--- a/docs/card-extraction-reference.xlsx
+++ b/docs/card-extraction-reference.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3249" uniqueCount="1050">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3258" uniqueCount="1053">
   <si>
     <t>현재 구현 규칙</t>
   </si>
@@ -2996,6 +2996,15 @@
     <t>PERCEPTION_WAIT_OBSERVATION_MIN</t>
   </si>
   <si>
+    <t>PLAIN_EDGE_MAX_BLOCKING_NODES</t>
+  </si>
+  <si>
+    <t>PLAIN_EDGE_MAX_LENGTH_FACTOR</t>
+  </si>
+  <si>
+    <t>PLAIN_EDGE_SCREEN_MAX_LENGTH_FACTOR</t>
+  </si>
+  <si>
     <t>POWER_CUT_DURATION</t>
   </si>
   <si>
@@ -3155,10 +3164,10 @@
     <t>TOWER_ELEVATOR_REQUIREMENT</t>
   </si>
   <si>
+    <t>TOWER_LOBBY_RING_RADIUS</t>
+  </si>
+  <si>
     <t>TOWER_LOBBY_ROOMS</t>
-  </si>
-  <si>
-    <t>TOWER_LOBBY_SPREAD</t>
   </si>
   <si>
     <t>TRACE_CLEANUP_TIME_BY_PERCEPTION</t>
@@ -8240,7 +8249,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D154"/>
+  <dimension ref="A1:D157"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -9752,13 +9761,13 @@
     </row>
     <row r="110" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
-        <v>890</v>
+        <v>856</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>991</v>
       </c>
       <c r="C110" s="6">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>67</v>
@@ -9766,13 +9775,13 @@
     </row>
     <row r="111" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>992</v>
       </c>
       <c r="C111" s="5">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>67</v>
@@ -9780,13 +9789,13 @@
     </row>
     <row r="112" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
-        <v>890</v>
+        <v>856</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>993</v>
       </c>
       <c r="C112" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>67</v>
@@ -9799,8 +9808,8 @@
       <c r="B113" s="5" t="s">
         <v>994</v>
       </c>
-      <c r="C113" s="5" t="s">
-        <v>995</v>
+      <c r="C113" s="5">
+        <v>30</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>67</v>
@@ -9811,10 +9820,10 @@
         <v>858</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>996</v>
-      </c>
-      <c r="C114" s="6" t="s">
-        <v>997</v>
+        <v>995</v>
+      </c>
+      <c r="C114" s="6">
+        <v>3</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>67</v>
@@ -9822,13 +9831,13 @@
     </row>
     <row r="115" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>864</v>
+        <v>890</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>998</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>999</v>
+        <v>996</v>
+      </c>
+      <c r="C115" s="5">
+        <v>3</v>
       </c>
       <c r="D115" s="5" t="s">
         <v>67</v>
@@ -9839,10 +9848,10 @@
         <v>890</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C116" s="6">
-        <v>3</v>
+        <v>997</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>998</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>67</v>
@@ -9850,13 +9859,13 @@
     </row>
     <row r="117" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>67</v>
@@ -9864,13 +9873,13 @@
     </row>
     <row r="118" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
-        <v>890</v>
+        <v>864</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>67</v>
@@ -9878,13 +9887,13 @@
     </row>
     <row r="119" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>858</v>
+        <v>890</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="C119" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>67</v>
@@ -9892,13 +9901,13 @@
     </row>
     <row r="120" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
-        <v>890</v>
+        <v>856</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C120" s="6">
-        <v>6</v>
+        <v>1004</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>1005</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>67</v>
@@ -9906,13 +9915,13 @@
     </row>
     <row r="121" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>864</v>
+        <v>890</v>
       </c>
       <c r="B121" s="5" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C121" s="5" t="s">
         <v>1007</v>
-      </c>
-      <c r="C121" s="5">
-        <v>180</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>67</v>
@@ -9920,13 +9929,13 @@
     </row>
     <row r="122" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>1008</v>
       </c>
       <c r="C122" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>67</v>
@@ -9934,13 +9943,13 @@
     </row>
     <row r="123" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>104</v>
+        <v>890</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>1009</v>
       </c>
       <c r="C123" s="5">
-        <v>240</v>
+        <v>6</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>67</v>
@@ -9948,13 +9957,13 @@
     </row>
     <row r="124" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>1010</v>
       </c>
       <c r="C124" s="6">
-        <v>4</v>
+        <v>180</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>67</v>
@@ -9962,13 +9971,13 @@
     </row>
     <row r="125" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>1011</v>
       </c>
       <c r="C125" s="5">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="D125" s="5" t="s">
         <v>67</v>
@@ -9976,13 +9985,13 @@
     </row>
     <row r="126" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
-        <v>858</v>
+        <v>104</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="C126" s="6" t="s">
-        <v>1013</v>
+      <c r="C126" s="6">
+        <v>240</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>67</v>
@@ -9990,13 +9999,13 @@
     </row>
     <row r="127" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>973</v>
+        <v>1013</v>
+      </c>
+      <c r="C127" s="5">
+        <v>4</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>67</v>
@@ -10004,13 +10013,13 @@
     </row>
     <row r="128" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C128" s="6" t="s">
-        <v>1016</v>
+        <v>1014</v>
+      </c>
+      <c r="C128" s="6">
+        <v>2</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>67</v>
@@ -10018,13 +10027,13 @@
     </row>
     <row r="129" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>67</v>
@@ -10032,13 +10041,13 @@
     </row>
     <row r="130" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>1019</v>
-      </c>
-      <c r="C130" s="6">
-        <v>396</v>
+        <v>1017</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>973</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>67</v>
@@ -10049,10 +10058,10 @@
         <v>856</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C131" s="5">
-        <v>1273</v>
+        <v>1018</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>1019</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>67</v>
@@ -10063,10 +10072,10 @@
         <v>856</v>
       </c>
       <c r="B132" s="6" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C132" s="6" t="s">
         <v>1021</v>
-      </c>
-      <c r="C132" s="6" t="s">
-        <v>1022</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>67</v>
@@ -10077,10 +10086,10 @@
         <v>856</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="C133" s="5">
-        <v>0.4</v>
+        <v>396</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>67</v>
@@ -10091,10 +10100,10 @@
         <v>856</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="C134" s="6">
-        <v>12</v>
+        <v>1273</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>67</v>
@@ -10105,10 +10114,10 @@
         <v>856</v>
       </c>
       <c r="B135" s="5" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C135" s="5" t="s">
         <v>1025</v>
-      </c>
-      <c r="C135" s="5">
-        <v>8</v>
       </c>
       <c r="D135" s="5" t="s">
         <v>67</v>
@@ -10121,8 +10130,8 @@
       <c r="B136" s="6" t="s">
         <v>1026</v>
       </c>
-      <c r="C136" s="6" t="s">
-        <v>1027</v>
+      <c r="C136" s="6">
+        <v>0.4</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>67</v>
@@ -10130,13 +10139,13 @@
     </row>
     <row r="137" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
-        <v>877</v>
+        <v>856</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="C137" s="5">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="D137" s="5" t="s">
         <v>67</v>
@@ -10144,13 +10153,13 @@
     </row>
     <row r="138" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
-        <v>890</v>
+        <v>856</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="C138" s="6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>67</v>
@@ -10158,13 +10167,13 @@
     </row>
     <row r="139" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="s">
-        <v>890</v>
+        <v>856</v>
       </c>
       <c r="B139" s="5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C139" s="5" t="s">
         <v>1030</v>
-      </c>
-      <c r="C139" s="5">
-        <v>1</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>67</v>
@@ -10172,13 +10181,13 @@
     </row>
     <row r="140" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>1031</v>
       </c>
       <c r="C140" s="6">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>67</v>
@@ -10186,13 +10195,13 @@
     </row>
     <row r="141" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
-        <v>864</v>
+        <v>890</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>1032</v>
       </c>
       <c r="C141" s="5">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>67</v>
@@ -10200,13 +10209,13 @@
     </row>
     <row r="142" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
-        <v>858</v>
+        <v>890</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>1033</v>
       </c>
-      <c r="C142" s="6" t="s">
-        <v>1034</v>
+      <c r="C142" s="6">
+        <v>1</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>67</v>
@@ -10217,10 +10226,10 @@
         <v>858</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>1036</v>
+        <v>1034</v>
+      </c>
+      <c r="C143" s="5">
+        <v>1</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>67</v>
@@ -10228,13 +10237,13 @@
     </row>
     <row r="144" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
-        <v>858</v>
+        <v>864</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="C144" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>67</v>
@@ -10245,10 +10254,10 @@
         <v>858</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C145" s="5">
-        <v>3</v>
+        <v>1036</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>1037</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>67</v>
@@ -10259,10 +10268,10 @@
         <v>858</v>
       </c>
       <c r="B146" s="6" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C146" s="6" t="s">
         <v>1039</v>
-      </c>
-      <c r="C146" s="6" t="s">
-        <v>1040</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>67</v>
@@ -10273,10 +10282,10 @@
         <v>858</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C147" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>67</v>
@@ -10287,10 +10296,10 @@
         <v>858</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C148" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>67</v>
@@ -10298,13 +10307,13 @@
     </row>
     <row r="149" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
-        <v>890</v>
+        <v>858</v>
       </c>
       <c r="B149" s="5" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C149" s="5" t="s">
         <v>1043</v>
-      </c>
-      <c r="C149" s="5">
-        <v>3</v>
       </c>
       <c r="D149" s="5" t="s">
         <v>67</v>
@@ -10312,13 +10321,13 @@
     </row>
     <row r="150" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
-        <v>890</v>
+        <v>858</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>1044</v>
       </c>
       <c r="C150" s="6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>67</v>
@@ -10326,13 +10335,13 @@
     </row>
     <row r="151" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
-        <v>890</v>
+        <v>858</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>1045</v>
       </c>
       <c r="C151" s="5">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>67</v>
@@ -10345,8 +10354,8 @@
       <c r="B152" s="6" t="s">
         <v>1046</v>
       </c>
-      <c r="C152" s="6" t="s">
-        <v>1047</v>
+      <c r="C152" s="6">
+        <v>3</v>
       </c>
       <c r="D152" s="6" t="s">
         <v>67</v>
@@ -10354,13 +10363,13 @@
     </row>
     <row r="153" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
-        <v>864</v>
+        <v>890</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C153" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D153" s="5" t="s">
         <v>67</v>
@@ -10368,20 +10377,62 @@
     </row>
     <row r="154" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
-        <v>864</v>
+        <v>890</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C154" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D154" s="6" t="s">
         <v>67</v>
       </c>
     </row>
+    <row r="155" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="5" t="s">
+        <v>890</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D155" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="6" t="s">
+        <v>864</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C156" s="6">
+        <v>5</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="5" t="s">
+        <v>864</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C157" s="5">
+        <v>1</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:D154"/>
+  <autoFilter ref="A4:D157"/>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
